--- a/pages/video_analysis/IP_Master_Women.xlsx
+++ b/pages/video_analysis/IP_Master_Women.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{985A9FFD-8F2E-4D53-8360-4B27C8DD32CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5594BCCF-5F4D-4C7B-B827-5C87D4D2BD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="456" windowWidth="12468" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="11">
   <si>
     <t>Title</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>No Change</t>
+  </si>
+  <si>
+    <t>https://youtu.be/9AmV3XlPZeA</t>
   </si>
 </sst>
 </file>
@@ -472,6 +475,9 @@
       <c r="G2" t="s">
         <v>9</v>
       </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">

--- a/pages/video_analysis/IP_Master_Women.xlsx
+++ b/pages/video_analysis/IP_Master_Women.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5594BCCF-5F4D-4C7B-B827-5C87D4D2BD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8650F8-B4BA-4516-9B1F-DA0A5F7F6B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9504" yWindow="1128" windowWidth="9612" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="15">
   <si>
     <t>Title</t>
   </si>
@@ -49,10 +49,22 @@
     <t>26/7/2023 Sami Donnelly Race Sim</t>
   </si>
   <si>
+    <t>3/8/2023 Sami Donnelly IP Q Glasgow WCH</t>
+  </si>
+  <si>
+    <t>3/8/2023 Bryony Botha IP Q Glasgow WCH</t>
+  </si>
+  <si>
     <t>No Change</t>
   </si>
   <si>
     <t>https://youtu.be/9AmV3XlPZeA</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UQrTnsCV3nI</t>
+  </si>
+  <si>
+    <t>https://youtu.be/63pks-zGKqc</t>
   </si>
 </sst>
 </file>
@@ -62,7 +74,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,6 +89,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -111,17 +130,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -424,8 +449,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -473,10 +508,10 @@
         <v>24.25</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -499,7 +534,7 @@
         <v>43.95</v>
       </c>
       <c r="G3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -522,7 +557,7 @@
         <v>50.45</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -545,7 +580,7 @@
         <v>53.57</v>
       </c>
       <c r="G5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -568,7 +603,7 @@
         <v>54.88</v>
       </c>
       <c r="G6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -591,7 +626,7 @@
         <v>54.61</v>
       </c>
       <c r="G7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -614,7 +649,7 @@
         <v>55.42</v>
       </c>
       <c r="G8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -637,7 +672,7 @@
         <v>55.42</v>
       </c>
       <c r="G9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -660,7 +695,7 @@
         <v>54.88</v>
       </c>
       <c r="G10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -683,7 +718,7 @@
         <v>54.35</v>
       </c>
       <c r="G11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -706,7 +741,7 @@
         <v>54.35</v>
       </c>
       <c r="G12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -729,7 +764,7 @@
         <v>54.09</v>
       </c>
       <c r="G13" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -752,7 +787,7 @@
         <v>54.35</v>
       </c>
       <c r="G14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -775,7 +810,7 @@
         <v>53.57</v>
       </c>
       <c r="G15" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -798,7 +833,7 @@
         <v>54.09</v>
       </c>
       <c r="G16" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -821,7 +856,7 @@
         <v>53.83</v>
       </c>
       <c r="G17" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -844,7 +879,7 @@
         <v>52.08</v>
       </c>
       <c r="G18" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -867,7 +902,7 @@
         <v>56.25</v>
       </c>
       <c r="G19" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -890,7 +925,7 @@
         <v>54.35</v>
       </c>
       <c r="G20" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -913,7 +948,7 @@
         <v>54.35</v>
       </c>
       <c r="G21" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -936,7 +971,7 @@
         <v>54.09</v>
       </c>
       <c r="G22" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -959,7 +994,7 @@
         <v>54.09</v>
       </c>
       <c r="G23" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -982,7 +1017,7 @@
         <v>54.35</v>
       </c>
       <c r="G24" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1005,7 +1040,7 @@
         <v>54.88</v>
       </c>
       <c r="G25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1028,7 +1063,7 @@
         <v>54.09</v>
       </c>
       <c r="G26" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1051,7 +1086,7 @@
         <v>54.09</v>
       </c>
       <c r="G27" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1074,7 +1109,7 @@
         <v>54.09</v>
       </c>
       <c r="G28" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1097,7 +1132,7 @@
         <v>53.57</v>
       </c>
       <c r="G29" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1120,7 +1155,7 @@
         <v>54.09</v>
       </c>
       <c r="G30" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -1143,7 +1178,7 @@
         <v>53.07</v>
       </c>
       <c r="G31" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -1166,7 +1201,7 @@
         <v>53.32</v>
       </c>
       <c r="G32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -1189,7 +1224,7 @@
         <v>53.32</v>
       </c>
       <c r="G33" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -1212,7 +1247,7 @@
         <v>52.33</v>
       </c>
       <c r="G34" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -1235,7 +1270,7 @@
         <v>51.84</v>
       </c>
       <c r="G35" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -1258,7 +1293,7 @@
         <v>52.08</v>
       </c>
       <c r="G36" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -1281,7 +1316,7 @@
         <v>52.33</v>
       </c>
       <c r="G37" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -1304,7 +1339,7 @@
         <v>52.08</v>
       </c>
       <c r="G38" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -1327,7 +1362,7 @@
         <v>51.61</v>
       </c>
       <c r="G39" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -1350,7 +1385,7 @@
         <v>52.33</v>
       </c>
       <c r="G40" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -1373,7 +1408,7 @@
         <v>51.84</v>
       </c>
       <c r="G41" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -1396,7 +1431,7 @@
         <v>51.61</v>
       </c>
       <c r="G42" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -1419,7 +1454,7 @@
         <v>51.61</v>
       </c>
       <c r="G43" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -1442,7 +1477,7 @@
         <v>51.61</v>
       </c>
       <c r="G44" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -1465,7 +1500,7 @@
         <v>51.14</v>
       </c>
       <c r="G45" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -1488,7 +1523,7 @@
         <v>51.37</v>
       </c>
       <c r="G46" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -1511,7 +1546,7 @@
         <v>51.37</v>
       </c>
       <c r="G47" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -1534,10 +1569,10 @@
         <v>51.37</v>
       </c>
       <c r="G48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -1557,10 +1592,2227 @@
         <v>51.14</v>
       </c>
       <c r="G49" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C50">
+        <v>62.5</v>
+      </c>
+      <c r="D50">
+        <v>9.4599999999991269</v>
+      </c>
+      <c r="E50">
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="F50">
+        <v>23.78</v>
+      </c>
+      <c r="G50" t="s">
+        <v>11</v>
+      </c>
+      <c r="H50" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C51">
+        <v>125</v>
+      </c>
+      <c r="D51">
+        <v>14.659999999999849</v>
+      </c>
+      <c r="E51">
+        <v>5.2</v>
+      </c>
+      <c r="F51">
+        <v>43.27</v>
+      </c>
+      <c r="G51" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C52">
+        <v>187.5</v>
+      </c>
+      <c r="D52">
+        <v>19.239999999999782</v>
+      </c>
+      <c r="E52">
+        <v>4.58</v>
+      </c>
+      <c r="F52">
+        <v>49.13</v>
+      </c>
+      <c r="G52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C53">
+        <v>250</v>
+      </c>
+      <c r="D53">
+        <v>23.52000000000044</v>
+      </c>
+      <c r="E53">
+        <v>4.28</v>
+      </c>
+      <c r="F53">
+        <v>52.57</v>
+      </c>
+      <c r="G53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C54">
+        <v>312.5</v>
+      </c>
+      <c r="D54">
+        <v>27.639999999999421</v>
+      </c>
+      <c r="E54">
+        <v>4.12</v>
+      </c>
+      <c r="F54">
+        <v>54.61</v>
+      </c>
+      <c r="G54" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C55">
+        <v>375</v>
+      </c>
+      <c r="D55">
+        <v>31.760000000000218</v>
+      </c>
+      <c r="E55">
+        <v>4.12</v>
+      </c>
+      <c r="F55">
+        <v>54.61</v>
+      </c>
+      <c r="G55" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C56">
+        <v>437.5</v>
+      </c>
+      <c r="D56">
+        <v>35.859999999998763</v>
+      </c>
+      <c r="E56">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F56">
+        <v>54.88</v>
+      </c>
+      <c r="G56" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C57">
+        <v>500</v>
+      </c>
+      <c r="D57">
+        <v>39.93999999999869</v>
+      </c>
+      <c r="E57">
+        <v>4.08</v>
+      </c>
+      <c r="F57">
+        <v>55.15</v>
+      </c>
+      <c r="G57" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C58">
+        <v>562.5</v>
+      </c>
+      <c r="D58">
+        <v>44.020000000000437</v>
+      </c>
+      <c r="E58">
+        <v>4.08</v>
+      </c>
+      <c r="F58">
+        <v>55.15</v>
+      </c>
+      <c r="G58" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C59">
+        <v>625</v>
+      </c>
+      <c r="D59">
+        <v>48.119999999998981</v>
+      </c>
+      <c r="E59">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F59">
+        <v>54.88</v>
+      </c>
+      <c r="G59" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C60">
+        <v>687.5</v>
+      </c>
+      <c r="D60">
+        <v>52.249309999999241</v>
+      </c>
+      <c r="E60">
+        <v>4.1289999999999996</v>
+      </c>
+      <c r="F60">
+        <v>54.49</v>
+      </c>
+      <c r="G60" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C61">
+        <v>750</v>
+      </c>
+      <c r="D61">
+        <v>56.359999999998763</v>
+      </c>
+      <c r="E61">
+        <v>4.1109999999999998</v>
+      </c>
+      <c r="F61">
+        <v>54.73</v>
+      </c>
+      <c r="G61" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C62">
+        <v>812.5</v>
+      </c>
+      <c r="D62">
+        <v>60.520000000000437</v>
+      </c>
+      <c r="E62">
+        <v>4.16</v>
+      </c>
+      <c r="F62">
+        <v>54.09</v>
+      </c>
+      <c r="G62" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B63" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C63">
+        <v>875</v>
+      </c>
+      <c r="D63">
+        <v>64.719999999999345</v>
+      </c>
+      <c r="E63">
+        <v>4.2</v>
+      </c>
+      <c r="F63">
+        <v>53.57</v>
+      </c>
+      <c r="G63" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B64" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C64">
+        <v>937.5</v>
+      </c>
+      <c r="D64">
+        <v>68.922959999999875</v>
+      </c>
+      <c r="E64">
+        <v>4.2030000000000003</v>
+      </c>
+      <c r="F64">
+        <v>53.53</v>
+      </c>
+      <c r="G64" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B65" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C65">
+        <v>1000</v>
+      </c>
+      <c r="D65">
+        <v>73.119999999998981</v>
+      </c>
+      <c r="E65">
+        <v>4.1970000000000001</v>
+      </c>
+      <c r="F65">
+        <v>53.61</v>
+      </c>
+      <c r="G65" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>9</v>
+      </c>
+      <c r="B66" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C66">
+        <v>1062.5</v>
+      </c>
+      <c r="D66">
+        <v>77.319999999999709</v>
+      </c>
+      <c r="E66">
+        <v>4.2</v>
+      </c>
+      <c r="F66">
+        <v>53.57</v>
+      </c>
+      <c r="G66" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>9</v>
+      </c>
+      <c r="B67" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C67">
+        <v>1125</v>
+      </c>
+      <c r="D67">
+        <v>81.520000000000437</v>
+      </c>
+      <c r="E67">
+        <v>4.2</v>
+      </c>
+      <c r="F67">
+        <v>53.57</v>
+      </c>
+      <c r="G67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>9</v>
+      </c>
+      <c r="B68" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C68">
+        <v>1187.5</v>
+      </c>
+      <c r="D68">
+        <v>85.739999999999782</v>
+      </c>
+      <c r="E68">
+        <v>4.22</v>
+      </c>
+      <c r="F68">
+        <v>53.32</v>
+      </c>
+      <c r="G68" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>9</v>
+      </c>
+      <c r="B69" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C69">
+        <v>1250</v>
+      </c>
+      <c r="D69">
+        <v>89.959999999999127</v>
+      </c>
+      <c r="E69">
+        <v>4.22</v>
+      </c>
+      <c r="F69">
+        <v>53.32</v>
+      </c>
+      <c r="G69" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B70" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C70">
+        <v>1312.5</v>
+      </c>
+      <c r="D70">
+        <v>94.180000000000291</v>
+      </c>
+      <c r="E70">
+        <v>4.22</v>
+      </c>
+      <c r="F70">
+        <v>53.32</v>
+      </c>
+      <c r="G70" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>9</v>
+      </c>
+      <c r="B71" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C71">
+        <v>1375</v>
+      </c>
+      <c r="D71">
+        <v>98.3799999999992</v>
+      </c>
+      <c r="E71">
+        <v>4.2</v>
+      </c>
+      <c r="F71">
+        <v>53.57</v>
+      </c>
+      <c r="G71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B72" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C72">
+        <v>1437.5</v>
+      </c>
+      <c r="D72">
+        <v>102.619999999999</v>
+      </c>
+      <c r="E72">
+        <v>4.24</v>
+      </c>
+      <c r="F72">
+        <v>53.07</v>
+      </c>
+      <c r="G72" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>9</v>
+      </c>
+      <c r="B73" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C73">
+        <v>1500</v>
+      </c>
+      <c r="D73">
+        <v>106.85999999999881</v>
+      </c>
+      <c r="E73">
+        <v>4.24</v>
+      </c>
+      <c r="F73">
+        <v>53.07</v>
+      </c>
+      <c r="G73" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>9</v>
+      </c>
+      <c r="B74" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C74">
+        <v>1562.5</v>
+      </c>
+      <c r="D74">
+        <v>111.0764999999992</v>
+      </c>
+      <c r="E74">
+        <v>4.2169999999999996</v>
+      </c>
+      <c r="F74">
+        <v>53.36</v>
+      </c>
+      <c r="G74" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>9</v>
+      </c>
+      <c r="B75" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C75">
+        <v>1625</v>
+      </c>
+      <c r="D75">
+        <v>115.2999999999993</v>
+      </c>
+      <c r="E75">
+        <v>4.2240000000000002</v>
+      </c>
+      <c r="F75">
+        <v>53.27</v>
+      </c>
+      <c r="G75" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>9</v>
+      </c>
+      <c r="B76" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C76">
+        <v>1687.5</v>
+      </c>
+      <c r="D76">
+        <v>119.52000000000039</v>
+      </c>
+      <c r="E76">
+        <v>4.22</v>
+      </c>
+      <c r="F76">
+        <v>53.32</v>
+      </c>
+      <c r="G76" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>9</v>
+      </c>
+      <c r="B77" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C77">
+        <v>1750</v>
+      </c>
+      <c r="D77">
+        <v>123.7600000000002</v>
+      </c>
+      <c r="E77">
+        <v>4.24</v>
+      </c>
+      <c r="F77">
+        <v>53.07</v>
+      </c>
+      <c r="G77" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>9</v>
+      </c>
+      <c r="B78" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C78">
+        <v>1812.5</v>
+      </c>
+      <c r="D78">
+        <v>127.97999999999961</v>
+      </c>
+      <c r="E78">
+        <v>4.22</v>
+      </c>
+      <c r="F78">
+        <v>53.32</v>
+      </c>
+      <c r="G78" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>9</v>
+      </c>
+      <c r="B79" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C79">
+        <v>1875</v>
+      </c>
+      <c r="D79">
+        <v>132.19999999999891</v>
+      </c>
+      <c r="E79">
+        <v>4.22</v>
+      </c>
+      <c r="F79">
+        <v>53.32</v>
+      </c>
+      <c r="G79" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>9</v>
+      </c>
+      <c r="B80" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C80">
+        <v>1937.5</v>
+      </c>
+      <c r="D80">
+        <v>136.4599999999991</v>
+      </c>
+      <c r="E80">
+        <v>4.26</v>
+      </c>
+      <c r="F80">
+        <v>52.82</v>
+      </c>
+      <c r="G80" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>9</v>
+      </c>
+      <c r="B81" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C81">
+        <v>2000</v>
+      </c>
+      <c r="D81">
+        <v>140.68000000000029</v>
+      </c>
+      <c r="E81">
+        <v>4.22</v>
+      </c>
+      <c r="F81">
+        <v>53.32</v>
+      </c>
+      <c r="G81" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>9</v>
+      </c>
+      <c r="B82" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C82">
+        <v>2062.5</v>
+      </c>
+      <c r="D82">
+        <v>144.9200000000001</v>
+      </c>
+      <c r="E82">
+        <v>4.24</v>
+      </c>
+      <c r="F82">
+        <v>53.07</v>
+      </c>
+      <c r="G82" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>9</v>
+      </c>
+      <c r="B83" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C83">
+        <v>2125</v>
+      </c>
+      <c r="D83">
+        <v>149.13999999999939</v>
+      </c>
+      <c r="E83">
+        <v>4.22</v>
+      </c>
+      <c r="F83">
+        <v>53.32</v>
+      </c>
+      <c r="G83" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>9</v>
+      </c>
+      <c r="B84" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C84">
+        <v>2187.5</v>
+      </c>
+      <c r="D84">
+        <v>153.35999999999879</v>
+      </c>
+      <c r="E84">
+        <v>4.22</v>
+      </c>
+      <c r="F84">
+        <v>53.32</v>
+      </c>
+      <c r="G84" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>9</v>
+      </c>
+      <c r="B85" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C85">
+        <v>2250</v>
+      </c>
+      <c r="D85">
+        <v>157.55999999999949</v>
+      </c>
+      <c r="E85">
+        <v>4.2</v>
+      </c>
+      <c r="F85">
+        <v>53.57</v>
+      </c>
+      <c r="G85" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>9</v>
+      </c>
+      <c r="B86" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C86">
+        <v>2312.5</v>
+      </c>
+      <c r="D86">
+        <v>161.77999999999881</v>
+      </c>
+      <c r="E86">
+        <v>4.22</v>
+      </c>
+      <c r="F86">
+        <v>53.32</v>
+      </c>
+      <c r="G86" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>9</v>
+      </c>
+      <c r="B87" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C87">
+        <v>2375</v>
+      </c>
+      <c r="D87">
+        <v>165.97999999999959</v>
+      </c>
+      <c r="E87">
+        <v>4.2</v>
+      </c>
+      <c r="F87">
+        <v>53.57</v>
+      </c>
+      <c r="G87" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>9</v>
+      </c>
+      <c r="B88" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C88">
+        <v>2437.5</v>
+      </c>
+      <c r="D88">
+        <v>170.13999999999939</v>
+      </c>
+      <c r="E88">
+        <v>4.16</v>
+      </c>
+      <c r="F88">
+        <v>54.09</v>
+      </c>
+      <c r="G88" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>9</v>
+      </c>
+      <c r="B89" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C89">
+        <v>2500</v>
+      </c>
+      <c r="D89">
+        <v>174.27999999999881</v>
+      </c>
+      <c r="E89">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="F89">
+        <v>54.35</v>
+      </c>
+      <c r="G89" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>9</v>
+      </c>
+      <c r="B90" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C90">
+        <v>2562.5</v>
+      </c>
+      <c r="D90">
+        <v>178.43999999999869</v>
+      </c>
+      <c r="E90">
+        <v>4.16</v>
+      </c>
+      <c r="F90">
+        <v>54.09</v>
+      </c>
+      <c r="G90" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>9</v>
+      </c>
+      <c r="B91" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C91">
+        <v>2625</v>
+      </c>
+      <c r="D91">
+        <v>182.60000000000039</v>
+      </c>
+      <c r="E91">
+        <v>4.16</v>
+      </c>
+      <c r="F91">
+        <v>54.09</v>
+      </c>
+      <c r="G91" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>9</v>
+      </c>
+      <c r="B92" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C92">
+        <v>2687.5</v>
+      </c>
+      <c r="D92">
+        <v>186.76000000000019</v>
+      </c>
+      <c r="E92">
+        <v>4.16</v>
+      </c>
+      <c r="F92">
+        <v>54.09</v>
+      </c>
+      <c r="G92" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>9</v>
+      </c>
+      <c r="B93" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C93">
+        <v>2750</v>
+      </c>
+      <c r="D93">
+        <v>190.9200000000001</v>
+      </c>
+      <c r="E93">
+        <v>4.16</v>
+      </c>
+      <c r="F93">
+        <v>54.09</v>
+      </c>
+      <c r="G93" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>9</v>
+      </c>
+      <c r="B94" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C94">
+        <v>2812.5</v>
+      </c>
+      <c r="D94">
+        <v>195.05999999999949</v>
+      </c>
+      <c r="E94">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="F94">
+        <v>54.35</v>
+      </c>
+      <c r="G94" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>9</v>
+      </c>
+      <c r="B95" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C95">
+        <v>2875</v>
+      </c>
+      <c r="D95">
+        <v>199.21999999999929</v>
+      </c>
+      <c r="E95">
+        <v>4.16</v>
+      </c>
+      <c r="F95">
+        <v>54.09</v>
+      </c>
+      <c r="G95" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>9</v>
+      </c>
+      <c r="B96" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C96">
+        <v>2937.5</v>
+      </c>
+      <c r="D96">
+        <v>203.35999999999879</v>
+      </c>
+      <c r="E96">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="F96">
+        <v>54.35</v>
+      </c>
+      <c r="G96" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>9</v>
+      </c>
+      <c r="B97" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C97">
+        <v>3000</v>
+      </c>
+      <c r="D97">
+        <v>207.60000000000039</v>
+      </c>
+      <c r="E97">
+        <v>4.24</v>
+      </c>
+      <c r="F97">
+        <v>53.07</v>
+      </c>
+      <c r="G97" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>10</v>
+      </c>
+      <c r="B98" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C98">
+        <v>62.5</v>
+      </c>
+      <c r="D98">
+        <v>9.5</v>
+      </c>
+      <c r="E98">
+        <v>9.5</v>
+      </c>
+      <c r="F98">
+        <v>23.68</v>
+      </c>
+      <c r="G98" t="s">
+        <v>11</v>
+      </c>
+      <c r="H98" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>10</v>
+      </c>
+      <c r="B99" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C99">
+        <v>125</v>
+      </c>
+      <c r="D99">
+        <v>14.659999999999849</v>
+      </c>
+      <c r="E99">
+        <v>5.16</v>
+      </c>
+      <c r="F99">
+        <v>43.6</v>
+      </c>
+      <c r="G99" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>10</v>
+      </c>
+      <c r="B100" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C100">
+        <v>187.5</v>
+      </c>
+      <c r="D100">
+        <v>19.099999999998541</v>
+      </c>
+      <c r="E100">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="F100">
+        <v>50.68</v>
+      </c>
+      <c r="G100" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>10</v>
+      </c>
+      <c r="B101" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C101">
+        <v>250</v>
+      </c>
+      <c r="D101">
+        <v>23.319999999999709</v>
+      </c>
+      <c r="E101">
+        <v>4.22</v>
+      </c>
+      <c r="F101">
+        <v>53.32</v>
+      </c>
+      <c r="G101" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>10</v>
+      </c>
+      <c r="B102" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C102">
+        <v>312.5</v>
+      </c>
+      <c r="D102">
+        <v>27.3799999999992</v>
+      </c>
+      <c r="E102">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="F102">
+        <v>55.42</v>
+      </c>
+      <c r="G102" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>10</v>
+      </c>
+      <c r="B103" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C103">
+        <v>375</v>
+      </c>
+      <c r="D103">
+        <v>31.39999999999964</v>
+      </c>
+      <c r="E103">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F103">
+        <v>55.97</v>
+      </c>
+      <c r="G103" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>10</v>
+      </c>
+      <c r="B104" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C104">
+        <v>437.5</v>
+      </c>
+      <c r="D104">
+        <v>35.399999999999643</v>
+      </c>
+      <c r="E104">
+        <v>4</v>
+      </c>
+      <c r="F104">
+        <v>56.25</v>
+      </c>
+      <c r="G104" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>10</v>
+      </c>
+      <c r="B105" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C105">
+        <v>500</v>
+      </c>
+      <c r="D105">
+        <v>39.339999999998327</v>
+      </c>
+      <c r="E105">
+        <v>3.94</v>
+      </c>
+      <c r="F105">
+        <v>57.11</v>
+      </c>
+      <c r="G105" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>10</v>
+      </c>
+      <c r="B106" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C106">
+        <v>562.5</v>
+      </c>
+      <c r="D106">
+        <v>43.299999999999272</v>
+      </c>
+      <c r="E106">
+        <v>3.96</v>
+      </c>
+      <c r="F106">
+        <v>56.82</v>
+      </c>
+      <c r="G106" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>10</v>
+      </c>
+      <c r="B107" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C107">
+        <v>625</v>
+      </c>
+      <c r="D107">
+        <v>47.299999999999272</v>
+      </c>
+      <c r="E107">
+        <v>4</v>
+      </c>
+      <c r="F107">
+        <v>56.25</v>
+      </c>
+      <c r="G107" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>10</v>
+      </c>
+      <c r="B108" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C108">
+        <v>687.5</v>
+      </c>
+      <c r="D108">
+        <v>51.259999999998399</v>
+      </c>
+      <c r="E108">
+        <v>3.96</v>
+      </c>
+      <c r="F108">
+        <v>56.82</v>
+      </c>
+      <c r="G108" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>10</v>
+      </c>
+      <c r="B109" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C109">
+        <v>750</v>
+      </c>
+      <c r="D109">
+        <v>55.239999999999782</v>
+      </c>
+      <c r="E109">
+        <v>3.98</v>
+      </c>
+      <c r="F109">
+        <v>56.53</v>
+      </c>
+      <c r="G109" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>10</v>
+      </c>
+      <c r="B110" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C110">
+        <v>812.5</v>
+      </c>
+      <c r="D110">
+        <v>59.219999999999352</v>
+      </c>
+      <c r="E110">
+        <v>3.98</v>
+      </c>
+      <c r="F110">
+        <v>56.53</v>
+      </c>
+      <c r="G110" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>10</v>
+      </c>
+      <c r="B111" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C111">
+        <v>875</v>
+      </c>
+      <c r="D111">
+        <v>63.239999999999782</v>
+      </c>
+      <c r="E111">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F111">
+        <v>55.97</v>
+      </c>
+      <c r="G111" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>10</v>
+      </c>
+      <c r="B112" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C112">
+        <v>937.5</v>
+      </c>
+      <c r="D112">
+        <v>67.259999999998399</v>
+      </c>
+      <c r="E112">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F112">
+        <v>55.97</v>
+      </c>
+      <c r="G112" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>10</v>
+      </c>
+      <c r="B113" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C113">
+        <v>1000</v>
+      </c>
+      <c r="D113">
+        <v>71.279999999998836</v>
+      </c>
+      <c r="E113">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F113">
+        <v>55.97</v>
+      </c>
+      <c r="G113" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>10</v>
+      </c>
+      <c r="B114" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C114">
+        <v>1062.5</v>
+      </c>
+      <c r="D114">
+        <v>75.299999999999272</v>
+      </c>
+      <c r="E114">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F114">
+        <v>55.97</v>
+      </c>
+      <c r="G114" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>10</v>
+      </c>
+      <c r="B115" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C115">
+        <v>1125</v>
+      </c>
+      <c r="D115">
+        <v>79.339999999998327</v>
+      </c>
+      <c r="E115">
+        <v>4.04</v>
+      </c>
+      <c r="F115">
+        <v>55.69</v>
+      </c>
+      <c r="G115" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>10</v>
+      </c>
+      <c r="B116" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C116">
+        <v>1187.5</v>
+      </c>
+      <c r="D116">
+        <v>83.359999999998763</v>
+      </c>
+      <c r="E116">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F116">
+        <v>55.97</v>
+      </c>
+      <c r="G116" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>10</v>
+      </c>
+      <c r="B117" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C117">
+        <v>1250</v>
+      </c>
+      <c r="D117">
+        <v>87.359999999998763</v>
+      </c>
+      <c r="E117">
+        <v>4</v>
+      </c>
+      <c r="F117">
+        <v>56.25</v>
+      </c>
+      <c r="G117" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>10</v>
+      </c>
+      <c r="B118" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C118">
+        <v>1312.5</v>
+      </c>
+      <c r="D118">
+        <v>91.3799999999992</v>
+      </c>
+      <c r="E118">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F118">
+        <v>55.97</v>
+      </c>
+      <c r="G118" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>10</v>
+      </c>
+      <c r="B119" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C119">
+        <v>1375</v>
+      </c>
+      <c r="D119">
+        <v>95.3799999999992</v>
+      </c>
+      <c r="E119">
+        <v>4</v>
+      </c>
+      <c r="F119">
+        <v>56.25</v>
+      </c>
+      <c r="G119" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>10</v>
+      </c>
+      <c r="B120" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C120">
+        <v>1437.5</v>
+      </c>
+      <c r="D120">
+        <v>99.399999999999636</v>
+      </c>
+      <c r="E120">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F120">
+        <v>55.97</v>
+      </c>
+      <c r="G120" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>10</v>
+      </c>
+      <c r="B121" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C121">
+        <v>1500</v>
+      </c>
+      <c r="D121">
+        <v>103.4200000000001</v>
+      </c>
+      <c r="E121">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F121">
+        <v>55.97</v>
+      </c>
+      <c r="G121" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>10</v>
+      </c>
+      <c r="B122" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C122">
+        <v>1562.5</v>
+      </c>
+      <c r="D122">
+        <v>107.4399999999987</v>
+      </c>
+      <c r="E122">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F122">
+        <v>55.97</v>
+      </c>
+      <c r="G122" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>10</v>
+      </c>
+      <c r="B123" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C123">
+        <v>1625</v>
+      </c>
+      <c r="D123">
+        <v>111.4399999999987</v>
+      </c>
+      <c r="E123">
+        <v>4</v>
+      </c>
+      <c r="F123">
+        <v>56.25</v>
+      </c>
+      <c r="G123" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>10</v>
+      </c>
+      <c r="B124" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C124">
+        <v>1687.5</v>
+      </c>
+      <c r="D124">
+        <v>115.4599999999991</v>
+      </c>
+      <c r="E124">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F124">
+        <v>55.97</v>
+      </c>
+      <c r="G124" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>10</v>
+      </c>
+      <c r="B125" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C125">
+        <v>1750</v>
+      </c>
+      <c r="D125">
+        <v>119.47999999999961</v>
+      </c>
+      <c r="E125">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F125">
+        <v>55.97</v>
+      </c>
+      <c r="G125" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>10</v>
+      </c>
+      <c r="B126" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C126">
+        <v>1812.5</v>
+      </c>
+      <c r="D126">
+        <v>123.47999999999961</v>
+      </c>
+      <c r="E126">
+        <v>4</v>
+      </c>
+      <c r="F126">
+        <v>56.25</v>
+      </c>
+      <c r="G126" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>10</v>
+      </c>
+      <c r="B127" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C127">
+        <v>1875</v>
+      </c>
+      <c r="D127">
+        <v>127.47999999999961</v>
+      </c>
+      <c r="E127">
+        <v>4</v>
+      </c>
+      <c r="F127">
+        <v>56.25</v>
+      </c>
+      <c r="G127" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>10</v>
+      </c>
+      <c r="B128" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C128">
+        <v>1937.5</v>
+      </c>
+      <c r="D128">
+        <v>131.47999999999959</v>
+      </c>
+      <c r="E128">
+        <v>4</v>
+      </c>
+      <c r="F128">
+        <v>56.25</v>
+      </c>
+      <c r="G128" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>10</v>
+      </c>
+      <c r="B129" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C129">
+        <v>2000</v>
+      </c>
+      <c r="D129">
+        <v>135.4599999999991</v>
+      </c>
+      <c r="E129">
+        <v>3.98</v>
+      </c>
+      <c r="F129">
+        <v>56.53</v>
+      </c>
+      <c r="G129" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>10</v>
+      </c>
+      <c r="B130" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C130">
+        <v>2062.5</v>
+      </c>
+      <c r="D130">
+        <v>139.47999999999959</v>
+      </c>
+      <c r="E130">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F130">
+        <v>55.97</v>
+      </c>
+      <c r="G130" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>10</v>
+      </c>
+      <c r="B131" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C131">
+        <v>2125</v>
+      </c>
+      <c r="D131">
+        <v>143.47999999999959</v>
+      </c>
+      <c r="E131">
+        <v>4</v>
+      </c>
+      <c r="F131">
+        <v>56.25</v>
+      </c>
+      <c r="G131" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>10</v>
+      </c>
+      <c r="B132" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C132">
+        <v>2187.5</v>
+      </c>
+      <c r="D132">
+        <v>147.5</v>
+      </c>
+      <c r="E132">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F132">
+        <v>55.97</v>
+      </c>
+      <c r="G132" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>10</v>
+      </c>
+      <c r="B133" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C133">
+        <v>2250</v>
+      </c>
+      <c r="D133">
+        <v>151.5</v>
+      </c>
+      <c r="E133">
+        <v>4</v>
+      </c>
+      <c r="F133">
+        <v>56.25</v>
+      </c>
+      <c r="G133" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>10</v>
+      </c>
+      <c r="B134" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C134">
+        <v>2312.5</v>
+      </c>
+      <c r="D134">
+        <v>155.51999999999859</v>
+      </c>
+      <c r="E134">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F134">
+        <v>55.97</v>
+      </c>
+      <c r="G134" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>10</v>
+      </c>
+      <c r="B135" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C135">
+        <v>2375</v>
+      </c>
+      <c r="D135">
+        <v>159.53999999999911</v>
+      </c>
+      <c r="E135">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F135">
+        <v>55.97</v>
+      </c>
+      <c r="G135" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>10</v>
+      </c>
+      <c r="B136" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C136">
+        <v>2437.5</v>
+      </c>
+      <c r="D136">
+        <v>163.5799999999999</v>
+      </c>
+      <c r="E136">
+        <v>4.04</v>
+      </c>
+      <c r="F136">
+        <v>55.69</v>
+      </c>
+      <c r="G136" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>10</v>
+      </c>
+      <c r="B137" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C137">
+        <v>2500</v>
+      </c>
+      <c r="D137">
+        <v>167.63999999999939</v>
+      </c>
+      <c r="E137">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="F137">
+        <v>55.42</v>
+      </c>
+      <c r="G137" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>10</v>
+      </c>
+      <c r="B138" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C138">
+        <v>2562.5</v>
+      </c>
+      <c r="D138">
+        <v>171.73999999999981</v>
+      </c>
+      <c r="E138">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F138">
+        <v>54.88</v>
+      </c>
+      <c r="G138" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>10</v>
+      </c>
+      <c r="B139" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C139">
+        <v>2625</v>
+      </c>
+      <c r="D139">
+        <v>175.77999999999881</v>
+      </c>
+      <c r="E139">
+        <v>4.04</v>
+      </c>
+      <c r="F139">
+        <v>55.69</v>
+      </c>
+      <c r="G139" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>10</v>
+      </c>
+      <c r="B140" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C140">
+        <v>2687.5</v>
+      </c>
+      <c r="D140">
+        <v>179.8799999999992</v>
+      </c>
+      <c r="E140">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F140">
+        <v>54.88</v>
+      </c>
+      <c r="G140" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>10</v>
+      </c>
+      <c r="B141" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C141">
+        <v>2750</v>
+      </c>
+      <c r="D141">
+        <v>183.93999999999869</v>
+      </c>
+      <c r="E141">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="F141">
+        <v>55.42</v>
+      </c>
+      <c r="G141" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>10</v>
+      </c>
+      <c r="B142" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C142">
+        <v>2812.5</v>
+      </c>
+      <c r="D142">
+        <v>188.03999999999911</v>
+      </c>
+      <c r="E142">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F142">
+        <v>54.88</v>
+      </c>
+      <c r="G142" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>10</v>
+      </c>
+      <c r="B143" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C143">
+        <v>2875</v>
+      </c>
+      <c r="D143">
+        <v>192.09999999999849</v>
+      </c>
+      <c r="E143">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="F143">
+        <v>55.42</v>
+      </c>
+      <c r="G143" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>10</v>
+      </c>
+      <c r="B144" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C144">
+        <v>2937.5</v>
+      </c>
+      <c r="D144">
+        <v>196.21999999999929</v>
+      </c>
+      <c r="E144">
+        <v>4.12</v>
+      </c>
+      <c r="F144">
+        <v>54.61</v>
+      </c>
+      <c r="G144" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>10</v>
+      </c>
+      <c r="B145" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C145">
+        <v>3000</v>
+      </c>
+      <c r="D145">
+        <v>200.2999999999993</v>
+      </c>
+      <c r="E145">
+        <v>4.08</v>
+      </c>
+      <c r="F145">
+        <v>55.15</v>
+      </c>
+      <c r="G145" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/pages/video_analysis/IP_Master_Women.xlsx
+++ b/pages/video_analysis/IP_Master_Women.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8650F8-B4BA-4516-9B1F-DA0A5F7F6B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD238D62-7738-4A67-AEAD-72EACB3C1744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9504" yWindow="1128" windowWidth="9612" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$193</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="17">
   <si>
     <t>Title</t>
   </si>
@@ -55,6 +58,9 @@
     <t>3/8/2023 Bryony Botha IP Q Glasgow WCH</t>
   </si>
   <si>
+    <t>3/8/2023 Bryony Botha IP Bronze F Glasgow WCH</t>
+  </si>
+  <si>
     <t>No Change</t>
   </si>
   <si>
@@ -65,6 +71,9 @@
   </si>
   <si>
     <t>https://youtu.be/63pks-zGKqc</t>
+  </si>
+  <si>
+    <t>https://youtu.be/jN5BZ0WpgDc</t>
   </si>
 </sst>
 </file>
@@ -449,10 +458,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H193"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
@@ -460,6 +469,7 @@
     <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -490,134 +500,134 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C2">
         <v>62.5</v>
       </c>
       <c r="D2">
-        <v>9.2799999999999727</v>
+        <v>9.4599999999991269</v>
       </c>
       <c r="E2">
-        <v>9.2799999999999994</v>
+        <v>9.4600000000000009</v>
       </c>
       <c r="F2">
-        <v>24.25</v>
+        <v>23.78</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C3">
         <v>125</v>
       </c>
       <c r="D3">
-        <v>14.400000000000089</v>
+        <v>14.659999999999849</v>
       </c>
       <c r="E3">
-        <v>5.12</v>
+        <v>5.2</v>
       </c>
       <c r="F3">
-        <v>43.95</v>
+        <v>43.27</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C4">
         <v>187.5</v>
       </c>
       <c r="D4">
-        <v>18.860000000000131</v>
+        <v>19.239999999999782</v>
       </c>
       <c r="E4">
-        <v>4.46</v>
+        <v>4.58</v>
       </c>
       <c r="F4">
-        <v>50.45</v>
+        <v>49.13</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C5">
         <v>250</v>
       </c>
       <c r="D5">
-        <v>23.060000000000169</v>
+        <v>23.52000000000044</v>
       </c>
       <c r="E5">
-        <v>4.2</v>
+        <v>4.28</v>
       </c>
       <c r="F5">
-        <v>53.57</v>
+        <v>52.57</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C6">
         <v>312.5</v>
       </c>
       <c r="D6">
-        <v>27.160000000000078</v>
+        <v>27.639999999999421</v>
       </c>
       <c r="E6">
-        <v>4.0999999999999996</v>
+        <v>4.12</v>
       </c>
       <c r="F6">
-        <v>54.88</v>
+        <v>54.61</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C7">
         <v>375</v>
       </c>
       <c r="D7">
-        <v>31.279999999999969</v>
+        <v>31.760000000000218</v>
       </c>
       <c r="E7">
         <v>4.12</v>
@@ -626,182 +636,182 @@
         <v>54.61</v>
       </c>
       <c r="G7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C8">
         <v>437.5</v>
       </c>
       <c r="D8">
-        <v>35.340000000000153</v>
+        <v>35.859999999998763</v>
       </c>
       <c r="E8">
-        <v>4.0599999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F8">
-        <v>55.42</v>
+        <v>54.88</v>
       </c>
       <c r="G8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C9">
         <v>500</v>
       </c>
       <c r="D9">
-        <v>39.400000000000091</v>
+        <v>39.93999999999869</v>
       </c>
       <c r="E9">
-        <v>4.0599999999999996</v>
+        <v>4.08</v>
       </c>
       <c r="F9">
-        <v>55.42</v>
+        <v>55.15</v>
       </c>
       <c r="G9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C10">
         <v>562.5</v>
       </c>
       <c r="D10">
-        <v>43.5</v>
+        <v>44.020000000000437</v>
       </c>
       <c r="E10">
-        <v>4.0999999999999996</v>
+        <v>4.08</v>
       </c>
       <c r="F10">
-        <v>54.88</v>
+        <v>55.15</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C11">
         <v>625</v>
       </c>
       <c r="D11">
-        <v>47.6400000000001</v>
+        <v>48.119999999998981</v>
       </c>
       <c r="E11">
-        <v>4.1399999999999997</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F11">
-        <v>54.35</v>
+        <v>54.88</v>
       </c>
       <c r="G11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C12">
         <v>687.5</v>
       </c>
       <c r="D12">
-        <v>51.779999999999973</v>
+        <v>52.249309999999241</v>
       </c>
       <c r="E12">
-        <v>4.1399999999999997</v>
+        <v>4.1289999999999996</v>
       </c>
       <c r="F12">
-        <v>54.35</v>
+        <v>54.49</v>
       </c>
       <c r="G12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C13">
         <v>750</v>
       </c>
       <c r="D13">
-        <v>55.940000000000047</v>
+        <v>56.359999999998763</v>
       </c>
       <c r="E13">
-        <v>4.16</v>
+        <v>4.1109999999999998</v>
       </c>
       <c r="F13">
-        <v>54.09</v>
+        <v>54.73</v>
       </c>
       <c r="G13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C14">
         <v>812.5</v>
       </c>
       <c r="D14">
-        <v>60.080000000000148</v>
+        <v>60.520000000000437</v>
       </c>
       <c r="E14">
-        <v>4.1399999999999997</v>
+        <v>4.16</v>
       </c>
       <c r="F14">
-        <v>54.35</v>
+        <v>54.09</v>
       </c>
       <c r="G14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C15">
         <v>875</v>
       </c>
       <c r="D15">
-        <v>64.279999999999973</v>
+        <v>64.719999999999345</v>
       </c>
       <c r="E15">
         <v>4.2</v>
@@ -810,412 +820,412 @@
         <v>53.57</v>
       </c>
       <c r="G15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C16">
         <v>937.5</v>
       </c>
       <c r="D16">
-        <v>68.440000000000055</v>
+        <v>68.922959999999875</v>
       </c>
       <c r="E16">
-        <v>4.16</v>
+        <v>4.2030000000000003</v>
       </c>
       <c r="F16">
-        <v>54.09</v>
+        <v>53.53</v>
       </c>
       <c r="G16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C17">
         <v>1000</v>
       </c>
       <c r="D17">
-        <v>72.620000000000118</v>
+        <v>73.119999999998981</v>
       </c>
       <c r="E17">
-        <v>4.18</v>
+        <v>4.1970000000000001</v>
       </c>
       <c r="F17">
-        <v>53.83</v>
+        <v>53.61</v>
       </c>
       <c r="G17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C18">
         <v>1062.5</v>
       </c>
       <c r="D18">
-        <v>76.940000000000055</v>
+        <v>77.319999999999709</v>
       </c>
       <c r="E18">
-        <v>4.32</v>
+        <v>4.2</v>
       </c>
       <c r="F18">
-        <v>52.08</v>
+        <v>53.57</v>
       </c>
       <c r="G18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B19" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C19">
         <v>1125</v>
       </c>
       <c r="D19">
-        <v>80.940000000000055</v>
+        <v>81.520000000000437</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="F19">
-        <v>56.25</v>
+        <v>53.57</v>
       </c>
       <c r="G19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B20" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C20">
         <v>1187.5</v>
       </c>
       <c r="D20">
-        <v>85.080000000000155</v>
+        <v>85.739999999999782</v>
       </c>
       <c r="E20">
-        <v>4.1399999999999997</v>
+        <v>4.22</v>
       </c>
       <c r="F20">
-        <v>54.35</v>
+        <v>53.32</v>
       </c>
       <c r="G20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B21" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C21">
         <v>1250</v>
       </c>
       <c r="D21">
-        <v>89.220000000000027</v>
+        <v>89.959999999999127</v>
       </c>
       <c r="E21">
-        <v>4.1399999999999997</v>
+        <v>4.22</v>
       </c>
       <c r="F21">
-        <v>54.35</v>
+        <v>53.32</v>
       </c>
       <c r="G21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B22" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C22">
         <v>1312.5</v>
       </c>
       <c r="D22">
-        <v>93.380000000000109</v>
+        <v>94.180000000000291</v>
       </c>
       <c r="E22">
-        <v>4.16</v>
+        <v>4.22</v>
       </c>
       <c r="F22">
-        <v>54.09</v>
+        <v>53.32</v>
       </c>
       <c r="G22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B23" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C23">
         <v>1375</v>
       </c>
       <c r="D23">
-        <v>97.539999999999964</v>
+        <v>98.3799999999992</v>
       </c>
       <c r="E23">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="F23">
-        <v>54.09</v>
+        <v>53.57</v>
       </c>
       <c r="G23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B24" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C24">
         <v>1437.5</v>
       </c>
       <c r="D24">
-        <v>101.68000000000011</v>
+        <v>102.619999999999</v>
       </c>
       <c r="E24">
-        <v>4.1399999999999997</v>
+        <v>4.24</v>
       </c>
       <c r="F24">
-        <v>54.35</v>
+        <v>53.07</v>
       </c>
       <c r="G24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B25" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C25">
         <v>1500</v>
       </c>
       <c r="D25">
-        <v>105.78</v>
+        <v>106.85999999999881</v>
       </c>
       <c r="E25">
-        <v>4.0999999999999996</v>
+        <v>4.24</v>
       </c>
       <c r="F25">
-        <v>54.88</v>
+        <v>53.07</v>
       </c>
       <c r="G25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B26" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C26">
         <v>1562.5</v>
       </c>
       <c r="D26">
-        <v>109.9400000000001</v>
+        <v>111.0764999999992</v>
       </c>
       <c r="E26">
-        <v>4.16</v>
+        <v>4.2169999999999996</v>
       </c>
       <c r="F26">
-        <v>54.09</v>
+        <v>53.36</v>
       </c>
       <c r="G26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B27" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C27">
         <v>1625</v>
       </c>
       <c r="D27">
-        <v>114.10000000000009</v>
+        <v>115.2999999999993</v>
       </c>
       <c r="E27">
-        <v>4.16</v>
+        <v>4.2240000000000002</v>
       </c>
       <c r="F27">
-        <v>54.09</v>
+        <v>53.27</v>
       </c>
       <c r="G27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B28" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C28">
         <v>1687.5</v>
       </c>
       <c r="D28">
-        <v>118.26</v>
+        <v>119.52000000000039</v>
       </c>
       <c r="E28">
-        <v>4.16</v>
+        <v>4.22</v>
       </c>
       <c r="F28">
-        <v>54.09</v>
+        <v>53.32</v>
       </c>
       <c r="G28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B29" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C29">
         <v>1750</v>
       </c>
       <c r="D29">
-        <v>122.46</v>
+        <v>123.7600000000002</v>
       </c>
       <c r="E29">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="F29">
-        <v>53.57</v>
+        <v>53.07</v>
       </c>
       <c r="G29" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B30" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C30">
         <v>1812.5</v>
       </c>
       <c r="D30">
-        <v>126.6200000000001</v>
+        <v>127.97999999999961</v>
       </c>
       <c r="E30">
-        <v>4.16</v>
+        <v>4.22</v>
       </c>
       <c r="F30">
-        <v>54.09</v>
+        <v>53.32</v>
       </c>
       <c r="G30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B31" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C31">
         <v>1875</v>
       </c>
       <c r="D31">
-        <v>130.8600000000001</v>
+        <v>132.19999999999891</v>
       </c>
       <c r="E31">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="F31">
-        <v>53.07</v>
+        <v>53.32</v>
       </c>
       <c r="G31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B32" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C32">
         <v>1937.5</v>
       </c>
       <c r="D32">
-        <v>135.08000000000021</v>
+        <v>136.4599999999991</v>
       </c>
       <c r="E32">
-        <v>4.22</v>
+        <v>4.26</v>
       </c>
       <c r="F32">
-        <v>53.32</v>
+        <v>52.82</v>
       </c>
       <c r="G32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B33" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C33">
         <v>2000</v>
       </c>
       <c r="D33">
-        <v>139.30000000000001</v>
+        <v>140.68000000000029</v>
       </c>
       <c r="E33">
         <v>4.22</v>
@@ -1224,380 +1234,380 @@
         <v>53.32</v>
       </c>
       <c r="G33" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B34" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C34">
         <v>2062.5</v>
       </c>
       <c r="D34">
-        <v>143.60000000000011</v>
+        <v>144.9200000000001</v>
       </c>
       <c r="E34">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
       <c r="F34">
-        <v>52.33</v>
+        <v>53.07</v>
       </c>
       <c r="G34" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B35" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C35">
         <v>2125</v>
       </c>
       <c r="D35">
-        <v>147.94000000000011</v>
+        <v>149.13999999999939</v>
       </c>
       <c r="E35">
-        <v>4.34</v>
+        <v>4.22</v>
       </c>
       <c r="F35">
-        <v>51.84</v>
+        <v>53.32</v>
       </c>
       <c r="G35" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B36" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C36">
         <v>2187.5</v>
       </c>
       <c r="D36">
-        <v>152.26</v>
+        <v>153.35999999999879</v>
       </c>
       <c r="E36">
-        <v>4.32</v>
+        <v>4.22</v>
       </c>
       <c r="F36">
-        <v>52.08</v>
+        <v>53.32</v>
       </c>
       <c r="G36" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B37" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C37">
         <v>2250</v>
       </c>
       <c r="D37">
-        <v>156.5600000000002</v>
+        <v>157.55999999999949</v>
       </c>
       <c r="E37">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F37">
-        <v>52.33</v>
+        <v>53.57</v>
       </c>
       <c r="G37" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B38" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C38">
         <v>2312.5</v>
       </c>
       <c r="D38">
-        <v>160.88000000000011</v>
+        <v>161.77999999999881</v>
       </c>
       <c r="E38">
-        <v>4.32</v>
+        <v>4.22</v>
       </c>
       <c r="F38">
-        <v>52.08</v>
+        <v>53.32</v>
       </c>
       <c r="G38" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B39" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C39">
         <v>2375</v>
       </c>
       <c r="D39">
-        <v>165.24</v>
+        <v>165.97999999999959</v>
       </c>
       <c r="E39">
-        <v>4.3600000000000003</v>
+        <v>4.2</v>
       </c>
       <c r="F39">
-        <v>51.61</v>
+        <v>53.57</v>
       </c>
       <c r="G39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B40" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C40">
         <v>2437.5</v>
       </c>
       <c r="D40">
-        <v>169.54</v>
+        <v>170.13999999999939</v>
       </c>
       <c r="E40">
-        <v>4.3</v>
+        <v>4.16</v>
       </c>
       <c r="F40">
-        <v>52.33</v>
+        <v>54.09</v>
       </c>
       <c r="G40" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B41" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C41">
         <v>2500</v>
       </c>
       <c r="D41">
-        <v>173.88000000000011</v>
+        <v>174.27999999999881</v>
       </c>
       <c r="E41">
-        <v>4.34</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="F41">
-        <v>51.84</v>
+        <v>54.35</v>
       </c>
       <c r="G41" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B42" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C42">
         <v>2562.5</v>
       </c>
       <c r="D42">
-        <v>178.24</v>
+        <v>178.43999999999869</v>
       </c>
       <c r="E42">
-        <v>4.3600000000000003</v>
+        <v>4.16</v>
       </c>
       <c r="F42">
-        <v>51.61</v>
+        <v>54.09</v>
       </c>
       <c r="G42" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B43" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C43">
         <v>2625</v>
       </c>
       <c r="D43">
-        <v>182.60000000000011</v>
+        <v>182.60000000000039</v>
       </c>
       <c r="E43">
-        <v>4.3600000000000003</v>
+        <v>4.16</v>
       </c>
       <c r="F43">
-        <v>51.61</v>
+        <v>54.09</v>
       </c>
       <c r="G43" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B44" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C44">
         <v>2687.5</v>
       </c>
       <c r="D44">
-        <v>186.96</v>
+        <v>186.76000000000019</v>
       </c>
       <c r="E44">
-        <v>4.3600000000000003</v>
+        <v>4.16</v>
       </c>
       <c r="F44">
-        <v>51.61</v>
+        <v>54.09</v>
       </c>
       <c r="G44" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B45" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C45">
         <v>2750</v>
       </c>
       <c r="D45">
-        <v>191.3600000000001</v>
+        <v>190.9200000000001</v>
       </c>
       <c r="E45">
-        <v>4.4000000000000004</v>
+        <v>4.16</v>
       </c>
       <c r="F45">
-        <v>51.14</v>
+        <v>54.09</v>
       </c>
       <c r="G45" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B46" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C46">
         <v>2812.5</v>
       </c>
       <c r="D46">
-        <v>195.74</v>
+        <v>195.05999999999949</v>
       </c>
       <c r="E46">
-        <v>4.38</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="F46">
-        <v>51.37</v>
+        <v>54.35</v>
       </c>
       <c r="G46" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B47" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C47">
         <v>2875</v>
       </c>
       <c r="D47">
-        <v>200.12000000000009</v>
+        <v>199.21999999999929</v>
       </c>
       <c r="E47">
-        <v>4.38</v>
+        <v>4.16</v>
       </c>
       <c r="F47">
-        <v>51.37</v>
+        <v>54.09</v>
       </c>
       <c r="G47" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B48" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C48">
         <v>2937.5</v>
       </c>
       <c r="D48">
-        <v>204.5</v>
+        <v>203.35999999999879</v>
       </c>
       <c r="E48">
-        <v>4.38</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="F48">
-        <v>51.37</v>
+        <v>54.35</v>
       </c>
       <c r="G48" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B49" s="2">
-        <v>45133</v>
+        <v>45141</v>
       </c>
       <c r="C49">
         <v>3000</v>
       </c>
       <c r="D49">
-        <v>208.90000000000009</v>
+        <v>207.60000000000039</v>
       </c>
       <c r="E49">
-        <v>4.4000000000000004</v>
+        <v>4.24</v>
       </c>
       <c r="F49">
-        <v>51.14</v>
+        <v>53.07</v>
       </c>
       <c r="G49" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B50" s="2">
         <v>45141</v>
@@ -1606,24 +1616,24 @@
         <v>62.5</v>
       </c>
       <c r="D50">
-        <v>9.4599999999991269</v>
+        <v>9.5</v>
       </c>
       <c r="E50">
-        <v>9.4600000000000009</v>
+        <v>9.5</v>
       </c>
       <c r="F50">
-        <v>23.78</v>
+        <v>23.68</v>
       </c>
       <c r="G50" t="s">
-        <v>11</v>
-      </c>
-      <c r="H50" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B51" s="2">
         <v>45141</v>
@@ -1635,18 +1645,18 @@
         <v>14.659999999999849</v>
       </c>
       <c r="E51">
-        <v>5.2</v>
+        <v>5.16</v>
       </c>
       <c r="F51">
-        <v>43.27</v>
+        <v>43.6</v>
       </c>
       <c r="G51" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B52" s="2">
         <v>45141</v>
@@ -1655,21 +1665,21 @@
         <v>187.5</v>
       </c>
       <c r="D52">
-        <v>19.239999999999782</v>
+        <v>19.099999999998541</v>
       </c>
       <c r="E52">
-        <v>4.58</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="F52">
-        <v>49.13</v>
+        <v>50.68</v>
       </c>
       <c r="G52" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B53" s="2">
         <v>45141</v>
@@ -1678,21 +1688,21 @@
         <v>250</v>
       </c>
       <c r="D53">
-        <v>23.52000000000044</v>
+        <v>23.319999999999709</v>
       </c>
       <c r="E53">
-        <v>4.28</v>
+        <v>4.22</v>
       </c>
       <c r="F53">
-        <v>52.57</v>
+        <v>53.32</v>
       </c>
       <c r="G53" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B54" s="2">
         <v>45141</v>
@@ -1701,21 +1711,21 @@
         <v>312.5</v>
       </c>
       <c r="D54">
-        <v>27.639999999999421</v>
+        <v>27.3799999999992</v>
       </c>
       <c r="E54">
-        <v>4.12</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="F54">
-        <v>54.61</v>
+        <v>55.42</v>
       </c>
       <c r="G54" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B55" s="2">
         <v>45141</v>
@@ -1724,21 +1734,21 @@
         <v>375</v>
       </c>
       <c r="D55">
-        <v>31.760000000000218</v>
+        <v>31.39999999999964</v>
       </c>
       <c r="E55">
-        <v>4.12</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F55">
-        <v>54.61</v>
+        <v>55.97</v>
       </c>
       <c r="G55" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B56" s="2">
         <v>45141</v>
@@ -1747,21 +1757,21 @@
         <v>437.5</v>
       </c>
       <c r="D56">
-        <v>35.859999999998763</v>
+        <v>35.399999999999643</v>
       </c>
       <c r="E56">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="F56">
-        <v>54.88</v>
+        <v>56.25</v>
       </c>
       <c r="G56" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B57" s="2">
         <v>45141</v>
@@ -1770,21 +1780,21 @@
         <v>500</v>
       </c>
       <c r="D57">
-        <v>39.93999999999869</v>
+        <v>39.339999999998327</v>
       </c>
       <c r="E57">
-        <v>4.08</v>
+        <v>3.94</v>
       </c>
       <c r="F57">
-        <v>55.15</v>
+        <v>57.11</v>
       </c>
       <c r="G57" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B58" s="2">
         <v>45141</v>
@@ -1793,21 +1803,21 @@
         <v>562.5</v>
       </c>
       <c r="D58">
-        <v>44.020000000000437</v>
+        <v>43.299999999999272</v>
       </c>
       <c r="E58">
-        <v>4.08</v>
+        <v>3.96</v>
       </c>
       <c r="F58">
-        <v>55.15</v>
+        <v>56.82</v>
       </c>
       <c r="G58" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B59" s="2">
         <v>45141</v>
@@ -1816,21 +1826,21 @@
         <v>625</v>
       </c>
       <c r="D59">
-        <v>48.119999999998981</v>
+        <v>47.299999999999272</v>
       </c>
       <c r="E59">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="F59">
-        <v>54.88</v>
+        <v>56.25</v>
       </c>
       <c r="G59" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B60" s="2">
         <v>45141</v>
@@ -1839,21 +1849,21 @@
         <v>687.5</v>
       </c>
       <c r="D60">
-        <v>52.249309999999241</v>
+        <v>51.259999999998399</v>
       </c>
       <c r="E60">
-        <v>4.1289999999999996</v>
+        <v>3.96</v>
       </c>
       <c r="F60">
-        <v>54.49</v>
+        <v>56.82</v>
       </c>
       <c r="G60" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B61" s="2">
         <v>45141</v>
@@ -1862,21 +1872,21 @@
         <v>750</v>
       </c>
       <c r="D61">
-        <v>56.359999999998763</v>
+        <v>55.239999999999782</v>
       </c>
       <c r="E61">
-        <v>4.1109999999999998</v>
+        <v>3.98</v>
       </c>
       <c r="F61">
-        <v>54.73</v>
+        <v>56.53</v>
       </c>
       <c r="G61" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B62" s="2">
         <v>45141</v>
@@ -1885,21 +1895,21 @@
         <v>812.5</v>
       </c>
       <c r="D62">
-        <v>60.520000000000437</v>
+        <v>59.219999999999352</v>
       </c>
       <c r="E62">
-        <v>4.16</v>
+        <v>3.98</v>
       </c>
       <c r="F62">
-        <v>54.09</v>
+        <v>56.53</v>
       </c>
       <c r="G62" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B63" s="2">
         <v>45141</v>
@@ -1908,21 +1918,21 @@
         <v>875</v>
       </c>
       <c r="D63">
-        <v>64.719999999999345</v>
+        <v>63.239999999999782</v>
       </c>
       <c r="E63">
-        <v>4.2</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F63">
-        <v>53.57</v>
+        <v>55.97</v>
       </c>
       <c r="G63" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B64" s="2">
         <v>45141</v>
@@ -1931,21 +1941,21 @@
         <v>937.5</v>
       </c>
       <c r="D64">
-        <v>68.922959999999875</v>
+        <v>67.259999999998399</v>
       </c>
       <c r="E64">
-        <v>4.2030000000000003</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F64">
-        <v>53.53</v>
+        <v>55.97</v>
       </c>
       <c r="G64" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B65" s="2">
         <v>45141</v>
@@ -1954,21 +1964,21 @@
         <v>1000</v>
       </c>
       <c r="D65">
-        <v>73.119999999998981</v>
+        <v>71.279999999998836</v>
       </c>
       <c r="E65">
-        <v>4.1970000000000001</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F65">
-        <v>53.61</v>
+        <v>55.97</v>
       </c>
       <c r="G65" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B66" s="2">
         <v>45141</v>
@@ -1977,21 +1987,21 @@
         <v>1062.5</v>
       </c>
       <c r="D66">
-        <v>77.319999999999709</v>
+        <v>75.299999999999272</v>
       </c>
       <c r="E66">
-        <v>4.2</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F66">
-        <v>53.57</v>
+        <v>55.97</v>
       </c>
       <c r="G66" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B67" s="2">
         <v>45141</v>
@@ -2000,21 +2010,21 @@
         <v>1125</v>
       </c>
       <c r="D67">
-        <v>81.520000000000437</v>
+        <v>79.339999999998327</v>
       </c>
       <c r="E67">
-        <v>4.2</v>
+        <v>4.04</v>
       </c>
       <c r="F67">
-        <v>53.57</v>
+        <v>55.69</v>
       </c>
       <c r="G67" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B68" s="2">
         <v>45141</v>
@@ -2023,21 +2033,21 @@
         <v>1187.5</v>
       </c>
       <c r="D68">
-        <v>85.739999999999782</v>
+        <v>83.359999999998763</v>
       </c>
       <c r="E68">
-        <v>4.22</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F68">
-        <v>53.32</v>
+        <v>55.97</v>
       </c>
       <c r="G68" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B69" s="2">
         <v>45141</v>
@@ -2046,21 +2056,21 @@
         <v>1250</v>
       </c>
       <c r="D69">
-        <v>89.959999999999127</v>
+        <v>87.359999999998763</v>
       </c>
       <c r="E69">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="F69">
-        <v>53.32</v>
+        <v>56.25</v>
       </c>
       <c r="G69" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B70" s="2">
         <v>45141</v>
@@ -2069,21 +2079,21 @@
         <v>1312.5</v>
       </c>
       <c r="D70">
-        <v>94.180000000000291</v>
+        <v>91.3799999999992</v>
       </c>
       <c r="E70">
-        <v>4.22</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F70">
-        <v>53.32</v>
+        <v>55.97</v>
       </c>
       <c r="G70" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B71" s="2">
         <v>45141</v>
@@ -2092,21 +2102,21 @@
         <v>1375</v>
       </c>
       <c r="D71">
-        <v>98.3799999999992</v>
+        <v>95.3799999999992</v>
       </c>
       <c r="E71">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="F71">
-        <v>53.57</v>
+        <v>56.25</v>
       </c>
       <c r="G71" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B72" s="2">
         <v>45141</v>
@@ -2115,21 +2125,21 @@
         <v>1437.5</v>
       </c>
       <c r="D72">
-        <v>102.619999999999</v>
+        <v>99.399999999999636</v>
       </c>
       <c r="E72">
-        <v>4.24</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F72">
-        <v>53.07</v>
+        <v>55.97</v>
       </c>
       <c r="G72" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B73" s="2">
         <v>45141</v>
@@ -2138,21 +2148,21 @@
         <v>1500</v>
       </c>
       <c r="D73">
-        <v>106.85999999999881</v>
+        <v>103.4200000000001</v>
       </c>
       <c r="E73">
-        <v>4.24</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F73">
-        <v>53.07</v>
+        <v>55.97</v>
       </c>
       <c r="G73" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B74" s="2">
         <v>45141</v>
@@ -2161,21 +2171,21 @@
         <v>1562.5</v>
       </c>
       <c r="D74">
-        <v>111.0764999999992</v>
+        <v>107.4399999999987</v>
       </c>
       <c r="E74">
-        <v>4.2169999999999996</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F74">
-        <v>53.36</v>
+        <v>55.97</v>
       </c>
       <c r="G74" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B75" s="2">
         <v>45141</v>
@@ -2184,21 +2194,21 @@
         <v>1625</v>
       </c>
       <c r="D75">
-        <v>115.2999999999993</v>
+        <v>111.4399999999987</v>
       </c>
       <c r="E75">
-        <v>4.2240000000000002</v>
+        <v>4</v>
       </c>
       <c r="F75">
-        <v>53.27</v>
+        <v>56.25</v>
       </c>
       <c r="G75" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B76" s="2">
         <v>45141</v>
@@ -2207,21 +2217,21 @@
         <v>1687.5</v>
       </c>
       <c r="D76">
-        <v>119.52000000000039</v>
+        <v>115.4599999999991</v>
       </c>
       <c r="E76">
-        <v>4.22</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F76">
-        <v>53.32</v>
+        <v>55.97</v>
       </c>
       <c r="G76" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B77" s="2">
         <v>45141</v>
@@ -2230,21 +2240,21 @@
         <v>1750</v>
       </c>
       <c r="D77">
-        <v>123.7600000000002</v>
+        <v>119.47999999999961</v>
       </c>
       <c r="E77">
-        <v>4.24</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F77">
-        <v>53.07</v>
+        <v>55.97</v>
       </c>
       <c r="G77" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B78" s="2">
         <v>45141</v>
@@ -2253,21 +2263,21 @@
         <v>1812.5</v>
       </c>
       <c r="D78">
-        <v>127.97999999999961</v>
+        <v>123.47999999999961</v>
       </c>
       <c r="E78">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="F78">
-        <v>53.32</v>
+        <v>56.25</v>
       </c>
       <c r="G78" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B79" s="2">
         <v>45141</v>
@@ -2276,21 +2286,21 @@
         <v>1875</v>
       </c>
       <c r="D79">
-        <v>132.19999999999891</v>
+        <v>127.47999999999961</v>
       </c>
       <c r="E79">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="F79">
-        <v>53.32</v>
+        <v>56.25</v>
       </c>
       <c r="G79" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B80" s="2">
         <v>45141</v>
@@ -2299,21 +2309,21 @@
         <v>1937.5</v>
       </c>
       <c r="D80">
-        <v>136.4599999999991</v>
+        <v>131.47999999999959</v>
       </c>
       <c r="E80">
-        <v>4.26</v>
+        <v>4</v>
       </c>
       <c r="F80">
-        <v>52.82</v>
+        <v>56.25</v>
       </c>
       <c r="G80" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B81" s="2">
         <v>45141</v>
@@ -2322,21 +2332,21 @@
         <v>2000</v>
       </c>
       <c r="D81">
-        <v>140.68000000000029</v>
+        <v>135.4599999999991</v>
       </c>
       <c r="E81">
-        <v>4.22</v>
+        <v>3.98</v>
       </c>
       <c r="F81">
-        <v>53.32</v>
+        <v>56.53</v>
       </c>
       <c r="G81" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B82" s="2">
         <v>45141</v>
@@ -2345,21 +2355,21 @@
         <v>2062.5</v>
       </c>
       <c r="D82">
-        <v>144.9200000000001</v>
+        <v>139.47999999999959</v>
       </c>
       <c r="E82">
-        <v>4.24</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F82">
-        <v>53.07</v>
+        <v>55.97</v>
       </c>
       <c r="G82" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B83" s="2">
         <v>45141</v>
@@ -2368,21 +2378,21 @@
         <v>2125</v>
       </c>
       <c r="D83">
-        <v>149.13999999999939</v>
+        <v>143.47999999999959</v>
       </c>
       <c r="E83">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="F83">
-        <v>53.32</v>
+        <v>56.25</v>
       </c>
       <c r="G83" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B84" s="2">
         <v>45141</v>
@@ -2391,21 +2401,21 @@
         <v>2187.5</v>
       </c>
       <c r="D84">
-        <v>153.35999999999879</v>
+        <v>147.5</v>
       </c>
       <c r="E84">
-        <v>4.22</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F84">
-        <v>53.32</v>
+        <v>55.97</v>
       </c>
       <c r="G84" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B85" s="2">
         <v>45141</v>
@@ -2414,21 +2424,21 @@
         <v>2250</v>
       </c>
       <c r="D85">
-        <v>157.55999999999949</v>
+        <v>151.5</v>
       </c>
       <c r="E85">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="F85">
-        <v>53.57</v>
+        <v>56.25</v>
       </c>
       <c r="G85" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B86" s="2">
         <v>45141</v>
@@ -2437,21 +2447,21 @@
         <v>2312.5</v>
       </c>
       <c r="D86">
-        <v>161.77999999999881</v>
+        <v>155.51999999999859</v>
       </c>
       <c r="E86">
-        <v>4.22</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F86">
-        <v>53.32</v>
+        <v>55.97</v>
       </c>
       <c r="G86" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B87" s="2">
         <v>45141</v>
@@ -2460,21 +2470,21 @@
         <v>2375</v>
       </c>
       <c r="D87">
-        <v>165.97999999999959</v>
+        <v>159.53999999999911</v>
       </c>
       <c r="E87">
-        <v>4.2</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F87">
-        <v>53.57</v>
+        <v>55.97</v>
       </c>
       <c r="G87" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B88" s="2">
         <v>45141</v>
@@ -2483,21 +2493,21 @@
         <v>2437.5</v>
       </c>
       <c r="D88">
-        <v>170.13999999999939</v>
+        <v>163.5799999999999</v>
       </c>
       <c r="E88">
-        <v>4.16</v>
+        <v>4.04</v>
       </c>
       <c r="F88">
-        <v>54.09</v>
+        <v>55.69</v>
       </c>
       <c r="G88" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B89" s="2">
         <v>45141</v>
@@ -2506,21 +2516,21 @@
         <v>2500</v>
       </c>
       <c r="D89">
-        <v>174.27999999999881</v>
+        <v>167.63999999999939</v>
       </c>
       <c r="E89">
-        <v>4.1399999999999997</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="F89">
-        <v>54.35</v>
+        <v>55.42</v>
       </c>
       <c r="G89" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B90" s="2">
         <v>45141</v>
@@ -2529,21 +2539,21 @@
         <v>2562.5</v>
       </c>
       <c r="D90">
-        <v>178.43999999999869</v>
+        <v>171.73999999999981</v>
       </c>
       <c r="E90">
-        <v>4.16</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F90">
-        <v>54.09</v>
+        <v>54.88</v>
       </c>
       <c r="G90" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B91" s="2">
         <v>45141</v>
@@ -2552,21 +2562,21 @@
         <v>2625</v>
       </c>
       <c r="D91">
-        <v>182.60000000000039</v>
+        <v>175.77999999999881</v>
       </c>
       <c r="E91">
-        <v>4.16</v>
+        <v>4.04</v>
       </c>
       <c r="F91">
-        <v>54.09</v>
+        <v>55.69</v>
       </c>
       <c r="G91" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B92" s="2">
         <v>45141</v>
@@ -2575,21 +2585,21 @@
         <v>2687.5</v>
       </c>
       <c r="D92">
-        <v>186.76000000000019</v>
+        <v>179.8799999999992</v>
       </c>
       <c r="E92">
-        <v>4.16</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F92">
-        <v>54.09</v>
+        <v>54.88</v>
       </c>
       <c r="G92" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B93" s="2">
         <v>45141</v>
@@ -2598,21 +2608,21 @@
         <v>2750</v>
       </c>
       <c r="D93">
-        <v>190.9200000000001</v>
+        <v>183.93999999999869</v>
       </c>
       <c r="E93">
-        <v>4.16</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="F93">
-        <v>54.09</v>
+        <v>55.42</v>
       </c>
       <c r="G93" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B94" s="2">
         <v>45141</v>
@@ -2621,21 +2631,21 @@
         <v>2812.5</v>
       </c>
       <c r="D94">
-        <v>195.05999999999949</v>
+        <v>188.03999999999911</v>
       </c>
       <c r="E94">
-        <v>4.1399999999999997</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F94">
-        <v>54.35</v>
+        <v>54.88</v>
       </c>
       <c r="G94" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B95" s="2">
         <v>45141</v>
@@ -2644,21 +2654,21 @@
         <v>2875</v>
       </c>
       <c r="D95">
-        <v>199.21999999999929</v>
+        <v>192.09999999999849</v>
       </c>
       <c r="E95">
-        <v>4.16</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="F95">
-        <v>54.09</v>
+        <v>55.42</v>
       </c>
       <c r="G95" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B96" s="2">
         <v>45141</v>
@@ -2667,21 +2677,21 @@
         <v>2937.5</v>
       </c>
       <c r="D96">
-        <v>203.35999999999879</v>
+        <v>196.21999999999929</v>
       </c>
       <c r="E96">
-        <v>4.1399999999999997</v>
+        <v>4.12</v>
       </c>
       <c r="F96">
-        <v>54.35</v>
+        <v>54.61</v>
       </c>
       <c r="G96" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B97" s="2">
         <v>45141</v>
@@ -2690,21 +2700,21 @@
         <v>3000</v>
       </c>
       <c r="D97">
-        <v>207.60000000000039</v>
+        <v>200.2999999999993</v>
       </c>
       <c r="E97">
-        <v>4.24</v>
+        <v>4.08</v>
       </c>
       <c r="F97">
-        <v>53.07</v>
+        <v>55.15</v>
       </c>
       <c r="G97" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B98" s="2">
         <v>45141</v>
@@ -2713,24 +2723,24 @@
         <v>62.5</v>
       </c>
       <c r="D98">
-        <v>9.5</v>
+        <v>9.3400000000001455</v>
       </c>
       <c r="E98">
-        <v>9.5</v>
+        <v>9.34</v>
       </c>
       <c r="F98">
-        <v>23.68</v>
+        <v>24.09</v>
       </c>
       <c r="G98" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H98" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B99" s="2">
         <v>45141</v>
@@ -2739,21 +2749,21 @@
         <v>125</v>
       </c>
       <c r="D99">
-        <v>14.659999999999849</v>
+        <v>14.44000000000233</v>
       </c>
       <c r="E99">
-        <v>5.16</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="F99">
-        <v>43.6</v>
+        <v>44.12</v>
       </c>
       <c r="G99" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B100" s="2">
         <v>45141</v>
@@ -2762,21 +2772,21 @@
         <v>187.5</v>
       </c>
       <c r="D100">
-        <v>19.099999999998541</v>
+        <v>18.840000000000149</v>
       </c>
       <c r="E100">
-        <v>4.4400000000000004</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F100">
-        <v>50.68</v>
+        <v>51.14</v>
       </c>
       <c r="G100" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B101" s="2">
         <v>45141</v>
@@ -2785,21 +2795,21 @@
         <v>250</v>
       </c>
       <c r="D101">
-        <v>23.319999999999709</v>
+        <v>23.04000000000087</v>
       </c>
       <c r="E101">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="F101">
-        <v>53.32</v>
+        <v>53.57</v>
       </c>
       <c r="G101" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B102" s="2">
         <v>45141</v>
@@ -2808,21 +2818,21 @@
         <v>312.5</v>
       </c>
       <c r="D102">
-        <v>27.3799999999992</v>
+        <v>27.08000000000175</v>
       </c>
       <c r="E102">
-        <v>4.0599999999999996</v>
+        <v>4.04</v>
       </c>
       <c r="F102">
-        <v>55.42</v>
+        <v>55.69</v>
       </c>
       <c r="G102" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B103" s="2">
         <v>45141</v>
@@ -2831,21 +2841,21 @@
         <v>375</v>
       </c>
       <c r="D103">
-        <v>31.39999999999964</v>
+        <v>31.06000000000131</v>
       </c>
       <c r="E103">
-        <v>4.0199999999999996</v>
+        <v>3.98</v>
       </c>
       <c r="F103">
-        <v>55.97</v>
+        <v>56.53</v>
       </c>
       <c r="G103" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B104" s="2">
         <v>45141</v>
@@ -2854,21 +2864,21 @@
         <v>437.5</v>
       </c>
       <c r="D104">
-        <v>35.399999999999643</v>
+        <v>35</v>
       </c>
       <c r="E104">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="F104">
-        <v>56.25</v>
+        <v>57.11</v>
       </c>
       <c r="G104" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B105" s="2">
         <v>45141</v>
@@ -2877,7 +2887,7 @@
         <v>500</v>
       </c>
       <c r="D105">
-        <v>39.339999999998327</v>
+        <v>38.940000000002328</v>
       </c>
       <c r="E105">
         <v>3.94</v>
@@ -2886,12 +2896,12 @@
         <v>57.11</v>
       </c>
       <c r="G105" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B106" s="2">
         <v>45141</v>
@@ -2900,21 +2910,21 @@
         <v>562.5</v>
       </c>
       <c r="D106">
-        <v>43.299999999999272</v>
+        <v>42.880000000001019</v>
       </c>
       <c r="E106">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="F106">
-        <v>56.82</v>
+        <v>57.11</v>
       </c>
       <c r="G106" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B107" s="2">
         <v>45141</v>
@@ -2923,21 +2933,21 @@
         <v>625</v>
       </c>
       <c r="D107">
-        <v>47.299999999999272</v>
+        <v>46.840000000000153</v>
       </c>
       <c r="E107">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="F107">
-        <v>56.25</v>
+        <v>56.82</v>
       </c>
       <c r="G107" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B108" s="2">
         <v>45141</v>
@@ -2946,7 +2956,7 @@
         <v>687.5</v>
       </c>
       <c r="D108">
-        <v>51.259999999998399</v>
+        <v>50.80000000000291</v>
       </c>
       <c r="E108">
         <v>3.96</v>
@@ -2955,12 +2965,12 @@
         <v>56.82</v>
       </c>
       <c r="G108" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B109" s="2">
         <v>45141</v>
@@ -2969,21 +2979,21 @@
         <v>750</v>
       </c>
       <c r="D109">
-        <v>55.239999999999782</v>
+        <v>54.80000000000291</v>
       </c>
       <c r="E109">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="F109">
-        <v>56.53</v>
+        <v>56.25</v>
       </c>
       <c r="G109" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B110" s="2">
         <v>45141</v>
@@ -2992,21 +3002,21 @@
         <v>812.5</v>
       </c>
       <c r="D110">
-        <v>59.219999999999352</v>
+        <v>58.819999999999709</v>
       </c>
       <c r="E110">
-        <v>3.98</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F110">
-        <v>56.53</v>
+        <v>55.97</v>
       </c>
       <c r="G110" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B111" s="2">
         <v>45141</v>
@@ -3015,7 +3025,7 @@
         <v>875</v>
       </c>
       <c r="D111">
-        <v>63.239999999999782</v>
+        <v>62.840000000000153</v>
       </c>
       <c r="E111">
         <v>4.0199999999999996</v>
@@ -3024,12 +3034,12 @@
         <v>55.97</v>
       </c>
       <c r="G111" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B112" s="2">
         <v>45141</v>
@@ -3038,7 +3048,7 @@
         <v>937.5</v>
       </c>
       <c r="D112">
-        <v>67.259999999998399</v>
+        <v>66.860000000000582</v>
       </c>
       <c r="E112">
         <v>4.0199999999999996</v>
@@ -3047,12 +3057,12 @@
         <v>55.97</v>
       </c>
       <c r="G112" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B113" s="2">
         <v>45141</v>
@@ -3061,21 +3071,21 @@
         <v>1000</v>
       </c>
       <c r="D113">
-        <v>71.279999999998836</v>
+        <v>70.900000000001455</v>
       </c>
       <c r="E113">
-        <v>4.0199999999999996</v>
+        <v>4.04</v>
       </c>
       <c r="F113">
-        <v>55.97</v>
+        <v>55.69</v>
       </c>
       <c r="G113" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B114" s="2">
         <v>45141</v>
@@ -3084,21 +3094,21 @@
         <v>1062.5</v>
       </c>
       <c r="D114">
-        <v>75.299999999999272</v>
+        <v>74.940000000002328</v>
       </c>
       <c r="E114">
-        <v>4.0199999999999996</v>
+        <v>4.04</v>
       </c>
       <c r="F114">
-        <v>55.97</v>
+        <v>55.69</v>
       </c>
       <c r="G114" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B115" s="2">
         <v>45141</v>
@@ -3107,7 +3117,7 @@
         <v>1125</v>
       </c>
       <c r="D115">
-        <v>79.339999999998327</v>
+        <v>78.979999999999563</v>
       </c>
       <c r="E115">
         <v>4.04</v>
@@ -3116,12 +3126,12 @@
         <v>55.69</v>
       </c>
       <c r="G115" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B116" s="2">
         <v>45141</v>
@@ -3130,21 +3140,21 @@
         <v>1187.5</v>
       </c>
       <c r="D116">
-        <v>83.359999999998763</v>
+        <v>83.020000000000437</v>
       </c>
       <c r="E116">
-        <v>4.0199999999999996</v>
+        <v>4.04</v>
       </c>
       <c r="F116">
-        <v>55.97</v>
+        <v>55.69</v>
       </c>
       <c r="G116" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B117" s="2">
         <v>45141</v>
@@ -3153,21 +3163,21 @@
         <v>1250</v>
       </c>
       <c r="D117">
-        <v>87.359999999998763</v>
+        <v>87.06000000000131</v>
       </c>
       <c r="E117">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="F117">
-        <v>56.25</v>
+        <v>55.69</v>
       </c>
       <c r="G117" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B118" s="2">
         <v>45141</v>
@@ -3176,21 +3186,21 @@
         <v>1312.5</v>
       </c>
       <c r="D118">
-        <v>91.3799999999992</v>
+        <v>91.100000000002183</v>
       </c>
       <c r="E118">
-        <v>4.0199999999999996</v>
+        <v>4.04</v>
       </c>
       <c r="F118">
-        <v>55.97</v>
+        <v>55.69</v>
       </c>
       <c r="G118" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B119" s="2">
         <v>45141</v>
@@ -3199,21 +3209,21 @@
         <v>1375</v>
       </c>
       <c r="D119">
-        <v>95.3799999999992</v>
+        <v>95.120000000002619</v>
       </c>
       <c r="E119">
-        <v>4</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F119">
-        <v>56.25</v>
+        <v>55.97</v>
       </c>
       <c r="G119" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B120" s="2">
         <v>45141</v>
@@ -3222,21 +3232,21 @@
         <v>1437.5</v>
       </c>
       <c r="D120">
-        <v>99.399999999999636</v>
+        <v>99.159999999999854</v>
       </c>
       <c r="E120">
-        <v>4.0199999999999996</v>
+        <v>4.04</v>
       </c>
       <c r="F120">
-        <v>55.97</v>
+        <v>55.69</v>
       </c>
       <c r="G120" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B121" s="2">
         <v>45141</v>
@@ -3245,7 +3255,7 @@
         <v>1500</v>
       </c>
       <c r="D121">
-        <v>103.4200000000001</v>
+        <v>103.18000000000031</v>
       </c>
       <c r="E121">
         <v>4.0199999999999996</v>
@@ -3254,12 +3264,12 @@
         <v>55.97</v>
       </c>
       <c r="G121" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B122" s="2">
         <v>45141</v>
@@ -3268,7 +3278,7 @@
         <v>1562.5</v>
       </c>
       <c r="D122">
-        <v>107.4399999999987</v>
+        <v>107.2000000000007</v>
       </c>
       <c r="E122">
         <v>4.0199999999999996</v>
@@ -3277,12 +3287,12 @@
         <v>55.97</v>
       </c>
       <c r="G122" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B123" s="2">
         <v>45141</v>
@@ -3291,21 +3301,21 @@
         <v>1625</v>
       </c>
       <c r="D123">
-        <v>111.4399999999987</v>
+        <v>111.2400000000016</v>
       </c>
       <c r="E123">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="F123">
-        <v>56.25</v>
+        <v>55.69</v>
       </c>
       <c r="G123" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B124" s="2">
         <v>45141</v>
@@ -3314,21 +3324,21 @@
         <v>1687.5</v>
       </c>
       <c r="D124">
-        <v>115.4599999999991</v>
+        <v>115.3000000000029</v>
       </c>
       <c r="E124">
-        <v>4.0199999999999996</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="F124">
-        <v>55.97</v>
+        <v>55.42</v>
       </c>
       <c r="G124" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B125" s="2">
         <v>45141</v>
@@ -3337,21 +3347,21 @@
         <v>1750</v>
       </c>
       <c r="D125">
-        <v>119.47999999999961</v>
+        <v>119.3600000000006</v>
       </c>
       <c r="E125">
-        <v>4.0199999999999996</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="F125">
-        <v>55.97</v>
+        <v>55.42</v>
       </c>
       <c r="G125" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B126" s="2">
         <v>45141</v>
@@ -3360,21 +3370,21 @@
         <v>1812.5</v>
       </c>
       <c r="D126">
-        <v>123.47999999999961</v>
+        <v>123.46000000000279</v>
       </c>
       <c r="E126">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F126">
-        <v>56.25</v>
+        <v>54.88</v>
       </c>
       <c r="G126" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B127" s="2">
         <v>45141</v>
@@ -3383,21 +3393,21 @@
         <v>1875</v>
       </c>
       <c r="D127">
-        <v>127.47999999999961</v>
+        <v>127.52000000000039</v>
       </c>
       <c r="E127">
-        <v>4</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="F127">
-        <v>56.25</v>
+        <v>55.42</v>
       </c>
       <c r="G127" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B128" s="2">
         <v>45141</v>
@@ -3406,21 +3416,21 @@
         <v>1937.5</v>
       </c>
       <c r="D128">
-        <v>131.47999999999959</v>
+        <v>131.58000000000169</v>
       </c>
       <c r="E128">
-        <v>4</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="F128">
-        <v>56.25</v>
+        <v>55.42</v>
       </c>
       <c r="G128" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B129" s="2">
         <v>45141</v>
@@ -3429,21 +3439,21 @@
         <v>2000</v>
       </c>
       <c r="D129">
-        <v>135.4599999999991</v>
+        <v>135.63999999999939</v>
       </c>
       <c r="E129">
-        <v>3.98</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="F129">
-        <v>56.53</v>
+        <v>55.42</v>
       </c>
       <c r="G129" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B130" s="2">
         <v>45141</v>
@@ -3452,21 +3462,21 @@
         <v>2062.5</v>
       </c>
       <c r="D130">
-        <v>139.47999999999959</v>
+        <v>139.72000000000119</v>
       </c>
       <c r="E130">
-        <v>4.0199999999999996</v>
+        <v>4.08</v>
       </c>
       <c r="F130">
-        <v>55.97</v>
+        <v>55.15</v>
       </c>
       <c r="G130" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B131" s="2">
         <v>45141</v>
@@ -3475,21 +3485,21 @@
         <v>2125</v>
       </c>
       <c r="D131">
-        <v>143.47999999999959</v>
+        <v>143.80000000000291</v>
       </c>
       <c r="E131">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="F131">
-        <v>56.25</v>
+        <v>55.15</v>
       </c>
       <c r="G131" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B132" s="2">
         <v>45141</v>
@@ -3498,21 +3508,21 @@
         <v>2187.5</v>
       </c>
       <c r="D132">
-        <v>147.5</v>
+        <v>147.88000000000099</v>
       </c>
       <c r="E132">
-        <v>4.0199999999999996</v>
+        <v>4.08</v>
       </c>
       <c r="F132">
-        <v>55.97</v>
+        <v>55.15</v>
       </c>
       <c r="G132" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B133" s="2">
         <v>45141</v>
@@ -3521,21 +3531,21 @@
         <v>2250</v>
       </c>
       <c r="D133">
-        <v>151.5</v>
+        <v>151.96000000000279</v>
       </c>
       <c r="E133">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="F133">
-        <v>56.25</v>
+        <v>55.15</v>
       </c>
       <c r="G133" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B134" s="2">
         <v>45141</v>
@@ -3544,21 +3554,21 @@
         <v>2312.5</v>
       </c>
       <c r="D134">
-        <v>155.51999999999859</v>
+        <v>156.08000000000169</v>
       </c>
       <c r="E134">
-        <v>4.0199999999999996</v>
+        <v>4.12</v>
       </c>
       <c r="F134">
-        <v>55.97</v>
+        <v>54.61</v>
       </c>
       <c r="G134" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B135" s="2">
         <v>45141</v>
@@ -3567,21 +3577,21 @@
         <v>2375</v>
       </c>
       <c r="D135">
-        <v>159.53999999999911</v>
+        <v>160.2000000000007</v>
       </c>
       <c r="E135">
-        <v>4.0199999999999996</v>
+        <v>4.12</v>
       </c>
       <c r="F135">
-        <v>55.97</v>
+        <v>54.61</v>
       </c>
       <c r="G135" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B136" s="2">
         <v>45141</v>
@@ -3590,21 +3600,21 @@
         <v>2437.5</v>
       </c>
       <c r="D136">
-        <v>163.5799999999999</v>
+        <v>164.34000000000009</v>
       </c>
       <c r="E136">
-        <v>4.04</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="F136">
-        <v>55.69</v>
+        <v>54.35</v>
       </c>
       <c r="G136" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B137" s="2">
         <v>45141</v>
@@ -3613,21 +3623,21 @@
         <v>2500</v>
       </c>
       <c r="D137">
-        <v>167.63999999999939</v>
+        <v>168.46000000000279</v>
       </c>
       <c r="E137">
-        <v>4.0599999999999996</v>
+        <v>4.12</v>
       </c>
       <c r="F137">
-        <v>55.42</v>
+        <v>54.61</v>
       </c>
       <c r="G137" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B138" s="2">
         <v>45141</v>
@@ -3636,21 +3646,21 @@
         <v>2562.5</v>
       </c>
       <c r="D138">
-        <v>171.73999999999981</v>
+        <v>172.62000000000259</v>
       </c>
       <c r="E138">
-        <v>4.0999999999999996</v>
+        <v>4.16</v>
       </c>
       <c r="F138">
-        <v>54.88</v>
+        <v>54.09</v>
       </c>
       <c r="G138" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B139" s="2">
         <v>45141</v>
@@ -3659,21 +3669,21 @@
         <v>2625</v>
       </c>
       <c r="D139">
-        <v>175.77999999999881</v>
+        <v>176.7800000000025</v>
       </c>
       <c r="E139">
-        <v>4.04</v>
+        <v>4.16</v>
       </c>
       <c r="F139">
-        <v>55.69</v>
+        <v>54.09</v>
       </c>
       <c r="G139" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B140" s="2">
         <v>45141</v>
@@ -3682,21 +3692,21 @@
         <v>2687.5</v>
       </c>
       <c r="D140">
-        <v>179.8799999999992</v>
+        <v>180.97999999999959</v>
       </c>
       <c r="E140">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="F140">
-        <v>54.88</v>
+        <v>53.57</v>
       </c>
       <c r="G140" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B141" s="2">
         <v>45141</v>
@@ -3705,21 +3715,21 @@
         <v>2750</v>
       </c>
       <c r="D141">
-        <v>183.93999999999869</v>
+        <v>185.18000000000029</v>
       </c>
       <c r="E141">
-        <v>4.0599999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="F141">
-        <v>55.42</v>
+        <v>53.57</v>
       </c>
       <c r="G141" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B142" s="2">
         <v>45141</v>
@@ -3728,21 +3738,21 @@
         <v>2812.5</v>
       </c>
       <c r="D142">
-        <v>188.03999999999911</v>
+        <v>189.4400000000023</v>
       </c>
       <c r="E142">
-        <v>4.0999999999999996</v>
+        <v>4.26</v>
       </c>
       <c r="F142">
-        <v>54.88</v>
+        <v>52.82</v>
       </c>
       <c r="G142" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B143" s="2">
         <v>45141</v>
@@ -3751,21 +3761,21 @@
         <v>2875</v>
       </c>
       <c r="D143">
-        <v>192.09999999999849</v>
+        <v>193.65999999999991</v>
       </c>
       <c r="E143">
-        <v>4.0599999999999996</v>
+        <v>4.22</v>
       </c>
       <c r="F143">
-        <v>55.42</v>
+        <v>53.32</v>
       </c>
       <c r="G143" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B144" s="2">
         <v>45141</v>
@@ -3774,21 +3784,21 @@
         <v>2937.5</v>
       </c>
       <c r="D144">
-        <v>196.21999999999929</v>
+        <v>197.90000000000151</v>
       </c>
       <c r="E144">
-        <v>4.12</v>
+        <v>4.24</v>
       </c>
       <c r="F144">
-        <v>54.61</v>
+        <v>53.07</v>
       </c>
       <c r="G144" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
-        <v>10</v>
       </c>
       <c r="B145" s="2">
         <v>45141</v>
@@ -3797,21 +3807,1135 @@
         <v>3000</v>
       </c>
       <c r="D145">
-        <v>200.2999999999993</v>
+        <v>202.18000000000029</v>
       </c>
       <c r="E145">
-        <v>4.08</v>
+        <v>4.28</v>
       </c>
       <c r="F145">
-        <v>55.15</v>
+        <v>52.57</v>
       </c>
       <c r="G145" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>8</v>
+      </c>
+      <c r="B146" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C146">
+        <v>62.5</v>
+      </c>
+      <c r="D146">
+        <v>9.2799999999999727</v>
+      </c>
+      <c r="E146">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="F146">
+        <v>24.25</v>
+      </c>
+      <c r="G146" t="s">
+        <v>12</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>8</v>
+      </c>
+      <c r="B147" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C147">
+        <v>125</v>
+      </c>
+      <c r="D147">
+        <v>14.400000000000089</v>
+      </c>
+      <c r="E147">
+        <v>5.12</v>
+      </c>
+      <c r="F147">
+        <v>43.95</v>
+      </c>
+      <c r="G147" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>8</v>
+      </c>
+      <c r="B148" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C148">
+        <v>187.5</v>
+      </c>
+      <c r="D148">
+        <v>18.860000000000131</v>
+      </c>
+      <c r="E148">
+        <v>4.46</v>
+      </c>
+      <c r="F148">
+        <v>50.45</v>
+      </c>
+      <c r="G148" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>8</v>
+      </c>
+      <c r="B149" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C149">
+        <v>250</v>
+      </c>
+      <c r="D149">
+        <v>23.060000000000169</v>
+      </c>
+      <c r="E149">
+        <v>4.2</v>
+      </c>
+      <c r="F149">
+        <v>53.57</v>
+      </c>
+      <c r="G149" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>8</v>
+      </c>
+      <c r="B150" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C150">
+        <v>312.5</v>
+      </c>
+      <c r="D150">
+        <v>27.160000000000078</v>
+      </c>
+      <c r="E150">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F150">
+        <v>54.88</v>
+      </c>
+      <c r="G150" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>8</v>
+      </c>
+      <c r="B151" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C151">
+        <v>375</v>
+      </c>
+      <c r="D151">
+        <v>31.279999999999969</v>
+      </c>
+      <c r="E151">
+        <v>4.12</v>
+      </c>
+      <c r="F151">
+        <v>54.61</v>
+      </c>
+      <c r="G151" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>8</v>
+      </c>
+      <c r="B152" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C152">
+        <v>437.5</v>
+      </c>
+      <c r="D152">
+        <v>35.340000000000153</v>
+      </c>
+      <c r="E152">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="F152">
+        <v>55.42</v>
+      </c>
+      <c r="G152" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>8</v>
+      </c>
+      <c r="B153" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C153">
+        <v>500</v>
+      </c>
+      <c r="D153">
+        <v>39.400000000000091</v>
+      </c>
+      <c r="E153">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="F153">
+        <v>55.42</v>
+      </c>
+      <c r="G153" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>8</v>
+      </c>
+      <c r="B154" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C154">
+        <v>562.5</v>
+      </c>
+      <c r="D154">
+        <v>43.5</v>
+      </c>
+      <c r="E154">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F154">
+        <v>54.88</v>
+      </c>
+      <c r="G154" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>8</v>
+      </c>
+      <c r="B155" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C155">
+        <v>625</v>
+      </c>
+      <c r="D155">
+        <v>47.6400000000001</v>
+      </c>
+      <c r="E155">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="F155">
+        <v>54.35</v>
+      </c>
+      <c r="G155" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>8</v>
+      </c>
+      <c r="B156" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C156">
+        <v>687.5</v>
+      </c>
+      <c r="D156">
+        <v>51.779999999999973</v>
+      </c>
+      <c r="E156">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="F156">
+        <v>54.35</v>
+      </c>
+      <c r="G156" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>8</v>
+      </c>
+      <c r="B157" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C157">
+        <v>750</v>
+      </c>
+      <c r="D157">
+        <v>55.940000000000047</v>
+      </c>
+      <c r="E157">
+        <v>4.16</v>
+      </c>
+      <c r="F157">
+        <v>54.09</v>
+      </c>
+      <c r="G157" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>8</v>
+      </c>
+      <c r="B158" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C158">
+        <v>812.5</v>
+      </c>
+      <c r="D158">
+        <v>60.080000000000148</v>
+      </c>
+      <c r="E158">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="F158">
+        <v>54.35</v>
+      </c>
+      <c r="G158" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>8</v>
+      </c>
+      <c r="B159" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C159">
+        <v>875</v>
+      </c>
+      <c r="D159">
+        <v>64.279999999999973</v>
+      </c>
+      <c r="E159">
+        <v>4.2</v>
+      </c>
+      <c r="F159">
+        <v>53.57</v>
+      </c>
+      <c r="G159" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>8</v>
+      </c>
+      <c r="B160" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C160">
+        <v>937.5</v>
+      </c>
+      <c r="D160">
+        <v>68.440000000000055</v>
+      </c>
+      <c r="E160">
+        <v>4.16</v>
+      </c>
+      <c r="F160">
+        <v>54.09</v>
+      </c>
+      <c r="G160" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>8</v>
+      </c>
+      <c r="B161" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C161">
+        <v>1000</v>
+      </c>
+      <c r="D161">
+        <v>72.620000000000118</v>
+      </c>
+      <c r="E161">
+        <v>4.18</v>
+      </c>
+      <c r="F161">
+        <v>53.83</v>
+      </c>
+      <c r="G161" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>8</v>
+      </c>
+      <c r="B162" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C162">
+        <v>1062.5</v>
+      </c>
+      <c r="D162">
+        <v>76.940000000000055</v>
+      </c>
+      <c r="E162">
+        <v>4.32</v>
+      </c>
+      <c r="F162">
+        <v>52.08</v>
+      </c>
+      <c r="G162" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>8</v>
+      </c>
+      <c r="B163" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C163">
+        <v>1125</v>
+      </c>
+      <c r="D163">
+        <v>80.940000000000055</v>
+      </c>
+      <c r="E163">
+        <v>4</v>
+      </c>
+      <c r="F163">
+        <v>56.25</v>
+      </c>
+      <c r="G163" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>8</v>
+      </c>
+      <c r="B164" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C164">
+        <v>1187.5</v>
+      </c>
+      <c r="D164">
+        <v>85.080000000000155</v>
+      </c>
+      <c r="E164">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="F164">
+        <v>54.35</v>
+      </c>
+      <c r="G164" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>8</v>
+      </c>
+      <c r="B165" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C165">
+        <v>1250</v>
+      </c>
+      <c r="D165">
+        <v>89.220000000000027</v>
+      </c>
+      <c r="E165">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="F165">
+        <v>54.35</v>
+      </c>
+      <c r="G165" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>8</v>
+      </c>
+      <c r="B166" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C166">
+        <v>1312.5</v>
+      </c>
+      <c r="D166">
+        <v>93.380000000000109</v>
+      </c>
+      <c r="E166">
+        <v>4.16</v>
+      </c>
+      <c r="F166">
+        <v>54.09</v>
+      </c>
+      <c r="G166" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>8</v>
+      </c>
+      <c r="B167" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C167">
+        <v>1375</v>
+      </c>
+      <c r="D167">
+        <v>97.539999999999964</v>
+      </c>
+      <c r="E167">
+        <v>4.16</v>
+      </c>
+      <c r="F167">
+        <v>54.09</v>
+      </c>
+      <c r="G167" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>8</v>
+      </c>
+      <c r="B168" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C168">
+        <v>1437.5</v>
+      </c>
+      <c r="D168">
+        <v>101.68000000000011</v>
+      </c>
+      <c r="E168">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="F168">
+        <v>54.35</v>
+      </c>
+      <c r="G168" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>8</v>
+      </c>
+      <c r="B169" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C169">
+        <v>1500</v>
+      </c>
+      <c r="D169">
+        <v>105.78</v>
+      </c>
+      <c r="E169">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F169">
+        <v>54.88</v>
+      </c>
+      <c r="G169" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>8</v>
+      </c>
+      <c r="B170" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C170">
+        <v>1562.5</v>
+      </c>
+      <c r="D170">
+        <v>109.9400000000001</v>
+      </c>
+      <c r="E170">
+        <v>4.16</v>
+      </c>
+      <c r="F170">
+        <v>54.09</v>
+      </c>
+      <c r="G170" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>8</v>
+      </c>
+      <c r="B171" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C171">
+        <v>1625</v>
+      </c>
+      <c r="D171">
+        <v>114.10000000000009</v>
+      </c>
+      <c r="E171">
+        <v>4.16</v>
+      </c>
+      <c r="F171">
+        <v>54.09</v>
+      </c>
+      <c r="G171" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>8</v>
+      </c>
+      <c r="B172" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C172">
+        <v>1687.5</v>
+      </c>
+      <c r="D172">
+        <v>118.26</v>
+      </c>
+      <c r="E172">
+        <v>4.16</v>
+      </c>
+      <c r="F172">
+        <v>54.09</v>
+      </c>
+      <c r="G172" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>8</v>
+      </c>
+      <c r="B173" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C173">
+        <v>1750</v>
+      </c>
+      <c r="D173">
+        <v>122.46</v>
+      </c>
+      <c r="E173">
+        <v>4.2</v>
+      </c>
+      <c r="F173">
+        <v>53.57</v>
+      </c>
+      <c r="G173" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>8</v>
+      </c>
+      <c r="B174" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C174">
+        <v>1812.5</v>
+      </c>
+      <c r="D174">
+        <v>126.6200000000001</v>
+      </c>
+      <c r="E174">
+        <v>4.16</v>
+      </c>
+      <c r="F174">
+        <v>54.09</v>
+      </c>
+      <c r="G174" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>8</v>
+      </c>
+      <c r="B175" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C175">
+        <v>1875</v>
+      </c>
+      <c r="D175">
+        <v>130.8600000000001</v>
+      </c>
+      <c r="E175">
+        <v>4.24</v>
+      </c>
+      <c r="F175">
+        <v>53.07</v>
+      </c>
+      <c r="G175" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>8</v>
+      </c>
+      <c r="B176" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C176">
+        <v>1937.5</v>
+      </c>
+      <c r="D176">
+        <v>135.08000000000021</v>
+      </c>
+      <c r="E176">
+        <v>4.22</v>
+      </c>
+      <c r="F176">
+        <v>53.32</v>
+      </c>
+      <c r="G176" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>8</v>
+      </c>
+      <c r="B177" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C177">
+        <v>2000</v>
+      </c>
+      <c r="D177">
+        <v>139.30000000000001</v>
+      </c>
+      <c r="E177">
+        <v>4.22</v>
+      </c>
+      <c r="F177">
+        <v>53.32</v>
+      </c>
+      <c r="G177" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>8</v>
+      </c>
+      <c r="B178" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C178">
+        <v>2062.5</v>
+      </c>
+      <c r="D178">
+        <v>143.60000000000011</v>
+      </c>
+      <c r="E178">
+        <v>4.3</v>
+      </c>
+      <c r="F178">
+        <v>52.33</v>
+      </c>
+      <c r="G178" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>8</v>
+      </c>
+      <c r="B179" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C179">
+        <v>2125</v>
+      </c>
+      <c r="D179">
+        <v>147.94000000000011</v>
+      </c>
+      <c r="E179">
+        <v>4.34</v>
+      </c>
+      <c r="F179">
+        <v>51.84</v>
+      </c>
+      <c r="G179" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>8</v>
+      </c>
+      <c r="B180" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C180">
+        <v>2187.5</v>
+      </c>
+      <c r="D180">
+        <v>152.26</v>
+      </c>
+      <c r="E180">
+        <v>4.32</v>
+      </c>
+      <c r="F180">
+        <v>52.08</v>
+      </c>
+      <c r="G180" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>8</v>
+      </c>
+      <c r="B181" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C181">
+        <v>2250</v>
+      </c>
+      <c r="D181">
+        <v>156.5600000000002</v>
+      </c>
+      <c r="E181">
+        <v>4.3</v>
+      </c>
+      <c r="F181">
+        <v>52.33</v>
+      </c>
+      <c r="G181" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>8</v>
+      </c>
+      <c r="B182" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C182">
+        <v>2312.5</v>
+      </c>
+      <c r="D182">
+        <v>160.88000000000011</v>
+      </c>
+      <c r="E182">
+        <v>4.32</v>
+      </c>
+      <c r="F182">
+        <v>52.08</v>
+      </c>
+      <c r="G182" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>8</v>
+      </c>
+      <c r="B183" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C183">
+        <v>2375</v>
+      </c>
+      <c r="D183">
+        <v>165.24</v>
+      </c>
+      <c r="E183">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="F183">
+        <v>51.61</v>
+      </c>
+      <c r="G183" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>8</v>
+      </c>
+      <c r="B184" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C184">
+        <v>2437.5</v>
+      </c>
+      <c r="D184">
+        <v>169.54</v>
+      </c>
+      <c r="E184">
+        <v>4.3</v>
+      </c>
+      <c r="F184">
+        <v>52.33</v>
+      </c>
+      <c r="G184" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>8</v>
+      </c>
+      <c r="B185" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C185">
+        <v>2500</v>
+      </c>
+      <c r="D185">
+        <v>173.88000000000011</v>
+      </c>
+      <c r="E185">
+        <v>4.34</v>
+      </c>
+      <c r="F185">
+        <v>51.84</v>
+      </c>
+      <c r="G185" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>8</v>
+      </c>
+      <c r="B186" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C186">
+        <v>2562.5</v>
+      </c>
+      <c r="D186">
+        <v>178.24</v>
+      </c>
+      <c r="E186">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="F186">
+        <v>51.61</v>
+      </c>
+      <c r="G186" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>8</v>
+      </c>
+      <c r="B187" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C187">
+        <v>2625</v>
+      </c>
+      <c r="D187">
+        <v>182.60000000000011</v>
+      </c>
+      <c r="E187">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="F187">
+        <v>51.61</v>
+      </c>
+      <c r="G187" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>8</v>
+      </c>
+      <c r="B188" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C188">
+        <v>2687.5</v>
+      </c>
+      <c r="D188">
+        <v>186.96</v>
+      </c>
+      <c r="E188">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="F188">
+        <v>51.61</v>
+      </c>
+      <c r="G188" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>8</v>
+      </c>
+      <c r="B189" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C189">
+        <v>2750</v>
+      </c>
+      <c r="D189">
+        <v>191.3600000000001</v>
+      </c>
+      <c r="E189">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F189">
+        <v>51.14</v>
+      </c>
+      <c r="G189" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>8</v>
+      </c>
+      <c r="B190" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C190">
+        <v>2812.5</v>
+      </c>
+      <c r="D190">
+        <v>195.74</v>
+      </c>
+      <c r="E190">
+        <v>4.38</v>
+      </c>
+      <c r="F190">
+        <v>51.37</v>
+      </c>
+      <c r="G190" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>8</v>
+      </c>
+      <c r="B191" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C191">
+        <v>2875</v>
+      </c>
+      <c r="D191">
+        <v>200.12000000000009</v>
+      </c>
+      <c r="E191">
+        <v>4.38</v>
+      </c>
+      <c r="F191">
+        <v>51.37</v>
+      </c>
+      <c r="G191" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>8</v>
+      </c>
+      <c r="B192" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C192">
+        <v>2937.5</v>
+      </c>
+      <c r="D192">
+        <v>204.5</v>
+      </c>
+      <c r="E192">
+        <v>4.38</v>
+      </c>
+      <c r="F192">
+        <v>51.37</v>
+      </c>
+      <c r="G192" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>8</v>
+      </c>
+      <c r="B193" s="2">
+        <v>45133</v>
+      </c>
+      <c r="C193">
+        <v>3000</v>
+      </c>
+      <c r="D193">
+        <v>208.90000000000009</v>
+      </c>
+      <c r="E193">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F193">
+        <v>51.14</v>
+      </c>
+      <c r="G193" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H193" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H193">
+      <sortCondition descending="1" ref="B1:B193"/>
+    </sortState>
+  </autoFilter>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="H146" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="H2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="H50" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pages/video_analysis/IP_Master_Women.xlsx
+++ b/pages/video_analysis/IP_Master_Women.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD238D62-7738-4A67-AEAD-72EACB3C1744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE18465E-053E-4316-A4EA-E7776AC006F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -49,18 +49,6 @@
     <t>Video</t>
   </si>
   <si>
-    <t>26/7/2023 Sami Donnelly Race Sim</t>
-  </si>
-  <si>
-    <t>3/8/2023 Sami Donnelly IP Q Glasgow WCH</t>
-  </si>
-  <si>
-    <t>3/8/2023 Bryony Botha IP Q Glasgow WCH</t>
-  </si>
-  <si>
-    <t>3/8/2023 Bryony Botha IP Bronze F Glasgow WCH</t>
-  </si>
-  <si>
     <t>No Change</t>
   </si>
   <si>
@@ -74,6 +62,18 @@
   </si>
   <si>
     <t>https://youtu.be/jN5BZ0WpgDc</t>
+  </si>
+  <si>
+    <t>23-08-03 Sami Donnelly IP Q Glasgow WCH</t>
+  </si>
+  <si>
+    <t>23-08-03 Bryony Botha IP Q Glasgow WCH</t>
+  </si>
+  <si>
+    <t>23-08-03 Bryony Botha IP Bronze F Glasgow WCH</t>
+  </si>
+  <si>
+    <t>23-07-26 Sami Donnelly Race Sim</t>
   </si>
 </sst>
 </file>
@@ -459,20 +459,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H193"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="42.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.86328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -498,9 +498,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2">
         <v>45141</v>
@@ -518,15 +518,15 @@
         <v>23.78</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2">
         <v>45141</v>
@@ -544,12 +544,12 @@
         <v>43.27</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2">
         <v>45141</v>
@@ -567,12 +567,12 @@
         <v>49.13</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2">
         <v>45141</v>
@@ -590,12 +590,12 @@
         <v>52.57</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2">
         <v>45141</v>
@@ -613,12 +613,12 @@
         <v>54.61</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B7" s="2">
         <v>45141</v>
@@ -636,12 +636,12 @@
         <v>54.61</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2">
         <v>45141</v>
@@ -659,12 +659,12 @@
         <v>54.88</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B9" s="2">
         <v>45141</v>
@@ -682,12 +682,12 @@
         <v>55.15</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B10" s="2">
         <v>45141</v>
@@ -705,12 +705,12 @@
         <v>55.15</v>
       </c>
       <c r="G10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B11" s="2">
         <v>45141</v>
@@ -728,12 +728,12 @@
         <v>54.88</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B12" s="2">
         <v>45141</v>
@@ -751,12 +751,12 @@
         <v>54.49</v>
       </c>
       <c r="G12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2">
         <v>45141</v>
@@ -774,12 +774,12 @@
         <v>54.73</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2">
         <v>45141</v>
@@ -797,12 +797,12 @@
         <v>54.09</v>
       </c>
       <c r="G14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2">
         <v>45141</v>
@@ -820,12 +820,12 @@
         <v>53.57</v>
       </c>
       <c r="G15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B16" s="2">
         <v>45141</v>
@@ -843,12 +843,12 @@
         <v>53.53</v>
       </c>
       <c r="G16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B17" s="2">
         <v>45141</v>
@@ -866,12 +866,12 @@
         <v>53.61</v>
       </c>
       <c r="G17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2">
         <v>45141</v>
@@ -889,12 +889,12 @@
         <v>53.57</v>
       </c>
       <c r="G18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B19" s="2">
         <v>45141</v>
@@ -912,12 +912,12 @@
         <v>53.57</v>
       </c>
       <c r="G19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B20" s="2">
         <v>45141</v>
@@ -935,12 +935,12 @@
         <v>53.32</v>
       </c>
       <c r="G20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B21" s="2">
         <v>45141</v>
@@ -958,12 +958,12 @@
         <v>53.32</v>
       </c>
       <c r="G21" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B22" s="2">
         <v>45141</v>
@@ -981,12 +981,12 @@
         <v>53.32</v>
       </c>
       <c r="G22" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B23" s="2">
         <v>45141</v>
@@ -1004,12 +1004,12 @@
         <v>53.57</v>
       </c>
       <c r="G23" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B24" s="2">
         <v>45141</v>
@@ -1027,12 +1027,12 @@
         <v>53.07</v>
       </c>
       <c r="G24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B25" s="2">
         <v>45141</v>
@@ -1050,12 +1050,12 @@
         <v>53.07</v>
       </c>
       <c r="G25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B26" s="2">
         <v>45141</v>
@@ -1073,12 +1073,12 @@
         <v>53.36</v>
       </c>
       <c r="G26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B27" s="2">
         <v>45141</v>
@@ -1096,12 +1096,12 @@
         <v>53.27</v>
       </c>
       <c r="G27" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B28" s="2">
         <v>45141</v>
@@ -1119,12 +1119,12 @@
         <v>53.32</v>
       </c>
       <c r="G28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B29" s="2">
         <v>45141</v>
@@ -1142,12 +1142,12 @@
         <v>53.07</v>
       </c>
       <c r="G29" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B30" s="2">
         <v>45141</v>
@@ -1165,12 +1165,12 @@
         <v>53.32</v>
       </c>
       <c r="G30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B31" s="2">
         <v>45141</v>
@@ -1188,12 +1188,12 @@
         <v>53.32</v>
       </c>
       <c r="G31" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B32" s="2">
         <v>45141</v>
@@ -1211,12 +1211,12 @@
         <v>52.82</v>
       </c>
       <c r="G32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B33" s="2">
         <v>45141</v>
@@ -1234,12 +1234,12 @@
         <v>53.32</v>
       </c>
       <c r="G33" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B34" s="2">
         <v>45141</v>
@@ -1257,12 +1257,12 @@
         <v>53.07</v>
       </c>
       <c r="G34" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B35" s="2">
         <v>45141</v>
@@ -1280,12 +1280,12 @@
         <v>53.32</v>
       </c>
       <c r="G35" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B36" s="2">
         <v>45141</v>
@@ -1303,12 +1303,12 @@
         <v>53.32</v>
       </c>
       <c r="G36" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B37" s="2">
         <v>45141</v>
@@ -1326,12 +1326,12 @@
         <v>53.57</v>
       </c>
       <c r="G37" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B38" s="2">
         <v>45141</v>
@@ -1349,12 +1349,12 @@
         <v>53.32</v>
       </c>
       <c r="G38" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B39" s="2">
         <v>45141</v>
@@ -1372,12 +1372,12 @@
         <v>53.57</v>
       </c>
       <c r="G39" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B40" s="2">
         <v>45141</v>
@@ -1395,12 +1395,12 @@
         <v>54.09</v>
       </c>
       <c r="G40" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B41" s="2">
         <v>45141</v>
@@ -1418,12 +1418,12 @@
         <v>54.35</v>
       </c>
       <c r="G41" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B42" s="2">
         <v>45141</v>
@@ -1441,12 +1441,12 @@
         <v>54.09</v>
       </c>
       <c r="G42" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B43" s="2">
         <v>45141</v>
@@ -1464,12 +1464,12 @@
         <v>54.09</v>
       </c>
       <c r="G43" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B44" s="2">
         <v>45141</v>
@@ -1487,12 +1487,12 @@
         <v>54.09</v>
       </c>
       <c r="G44" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B45" s="2">
         <v>45141</v>
@@ -1510,12 +1510,12 @@
         <v>54.09</v>
       </c>
       <c r="G45" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B46" s="2">
         <v>45141</v>
@@ -1533,12 +1533,12 @@
         <v>54.35</v>
       </c>
       <c r="G46" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B47" s="2">
         <v>45141</v>
@@ -1556,12 +1556,12 @@
         <v>54.09</v>
       </c>
       <c r="G47" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B48" s="2">
         <v>45141</v>
@@ -1579,12 +1579,12 @@
         <v>54.35</v>
       </c>
       <c r="G48" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B49" s="2">
         <v>45141</v>
@@ -1602,12 +1602,12 @@
         <v>53.07</v>
       </c>
       <c r="G49" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B50" s="2">
         <v>45141</v>
@@ -1625,15 +1625,15 @@
         <v>23.68</v>
       </c>
       <c r="G50" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B51" s="2">
         <v>45141</v>
@@ -1651,12 +1651,12 @@
         <v>43.6</v>
       </c>
       <c r="G51" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B52" s="2">
         <v>45141</v>
@@ -1674,12 +1674,12 @@
         <v>50.68</v>
       </c>
       <c r="G52" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B53" s="2">
         <v>45141</v>
@@ -1697,12 +1697,12 @@
         <v>53.32</v>
       </c>
       <c r="G53" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B54" s="2">
         <v>45141</v>
@@ -1720,12 +1720,12 @@
         <v>55.42</v>
       </c>
       <c r="G54" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B55" s="2">
         <v>45141</v>
@@ -1743,12 +1743,12 @@
         <v>55.97</v>
       </c>
       <c r="G55" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B56" s="2">
         <v>45141</v>
@@ -1766,12 +1766,12 @@
         <v>56.25</v>
       </c>
       <c r="G56" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B57" s="2">
         <v>45141</v>
@@ -1789,12 +1789,12 @@
         <v>57.11</v>
       </c>
       <c r="G57" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B58" s="2">
         <v>45141</v>
@@ -1812,12 +1812,12 @@
         <v>56.82</v>
       </c>
       <c r="G58" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B59" s="2">
         <v>45141</v>
@@ -1835,12 +1835,12 @@
         <v>56.25</v>
       </c>
       <c r="G59" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B60" s="2">
         <v>45141</v>
@@ -1858,12 +1858,12 @@
         <v>56.82</v>
       </c>
       <c r="G60" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B61" s="2">
         <v>45141</v>
@@ -1881,12 +1881,12 @@
         <v>56.53</v>
       </c>
       <c r="G61" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B62" s="2">
         <v>45141</v>
@@ -1904,12 +1904,12 @@
         <v>56.53</v>
       </c>
       <c r="G62" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B63" s="2">
         <v>45141</v>
@@ -1927,12 +1927,12 @@
         <v>55.97</v>
       </c>
       <c r="G63" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B64" s="2">
         <v>45141</v>
@@ -1950,12 +1950,12 @@
         <v>55.97</v>
       </c>
       <c r="G64" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B65" s="2">
         <v>45141</v>
@@ -1973,12 +1973,12 @@
         <v>55.97</v>
       </c>
       <c r="G65" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B66" s="2">
         <v>45141</v>
@@ -1996,12 +1996,12 @@
         <v>55.97</v>
       </c>
       <c r="G66" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B67" s="2">
         <v>45141</v>
@@ -2019,12 +2019,12 @@
         <v>55.69</v>
       </c>
       <c r="G67" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B68" s="2">
         <v>45141</v>
@@ -2042,12 +2042,12 @@
         <v>55.97</v>
       </c>
       <c r="G68" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B69" s="2">
         <v>45141</v>
@@ -2065,12 +2065,12 @@
         <v>56.25</v>
       </c>
       <c r="G69" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B70" s="2">
         <v>45141</v>
@@ -2088,12 +2088,12 @@
         <v>55.97</v>
       </c>
       <c r="G70" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B71" s="2">
         <v>45141</v>
@@ -2111,12 +2111,12 @@
         <v>56.25</v>
       </c>
       <c r="G71" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B72" s="2">
         <v>45141</v>
@@ -2134,12 +2134,12 @@
         <v>55.97</v>
       </c>
       <c r="G72" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B73" s="2">
         <v>45141</v>
@@ -2157,12 +2157,12 @@
         <v>55.97</v>
       </c>
       <c r="G73" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B74" s="2">
         <v>45141</v>
@@ -2180,12 +2180,12 @@
         <v>55.97</v>
       </c>
       <c r="G74" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B75" s="2">
         <v>45141</v>
@@ -2203,12 +2203,12 @@
         <v>56.25</v>
       </c>
       <c r="G75" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B76" s="2">
         <v>45141</v>
@@ -2226,12 +2226,12 @@
         <v>55.97</v>
       </c>
       <c r="G76" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B77" s="2">
         <v>45141</v>
@@ -2249,12 +2249,12 @@
         <v>55.97</v>
       </c>
       <c r="G77" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B78" s="2">
         <v>45141</v>
@@ -2272,12 +2272,12 @@
         <v>56.25</v>
       </c>
       <c r="G78" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B79" s="2">
         <v>45141</v>
@@ -2295,12 +2295,12 @@
         <v>56.25</v>
       </c>
       <c r="G79" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B80" s="2">
         <v>45141</v>
@@ -2318,12 +2318,12 @@
         <v>56.25</v>
       </c>
       <c r="G80" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B81" s="2">
         <v>45141</v>
@@ -2341,12 +2341,12 @@
         <v>56.53</v>
       </c>
       <c r="G81" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B82" s="2">
         <v>45141</v>
@@ -2364,12 +2364,12 @@
         <v>55.97</v>
       </c>
       <c r="G82" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B83" s="2">
         <v>45141</v>
@@ -2387,12 +2387,12 @@
         <v>56.25</v>
       </c>
       <c r="G83" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B84" s="2">
         <v>45141</v>
@@ -2410,12 +2410,12 @@
         <v>55.97</v>
       </c>
       <c r="G84" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B85" s="2">
         <v>45141</v>
@@ -2433,12 +2433,12 @@
         <v>56.25</v>
       </c>
       <c r="G85" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B86" s="2">
         <v>45141</v>
@@ -2456,12 +2456,12 @@
         <v>55.97</v>
       </c>
       <c r="G86" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B87" s="2">
         <v>45141</v>
@@ -2479,12 +2479,12 @@
         <v>55.97</v>
       </c>
       <c r="G87" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B88" s="2">
         <v>45141</v>
@@ -2502,12 +2502,12 @@
         <v>55.69</v>
       </c>
       <c r="G88" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B89" s="2">
         <v>45141</v>
@@ -2525,12 +2525,12 @@
         <v>55.42</v>
       </c>
       <c r="G89" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B90" s="2">
         <v>45141</v>
@@ -2548,12 +2548,12 @@
         <v>54.88</v>
       </c>
       <c r="G90" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B91" s="2">
         <v>45141</v>
@@ -2571,12 +2571,12 @@
         <v>55.69</v>
       </c>
       <c r="G91" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B92" s="2">
         <v>45141</v>
@@ -2594,12 +2594,12 @@
         <v>54.88</v>
       </c>
       <c r="G92" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B93" s="2">
         <v>45141</v>
@@ -2617,12 +2617,12 @@
         <v>55.42</v>
       </c>
       <c r="G93" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B94" s="2">
         <v>45141</v>
@@ -2640,12 +2640,12 @@
         <v>54.88</v>
       </c>
       <c r="G94" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B95" s="2">
         <v>45141</v>
@@ -2663,12 +2663,12 @@
         <v>55.42</v>
       </c>
       <c r="G95" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B96" s="2">
         <v>45141</v>
@@ -2686,12 +2686,12 @@
         <v>54.61</v>
       </c>
       <c r="G96" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B97" s="2">
         <v>45141</v>
@@ -2709,12 +2709,12 @@
         <v>55.15</v>
       </c>
       <c r="G97" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B98" s="2">
         <v>45141</v>
@@ -2732,15 +2732,15 @@
         <v>24.09</v>
       </c>
       <c r="G98" t="s">
+        <v>8</v>
+      </c>
+      <c r="H98" t="s">
         <v>12</v>
       </c>
-      <c r="H98" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B99" s="2">
         <v>45141</v>
@@ -2758,12 +2758,12 @@
         <v>44.12</v>
       </c>
       <c r="G99" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B100" s="2">
         <v>45141</v>
@@ -2781,12 +2781,12 @@
         <v>51.14</v>
       </c>
       <c r="G100" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B101" s="2">
         <v>45141</v>
@@ -2804,12 +2804,12 @@
         <v>53.57</v>
       </c>
       <c r="G101" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B102" s="2">
         <v>45141</v>
@@ -2827,12 +2827,12 @@
         <v>55.69</v>
       </c>
       <c r="G102" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B103" s="2">
         <v>45141</v>
@@ -2850,12 +2850,12 @@
         <v>56.53</v>
       </c>
       <c r="G103" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B104" s="2">
         <v>45141</v>
@@ -2873,12 +2873,12 @@
         <v>57.11</v>
       </c>
       <c r="G104" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B105" s="2">
         <v>45141</v>
@@ -2896,12 +2896,12 @@
         <v>57.11</v>
       </c>
       <c r="G105" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B106" s="2">
         <v>45141</v>
@@ -2919,12 +2919,12 @@
         <v>57.11</v>
       </c>
       <c r="G106" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B107" s="2">
         <v>45141</v>
@@ -2942,12 +2942,12 @@
         <v>56.82</v>
       </c>
       <c r="G107" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B108" s="2">
         <v>45141</v>
@@ -2965,12 +2965,12 @@
         <v>56.82</v>
       </c>
       <c r="G108" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B109" s="2">
         <v>45141</v>
@@ -2988,12 +2988,12 @@
         <v>56.25</v>
       </c>
       <c r="G109" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B110" s="2">
         <v>45141</v>
@@ -3011,12 +3011,12 @@
         <v>55.97</v>
       </c>
       <c r="G110" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B111" s="2">
         <v>45141</v>
@@ -3034,12 +3034,12 @@
         <v>55.97</v>
       </c>
       <c r="G111" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B112" s="2">
         <v>45141</v>
@@ -3057,12 +3057,12 @@
         <v>55.97</v>
       </c>
       <c r="G112" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B113" s="2">
         <v>45141</v>
@@ -3080,12 +3080,12 @@
         <v>55.69</v>
       </c>
       <c r="G113" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B114" s="2">
         <v>45141</v>
@@ -3103,12 +3103,12 @@
         <v>55.69</v>
       </c>
       <c r="G114" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B115" s="2">
         <v>45141</v>
@@ -3126,12 +3126,12 @@
         <v>55.69</v>
       </c>
       <c r="G115" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B116" s="2">
         <v>45141</v>
@@ -3149,12 +3149,12 @@
         <v>55.69</v>
       </c>
       <c r="G116" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B117" s="2">
         <v>45141</v>
@@ -3172,12 +3172,12 @@
         <v>55.69</v>
       </c>
       <c r="G117" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B118" s="2">
         <v>45141</v>
@@ -3195,12 +3195,12 @@
         <v>55.69</v>
       </c>
       <c r="G118" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B119" s="2">
         <v>45141</v>
@@ -3218,12 +3218,12 @@
         <v>55.97</v>
       </c>
       <c r="G119" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B120" s="2">
         <v>45141</v>
@@ -3241,12 +3241,12 @@
         <v>55.69</v>
       </c>
       <c r="G120" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B121" s="2">
         <v>45141</v>
@@ -3264,12 +3264,12 @@
         <v>55.97</v>
       </c>
       <c r="G121" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B122" s="2">
         <v>45141</v>
@@ -3287,12 +3287,12 @@
         <v>55.97</v>
       </c>
       <c r="G122" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B123" s="2">
         <v>45141</v>
@@ -3310,12 +3310,12 @@
         <v>55.69</v>
       </c>
       <c r="G123" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B124" s="2">
         <v>45141</v>
@@ -3333,12 +3333,12 @@
         <v>55.42</v>
       </c>
       <c r="G124" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B125" s="2">
         <v>45141</v>
@@ -3356,12 +3356,12 @@
         <v>55.42</v>
       </c>
       <c r="G125" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B126" s="2">
         <v>45141</v>
@@ -3379,12 +3379,12 @@
         <v>54.88</v>
       </c>
       <c r="G126" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B127" s="2">
         <v>45141</v>
@@ -3402,12 +3402,12 @@
         <v>55.42</v>
       </c>
       <c r="G127" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B128" s="2">
         <v>45141</v>
@@ -3425,12 +3425,12 @@
         <v>55.42</v>
       </c>
       <c r="G128" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B129" s="2">
         <v>45141</v>
@@ -3448,12 +3448,12 @@
         <v>55.42</v>
       </c>
       <c r="G129" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B130" s="2">
         <v>45141</v>
@@ -3471,12 +3471,12 @@
         <v>55.15</v>
       </c>
       <c r="G130" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B131" s="2">
         <v>45141</v>
@@ -3494,12 +3494,12 @@
         <v>55.15</v>
       </c>
       <c r="G131" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B132" s="2">
         <v>45141</v>
@@ -3517,12 +3517,12 @@
         <v>55.15</v>
       </c>
       <c r="G132" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B133" s="2">
         <v>45141</v>
@@ -3540,12 +3540,12 @@
         <v>55.15</v>
       </c>
       <c r="G133" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B134" s="2">
         <v>45141</v>
@@ -3563,12 +3563,12 @@
         <v>54.61</v>
       </c>
       <c r="G134" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B135" s="2">
         <v>45141</v>
@@ -3586,12 +3586,12 @@
         <v>54.61</v>
       </c>
       <c r="G135" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B136" s="2">
         <v>45141</v>
@@ -3609,12 +3609,12 @@
         <v>54.35</v>
       </c>
       <c r="G136" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B137" s="2">
         <v>45141</v>
@@ -3632,12 +3632,12 @@
         <v>54.61</v>
       </c>
       <c r="G137" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B138" s="2">
         <v>45141</v>
@@ -3655,12 +3655,12 @@
         <v>54.09</v>
       </c>
       <c r="G138" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B139" s="2">
         <v>45141</v>
@@ -3678,12 +3678,12 @@
         <v>54.09</v>
       </c>
       <c r="G139" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B140" s="2">
         <v>45141</v>
@@ -3701,12 +3701,12 @@
         <v>53.57</v>
       </c>
       <c r="G140" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B141" s="2">
         <v>45141</v>
@@ -3724,12 +3724,12 @@
         <v>53.57</v>
       </c>
       <c r="G141" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B142" s="2">
         <v>45141</v>
@@ -3747,12 +3747,12 @@
         <v>52.82</v>
       </c>
       <c r="G142" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B143" s="2">
         <v>45141</v>
@@ -3770,12 +3770,12 @@
         <v>53.32</v>
       </c>
       <c r="G143" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B144" s="2">
         <v>45141</v>
@@ -3793,12 +3793,12 @@
         <v>53.07</v>
       </c>
       <c r="G144" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B145" s="2">
         <v>45141</v>
@@ -3816,12 +3816,12 @@
         <v>52.57</v>
       </c>
       <c r="G145" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B146" s="2">
         <v>45133</v>
@@ -3839,15 +3839,15 @@
         <v>24.25</v>
       </c>
       <c r="G146" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B147" s="2">
         <v>45133</v>
@@ -3865,12 +3865,12 @@
         <v>43.95</v>
       </c>
       <c r="G147" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B148" s="2">
         <v>45133</v>
@@ -3888,12 +3888,12 @@
         <v>50.45</v>
       </c>
       <c r="G148" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B149" s="2">
         <v>45133</v>
@@ -3911,12 +3911,12 @@
         <v>53.57</v>
       </c>
       <c r="G149" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B150" s="2">
         <v>45133</v>
@@ -3934,12 +3934,12 @@
         <v>54.88</v>
       </c>
       <c r="G150" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B151" s="2">
         <v>45133</v>
@@ -3957,12 +3957,12 @@
         <v>54.61</v>
       </c>
       <c r="G151" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B152" s="2">
         <v>45133</v>
@@ -3980,12 +3980,12 @@
         <v>55.42</v>
       </c>
       <c r="G152" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B153" s="2">
         <v>45133</v>
@@ -4003,12 +4003,12 @@
         <v>55.42</v>
       </c>
       <c r="G153" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B154" s="2">
         <v>45133</v>
@@ -4026,12 +4026,12 @@
         <v>54.88</v>
       </c>
       <c r="G154" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B155" s="2">
         <v>45133</v>
@@ -4049,12 +4049,12 @@
         <v>54.35</v>
       </c>
       <c r="G155" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B156" s="2">
         <v>45133</v>
@@ -4072,12 +4072,12 @@
         <v>54.35</v>
       </c>
       <c r="G156" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B157" s="2">
         <v>45133</v>
@@ -4095,12 +4095,12 @@
         <v>54.09</v>
       </c>
       <c r="G157" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B158" s="2">
         <v>45133</v>
@@ -4118,12 +4118,12 @@
         <v>54.35</v>
       </c>
       <c r="G158" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B159" s="2">
         <v>45133</v>
@@ -4141,12 +4141,12 @@
         <v>53.57</v>
       </c>
       <c r="G159" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B160" s="2">
         <v>45133</v>
@@ -4164,12 +4164,12 @@
         <v>54.09</v>
       </c>
       <c r="G160" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B161" s="2">
         <v>45133</v>
@@ -4187,12 +4187,12 @@
         <v>53.83</v>
       </c>
       <c r="G161" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B162" s="2">
         <v>45133</v>
@@ -4210,12 +4210,12 @@
         <v>52.08</v>
       </c>
       <c r="G162" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B163" s="2">
         <v>45133</v>
@@ -4233,12 +4233,12 @@
         <v>56.25</v>
       </c>
       <c r="G163" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B164" s="2">
         <v>45133</v>
@@ -4256,12 +4256,12 @@
         <v>54.35</v>
       </c>
       <c r="G164" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B165" s="2">
         <v>45133</v>
@@ -4279,12 +4279,12 @@
         <v>54.35</v>
       </c>
       <c r="G165" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B166" s="2">
         <v>45133</v>
@@ -4302,12 +4302,12 @@
         <v>54.09</v>
       </c>
       <c r="G166" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B167" s="2">
         <v>45133</v>
@@ -4325,12 +4325,12 @@
         <v>54.09</v>
       </c>
       <c r="G167" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B168" s="2">
         <v>45133</v>
@@ -4348,12 +4348,12 @@
         <v>54.35</v>
       </c>
       <c r="G168" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B169" s="2">
         <v>45133</v>
@@ -4371,12 +4371,12 @@
         <v>54.88</v>
       </c>
       <c r="G169" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B170" s="2">
         <v>45133</v>
@@ -4394,12 +4394,12 @@
         <v>54.09</v>
       </c>
       <c r="G170" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B171" s="2">
         <v>45133</v>
@@ -4417,12 +4417,12 @@
         <v>54.09</v>
       </c>
       <c r="G171" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B172" s="2">
         <v>45133</v>
@@ -4440,12 +4440,12 @@
         <v>54.09</v>
       </c>
       <c r="G172" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B173" s="2">
         <v>45133</v>
@@ -4463,12 +4463,12 @@
         <v>53.57</v>
       </c>
       <c r="G173" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B174" s="2">
         <v>45133</v>
@@ -4486,12 +4486,12 @@
         <v>54.09</v>
       </c>
       <c r="G174" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B175" s="2">
         <v>45133</v>
@@ -4509,12 +4509,12 @@
         <v>53.07</v>
       </c>
       <c r="G175" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B176" s="2">
         <v>45133</v>
@@ -4532,12 +4532,12 @@
         <v>53.32</v>
       </c>
       <c r="G176" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B177" s="2">
         <v>45133</v>
@@ -4555,12 +4555,12 @@
         <v>53.32</v>
       </c>
       <c r="G177" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B178" s="2">
         <v>45133</v>
@@ -4578,12 +4578,12 @@
         <v>52.33</v>
       </c>
       <c r="G178" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B179" s="2">
         <v>45133</v>
@@ -4601,12 +4601,12 @@
         <v>51.84</v>
       </c>
       <c r="G179" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B180" s="2">
         <v>45133</v>
@@ -4624,12 +4624,12 @@
         <v>52.08</v>
       </c>
       <c r="G180" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B181" s="2">
         <v>45133</v>
@@ -4647,12 +4647,12 @@
         <v>52.33</v>
       </c>
       <c r="G181" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B182" s="2">
         <v>45133</v>
@@ -4670,12 +4670,12 @@
         <v>52.08</v>
       </c>
       <c r="G182" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B183" s="2">
         <v>45133</v>
@@ -4693,12 +4693,12 @@
         <v>51.61</v>
       </c>
       <c r="G183" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B184" s="2">
         <v>45133</v>
@@ -4716,12 +4716,12 @@
         <v>52.33</v>
       </c>
       <c r="G184" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B185" s="2">
         <v>45133</v>
@@ -4739,12 +4739,12 @@
         <v>51.84</v>
       </c>
       <c r="G185" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B186" s="2">
         <v>45133</v>
@@ -4762,12 +4762,12 @@
         <v>51.61</v>
       </c>
       <c r="G186" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B187" s="2">
         <v>45133</v>
@@ -4785,12 +4785,12 @@
         <v>51.61</v>
       </c>
       <c r="G187" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B188" s="2">
         <v>45133</v>
@@ -4808,12 +4808,12 @@
         <v>51.61</v>
       </c>
       <c r="G188" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B189" s="2">
         <v>45133</v>
@@ -4831,12 +4831,12 @@
         <v>51.14</v>
       </c>
       <c r="G189" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B190" s="2">
         <v>45133</v>
@@ -4854,12 +4854,12 @@
         <v>51.37</v>
       </c>
       <c r="G190" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B191" s="2">
         <v>45133</v>
@@ -4877,12 +4877,12 @@
         <v>51.37</v>
       </c>
       <c r="G191" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B192" s="2">
         <v>45133</v>
@@ -4900,12 +4900,12 @@
         <v>51.37</v>
       </c>
       <c r="G192" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B193" s="2">
         <v>45133</v>
@@ -4923,7 +4923,7 @@
         <v>51.14</v>
       </c>
       <c r="G193" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/pages/video_analysis/IP_Master_Women.xlsx
+++ b/pages/video_analysis/IP_Master_Women.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sportnzgroup-my.sharepoint.com/personal/anja_kuys_hpsnz_org_nz/Documents/Desktop/Scripts/CNZPD/pages/video_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE18465E-053E-4316-A4EA-E7776AC006F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_895A468780AFE1A16BBC3229C9E314422081DEFC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A59DB67-EAE6-4B0A-949F-2DAEC2BC9915}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1620" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$193</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="20">
   <si>
     <t>Title</t>
   </si>
@@ -49,62 +49,53 @@
     <t>Video</t>
   </si>
   <si>
+    <t>23-08-03 Sami Donnelly IP Q Glasgow WCH</t>
+  </si>
+  <si>
     <t>No Change</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UQrTnsCV3nI</t>
+  </si>
+  <si>
+    <t>23-08-03 Bryony Botha IP Q Glasgow WCH</t>
+  </si>
+  <si>
+    <t>https://youtu.be/63pks-zGKqc</t>
+  </si>
+  <si>
+    <t>23-08-03 Bryony Botha IP Bronze F Glasgow WCH</t>
+  </si>
+  <si>
+    <t>https://youtu.be/jN5BZ0WpgDc</t>
+  </si>
+  <si>
+    <t>23-07-26 Sami Donnelly Race Sim</t>
   </si>
   <si>
     <t>https://youtu.be/9AmV3XlPZeA</t>
   </si>
   <si>
-    <t>https://youtu.be/UQrTnsCV3nI</t>
+    <t>26-07-31 Glasgow CWG Botha Q</t>
   </si>
   <si>
-    <t>https://youtu.be/63pks-zGKqc</t>
+    <t/>
   </si>
   <si>
-    <t>https://youtu.be/jN5BZ0WpgDc</t>
-  </si>
-  <si>
-    <t>23-08-03 Sami Donnelly IP Q Glasgow WCH</t>
-  </si>
-  <si>
-    <t>23-08-03 Bryony Botha IP Q Glasgow WCH</t>
-  </si>
-  <si>
-    <t>23-08-03 Bryony Botha IP Bronze F Glasgow WCH</t>
-  </si>
-  <si>
-    <t>23-07-26 Sami Donnelly Race Sim</t>
+    <t>26-07-31 Glasgow CWG Shearman Q</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -115,7 +106,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -123,43 +114,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -458,51 +424,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H193"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I321"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="42.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.86328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="2">
+        <v>8</v>
+      </c>
+      <c r="B2">
         <v>45141</v>
       </c>
       <c r="C2">
@@ -518,17 +476,17 @@
         <v>23.78</v>
       </c>
       <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2">
+      <c r="B3">
         <v>45141</v>
       </c>
       <c r="C3">
@@ -544,14 +502,14 @@
         <v>43.27</v>
       </c>
       <c r="G3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2">
+      <c r="B4">
         <v>45141</v>
       </c>
       <c r="C4">
@@ -567,14 +525,14 @@
         <v>49.13</v>
       </c>
       <c r="G4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="B5">
         <v>45141</v>
       </c>
       <c r="C5">
@@ -590,14 +548,14 @@
         <v>52.57</v>
       </c>
       <c r="G5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <v>45141</v>
       </c>
       <c r="C6">
@@ -613,14 +571,14 @@
         <v>54.61</v>
       </c>
       <c r="G6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="B7">
         <v>45141</v>
       </c>
       <c r="C7">
@@ -636,14 +594,14 @@
         <v>54.61</v>
       </c>
       <c r="G7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="2">
+      <c r="B8">
         <v>45141</v>
       </c>
       <c r="C8">
@@ -659,14 +617,14 @@
         <v>54.88</v>
       </c>
       <c r="G8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="2">
+      <c r="B9">
         <v>45141</v>
       </c>
       <c r="C9">
@@ -682,14 +640,14 @@
         <v>55.15</v>
       </c>
       <c r="G9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="2">
+      <c r="B10">
         <v>45141</v>
       </c>
       <c r="C10">
@@ -705,14 +663,14 @@
         <v>55.15</v>
       </c>
       <c r="G10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="2">
+      <c r="B11">
         <v>45141</v>
       </c>
       <c r="C11">
@@ -728,14 +686,14 @@
         <v>54.88</v>
       </c>
       <c r="G11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="2">
+      <c r="B12">
         <v>45141</v>
       </c>
       <c r="C12">
@@ -751,14 +709,14 @@
         <v>54.49</v>
       </c>
       <c r="G12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="2">
+      <c r="B13">
         <v>45141</v>
       </c>
       <c r="C13">
@@ -774,14 +732,14 @@
         <v>54.73</v>
       </c>
       <c r="G13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2">
+      <c r="B14">
         <v>45141</v>
       </c>
       <c r="C14">
@@ -797,14 +755,14 @@
         <v>54.09</v>
       </c>
       <c r="G14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2">
+      <c r="B15">
         <v>45141</v>
       </c>
       <c r="C15">
@@ -820,14 +778,14 @@
         <v>53.57</v>
       </c>
       <c r="G15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="2">
+      <c r="B16">
         <v>45141</v>
       </c>
       <c r="C16">
@@ -843,14 +801,14 @@
         <v>53.53</v>
       </c>
       <c r="G16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="2">
+      <c r="B17">
         <v>45141</v>
       </c>
       <c r="C17">
@@ -866,14 +824,14 @@
         <v>53.61</v>
       </c>
       <c r="G17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="2">
+      <c r="B18">
         <v>45141</v>
       </c>
       <c r="C18">
@@ -889,14 +847,14 @@
         <v>53.57</v>
       </c>
       <c r="G18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="2">
+      <c r="B19">
         <v>45141</v>
       </c>
       <c r="C19">
@@ -912,14 +870,14 @@
         <v>53.57</v>
       </c>
       <c r="G19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="2">
+      <c r="B20">
         <v>45141</v>
       </c>
       <c r="C20">
@@ -935,14 +893,14 @@
         <v>53.32</v>
       </c>
       <c r="G20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="2">
+      <c r="B21">
         <v>45141</v>
       </c>
       <c r="C21">
@@ -958,14 +916,14 @@
         <v>53.32</v>
       </c>
       <c r="G21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="2">
+      <c r="B22">
         <v>45141</v>
       </c>
       <c r="C22">
@@ -981,14 +939,14 @@
         <v>53.32</v>
       </c>
       <c r="G22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="2">
+      <c r="B23">
         <v>45141</v>
       </c>
       <c r="C23">
@@ -1004,14 +962,14 @@
         <v>53.57</v>
       </c>
       <c r="G23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="2">
+      <c r="B24">
         <v>45141</v>
       </c>
       <c r="C24">
@@ -1027,14 +985,14 @@
         <v>53.07</v>
       </c>
       <c r="G24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="2">
+      <c r="B25">
         <v>45141</v>
       </c>
       <c r="C25">
@@ -1050,14 +1008,14 @@
         <v>53.07</v>
       </c>
       <c r="G25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" s="2">
+      <c r="B26">
         <v>45141</v>
       </c>
       <c r="C26">
@@ -1073,14 +1031,14 @@
         <v>53.36</v>
       </c>
       <c r="G26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="2">
+      <c r="B27">
         <v>45141</v>
       </c>
       <c r="C27">
@@ -1096,14 +1054,14 @@
         <v>53.27</v>
       </c>
       <c r="G27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" s="2">
+      <c r="B28">
         <v>45141</v>
       </c>
       <c r="C28">
@@ -1119,14 +1077,14 @@
         <v>53.32</v>
       </c>
       <c r="G28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" s="2">
+      <c r="B29">
         <v>45141</v>
       </c>
       <c r="C29">
@@ -1142,14 +1100,14 @@
         <v>53.07</v>
       </c>
       <c r="G29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="2">
+      <c r="B30">
         <v>45141</v>
       </c>
       <c r="C30">
@@ -1165,14 +1123,14 @@
         <v>53.32</v>
       </c>
       <c r="G30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="2">
+      <c r="B31">
         <v>45141</v>
       </c>
       <c r="C31">
@@ -1188,14 +1146,14 @@
         <v>53.32</v>
       </c>
       <c r="G31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" s="2">
+      <c r="B32">
         <v>45141</v>
       </c>
       <c r="C32">
@@ -1211,14 +1169,14 @@
         <v>52.82</v>
       </c>
       <c r="G32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" s="2">
+      <c r="B33">
         <v>45141</v>
       </c>
       <c r="C33">
@@ -1234,14 +1192,14 @@
         <v>53.32</v>
       </c>
       <c r="G33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" s="2">
+      <c r="B34">
         <v>45141</v>
       </c>
       <c r="C34">
@@ -1257,14 +1215,14 @@
         <v>53.07</v>
       </c>
       <c r="G34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>13</v>
-      </c>
-      <c r="B35" s="2">
+      <c r="B35">
         <v>45141</v>
       </c>
       <c r="C35">
@@ -1280,14 +1238,14 @@
         <v>53.32</v>
       </c>
       <c r="G35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>13</v>
-      </c>
-      <c r="B36" s="2">
+      <c r="B36">
         <v>45141</v>
       </c>
       <c r="C36">
@@ -1303,14 +1261,14 @@
         <v>53.32</v>
       </c>
       <c r="G36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>13</v>
-      </c>
-      <c r="B37" s="2">
+      <c r="B37">
         <v>45141</v>
       </c>
       <c r="C37">
@@ -1326,14 +1284,14 @@
         <v>53.57</v>
       </c>
       <c r="G37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>13</v>
-      </c>
-      <c r="B38" s="2">
+      <c r="B38">
         <v>45141</v>
       </c>
       <c r="C38">
@@ -1349,14 +1307,14 @@
         <v>53.32</v>
       </c>
       <c r="G38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>13</v>
-      </c>
-      <c r="B39" s="2">
+      <c r="B39">
         <v>45141</v>
       </c>
       <c r="C39">
@@ -1372,14 +1330,14 @@
         <v>53.57</v>
       </c>
       <c r="G39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>13</v>
-      </c>
-      <c r="B40" s="2">
+      <c r="B40">
         <v>45141</v>
       </c>
       <c r="C40">
@@ -1395,14 +1353,14 @@
         <v>54.09</v>
       </c>
       <c r="G40" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>13</v>
-      </c>
-      <c r="B41" s="2">
+      <c r="B41">
         <v>45141</v>
       </c>
       <c r="C41">
@@ -1418,14 +1376,14 @@
         <v>54.35</v>
       </c>
       <c r="G41" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>13</v>
-      </c>
-      <c r="B42" s="2">
+      <c r="B42">
         <v>45141</v>
       </c>
       <c r="C42">
@@ -1441,14 +1399,14 @@
         <v>54.09</v>
       </c>
       <c r="G42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>13</v>
-      </c>
-      <c r="B43" s="2">
+      <c r="B43">
         <v>45141</v>
       </c>
       <c r="C43">
@@ -1464,14 +1422,14 @@
         <v>54.09</v>
       </c>
       <c r="G43" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>13</v>
-      </c>
-      <c r="B44" s="2">
+      <c r="B44">
         <v>45141</v>
       </c>
       <c r="C44">
@@ -1487,14 +1445,14 @@
         <v>54.09</v>
       </c>
       <c r="G44" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>13</v>
-      </c>
-      <c r="B45" s="2">
+      <c r="B45">
         <v>45141</v>
       </c>
       <c r="C45">
@@ -1510,14 +1468,14 @@
         <v>54.09</v>
       </c>
       <c r="G45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
-        <v>13</v>
-      </c>
-      <c r="B46" s="2">
+      <c r="B46">
         <v>45141</v>
       </c>
       <c r="C46">
@@ -1533,14 +1491,14 @@
         <v>54.35</v>
       </c>
       <c r="G46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
-        <v>13</v>
-      </c>
-      <c r="B47" s="2">
+      <c r="B47">
         <v>45141</v>
       </c>
       <c r="C47">
@@ -1556,14 +1514,14 @@
         <v>54.09</v>
       </c>
       <c r="G47" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>13</v>
-      </c>
-      <c r="B48" s="2">
+      <c r="B48">
         <v>45141</v>
       </c>
       <c r="C48">
@@ -1579,14 +1537,14 @@
         <v>54.35</v>
       </c>
       <c r="G48" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>13</v>
-      </c>
-      <c r="B49" s="2">
+      <c r="B49">
         <v>45141</v>
       </c>
       <c r="C49">
@@ -1602,14 +1560,14 @@
         <v>53.07</v>
       </c>
       <c r="G49" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>14</v>
-      </c>
-      <c r="B50" s="2">
+        <v>11</v>
+      </c>
+      <c r="B50">
         <v>45141</v>
       </c>
       <c r="C50">
@@ -1625,17 +1583,17 @@
         <v>23.68</v>
       </c>
       <c r="G50" t="s">
-        <v>8</v>
-      </c>
-      <c r="H50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H50" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
-        <v>14</v>
-      </c>
-      <c r="B51" s="2">
+      <c r="B51">
         <v>45141</v>
       </c>
       <c r="C51">
@@ -1651,14 +1609,14 @@
         <v>43.6</v>
       </c>
       <c r="G51" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>14</v>
-      </c>
-      <c r="B52" s="2">
+        <v>11</v>
+      </c>
+      <c r="B52">
         <v>45141</v>
       </c>
       <c r="C52">
@@ -1674,14 +1632,14 @@
         <v>50.68</v>
       </c>
       <c r="G52" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>14</v>
-      </c>
-      <c r="B53" s="2">
+        <v>11</v>
+      </c>
+      <c r="B53">
         <v>45141</v>
       </c>
       <c r="C53">
@@ -1697,14 +1655,14 @@
         <v>53.32</v>
       </c>
       <c r="G53" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>14</v>
-      </c>
-      <c r="B54" s="2">
+        <v>11</v>
+      </c>
+      <c r="B54">
         <v>45141</v>
       </c>
       <c r="C54">
@@ -1720,14 +1678,14 @@
         <v>55.42</v>
       </c>
       <c r="G54" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>14</v>
-      </c>
-      <c r="B55" s="2">
+        <v>11</v>
+      </c>
+      <c r="B55">
         <v>45141</v>
       </c>
       <c r="C55">
@@ -1743,14 +1701,14 @@
         <v>55.97</v>
       </c>
       <c r="G55" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>14</v>
-      </c>
-      <c r="B56" s="2">
+        <v>11</v>
+      </c>
+      <c r="B56">
         <v>45141</v>
       </c>
       <c r="C56">
@@ -1766,14 +1724,14 @@
         <v>56.25</v>
       </c>
       <c r="G56" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>14</v>
-      </c>
-      <c r="B57" s="2">
+        <v>11</v>
+      </c>
+      <c r="B57">
         <v>45141</v>
       </c>
       <c r="C57">
@@ -1789,14 +1747,14 @@
         <v>57.11</v>
       </c>
       <c r="G57" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>14</v>
-      </c>
-      <c r="B58" s="2">
+        <v>11</v>
+      </c>
+      <c r="B58">
         <v>45141</v>
       </c>
       <c r="C58">
@@ -1812,14 +1770,14 @@
         <v>56.82</v>
       </c>
       <c r="G58" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>14</v>
-      </c>
-      <c r="B59" s="2">
+        <v>11</v>
+      </c>
+      <c r="B59">
         <v>45141</v>
       </c>
       <c r="C59">
@@ -1835,14 +1793,14 @@
         <v>56.25</v>
       </c>
       <c r="G59" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>14</v>
-      </c>
-      <c r="B60" s="2">
+        <v>11</v>
+      </c>
+      <c r="B60">
         <v>45141</v>
       </c>
       <c r="C60">
@@ -1858,14 +1816,14 @@
         <v>56.82</v>
       </c>
       <c r="G60" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>14</v>
-      </c>
-      <c r="B61" s="2">
+        <v>11</v>
+      </c>
+      <c r="B61">
         <v>45141</v>
       </c>
       <c r="C61">
@@ -1881,14 +1839,14 @@
         <v>56.53</v>
       </c>
       <c r="G61" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>14</v>
-      </c>
-      <c r="B62" s="2">
+        <v>11</v>
+      </c>
+      <c r="B62">
         <v>45141</v>
       </c>
       <c r="C62">
@@ -1904,14 +1862,14 @@
         <v>56.53</v>
       </c>
       <c r="G62" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>14</v>
-      </c>
-      <c r="B63" s="2">
+        <v>11</v>
+      </c>
+      <c r="B63">
         <v>45141</v>
       </c>
       <c r="C63">
@@ -1927,14 +1885,14 @@
         <v>55.97</v>
       </c>
       <c r="G63" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>14</v>
-      </c>
-      <c r="B64" s="2">
+        <v>11</v>
+      </c>
+      <c r="B64">
         <v>45141</v>
       </c>
       <c r="C64">
@@ -1950,14 +1908,14 @@
         <v>55.97</v>
       </c>
       <c r="G64" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>14</v>
-      </c>
-      <c r="B65" s="2">
+        <v>11</v>
+      </c>
+      <c r="B65">
         <v>45141</v>
       </c>
       <c r="C65">
@@ -1973,14 +1931,14 @@
         <v>55.97</v>
       </c>
       <c r="G65" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>14</v>
-      </c>
-      <c r="B66" s="2">
+        <v>11</v>
+      </c>
+      <c r="B66">
         <v>45141</v>
       </c>
       <c r="C66">
@@ -1996,14 +1954,14 @@
         <v>55.97</v>
       </c>
       <c r="G66" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>14</v>
-      </c>
-      <c r="B67" s="2">
+        <v>11</v>
+      </c>
+      <c r="B67">
         <v>45141</v>
       </c>
       <c r="C67">
@@ -2019,14 +1977,14 @@
         <v>55.69</v>
       </c>
       <c r="G67" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>14</v>
-      </c>
-      <c r="B68" s="2">
+        <v>11</v>
+      </c>
+      <c r="B68">
         <v>45141</v>
       </c>
       <c r="C68">
@@ -2042,14 +2000,14 @@
         <v>55.97</v>
       </c>
       <c r="G68" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>14</v>
-      </c>
-      <c r="B69" s="2">
+        <v>11</v>
+      </c>
+      <c r="B69">
         <v>45141</v>
       </c>
       <c r="C69">
@@ -2065,14 +2023,14 @@
         <v>56.25</v>
       </c>
       <c r="G69" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>14</v>
-      </c>
-      <c r="B70" s="2">
+        <v>11</v>
+      </c>
+      <c r="B70">
         <v>45141</v>
       </c>
       <c r="C70">
@@ -2088,14 +2046,14 @@
         <v>55.97</v>
       </c>
       <c r="G70" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>14</v>
-      </c>
-      <c r="B71" s="2">
+        <v>11</v>
+      </c>
+      <c r="B71">
         <v>45141</v>
       </c>
       <c r="C71">
@@ -2111,14 +2069,14 @@
         <v>56.25</v>
       </c>
       <c r="G71" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>14</v>
-      </c>
-      <c r="B72" s="2">
+        <v>11</v>
+      </c>
+      <c r="B72">
         <v>45141</v>
       </c>
       <c r="C72">
@@ -2134,14 +2092,14 @@
         <v>55.97</v>
       </c>
       <c r="G72" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>14</v>
-      </c>
-      <c r="B73" s="2">
+        <v>11</v>
+      </c>
+      <c r="B73">
         <v>45141</v>
       </c>
       <c r="C73">
@@ -2157,14 +2115,14 @@
         <v>55.97</v>
       </c>
       <c r="G73" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>14</v>
-      </c>
-      <c r="B74" s="2">
+        <v>11</v>
+      </c>
+      <c r="B74">
         <v>45141</v>
       </c>
       <c r="C74">
@@ -2180,14 +2138,14 @@
         <v>55.97</v>
       </c>
       <c r="G74" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>14</v>
-      </c>
-      <c r="B75" s="2">
+        <v>11</v>
+      </c>
+      <c r="B75">
         <v>45141</v>
       </c>
       <c r="C75">
@@ -2203,14 +2161,14 @@
         <v>56.25</v>
       </c>
       <c r="G75" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>14</v>
-      </c>
-      <c r="B76" s="2">
+        <v>11</v>
+      </c>
+      <c r="B76">
         <v>45141</v>
       </c>
       <c r="C76">
@@ -2226,14 +2184,14 @@
         <v>55.97</v>
       </c>
       <c r="G76" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>14</v>
-      </c>
-      <c r="B77" s="2">
+        <v>11</v>
+      </c>
+      <c r="B77">
         <v>45141</v>
       </c>
       <c r="C77">
@@ -2249,14 +2207,14 @@
         <v>55.97</v>
       </c>
       <c r="G77" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>14</v>
-      </c>
-      <c r="B78" s="2">
+        <v>11</v>
+      </c>
+      <c r="B78">
         <v>45141</v>
       </c>
       <c r="C78">
@@ -2272,14 +2230,14 @@
         <v>56.25</v>
       </c>
       <c r="G78" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>14</v>
-      </c>
-      <c r="B79" s="2">
+        <v>11</v>
+      </c>
+      <c r="B79">
         <v>45141</v>
       </c>
       <c r="C79">
@@ -2295,14 +2253,14 @@
         <v>56.25</v>
       </c>
       <c r="G79" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>14</v>
-      </c>
-      <c r="B80" s="2">
+        <v>11</v>
+      </c>
+      <c r="B80">
         <v>45141</v>
       </c>
       <c r="C80">
@@ -2318,14 +2276,14 @@
         <v>56.25</v>
       </c>
       <c r="G80" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>14</v>
-      </c>
-      <c r="B81" s="2">
+        <v>11</v>
+      </c>
+      <c r="B81">
         <v>45141</v>
       </c>
       <c r="C81">
@@ -2341,14 +2299,14 @@
         <v>56.53</v>
       </c>
       <c r="G81" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>14</v>
-      </c>
-      <c r="B82" s="2">
+        <v>11</v>
+      </c>
+      <c r="B82">
         <v>45141</v>
       </c>
       <c r="C82">
@@ -2364,14 +2322,14 @@
         <v>55.97</v>
       </c>
       <c r="G82" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>14</v>
-      </c>
-      <c r="B83" s="2">
+        <v>11</v>
+      </c>
+      <c r="B83">
         <v>45141</v>
       </c>
       <c r="C83">
@@ -2387,14 +2345,14 @@
         <v>56.25</v>
       </c>
       <c r="G83" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>14</v>
-      </c>
-      <c r="B84" s="2">
+        <v>11</v>
+      </c>
+      <c r="B84">
         <v>45141</v>
       </c>
       <c r="C84">
@@ -2410,14 +2368,14 @@
         <v>55.97</v>
       </c>
       <c r="G84" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>14</v>
-      </c>
-      <c r="B85" s="2">
+        <v>11</v>
+      </c>
+      <c r="B85">
         <v>45141</v>
       </c>
       <c r="C85">
@@ -2433,14 +2391,14 @@
         <v>56.25</v>
       </c>
       <c r="G85" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>14</v>
-      </c>
-      <c r="B86" s="2">
+        <v>11</v>
+      </c>
+      <c r="B86">
         <v>45141</v>
       </c>
       <c r="C86">
@@ -2456,14 +2414,14 @@
         <v>55.97</v>
       </c>
       <c r="G86" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>14</v>
-      </c>
-      <c r="B87" s="2">
+        <v>11</v>
+      </c>
+      <c r="B87">
         <v>45141</v>
       </c>
       <c r="C87">
@@ -2479,14 +2437,14 @@
         <v>55.97</v>
       </c>
       <c r="G87" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>14</v>
-      </c>
-      <c r="B88" s="2">
+        <v>11</v>
+      </c>
+      <c r="B88">
         <v>45141</v>
       </c>
       <c r="C88">
@@ -2502,14 +2460,14 @@
         <v>55.69</v>
       </c>
       <c r="G88" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>14</v>
-      </c>
-      <c r="B89" s="2">
+        <v>11</v>
+      </c>
+      <c r="B89">
         <v>45141</v>
       </c>
       <c r="C89">
@@ -2525,14 +2483,14 @@
         <v>55.42</v>
       </c>
       <c r="G89" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>14</v>
-      </c>
-      <c r="B90" s="2">
+        <v>11</v>
+      </c>
+      <c r="B90">
         <v>45141</v>
       </c>
       <c r="C90">
@@ -2548,14 +2506,14 @@
         <v>54.88</v>
       </c>
       <c r="G90" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>14</v>
-      </c>
-      <c r="B91" s="2">
+        <v>11</v>
+      </c>
+      <c r="B91">
         <v>45141</v>
       </c>
       <c r="C91">
@@ -2571,14 +2529,14 @@
         <v>55.69</v>
       </c>
       <c r="G91" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>14</v>
-      </c>
-      <c r="B92" s="2">
+        <v>11</v>
+      </c>
+      <c r="B92">
         <v>45141</v>
       </c>
       <c r="C92">
@@ -2594,14 +2552,14 @@
         <v>54.88</v>
       </c>
       <c r="G92" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>14</v>
-      </c>
-      <c r="B93" s="2">
+        <v>11</v>
+      </c>
+      <c r="B93">
         <v>45141</v>
       </c>
       <c r="C93">
@@ -2617,14 +2575,14 @@
         <v>55.42</v>
       </c>
       <c r="G93" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>14</v>
-      </c>
-      <c r="B94" s="2">
+        <v>11</v>
+      </c>
+      <c r="B94">
         <v>45141</v>
       </c>
       <c r="C94">
@@ -2640,14 +2598,14 @@
         <v>54.88</v>
       </c>
       <c r="G94" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>14</v>
-      </c>
-      <c r="B95" s="2">
+        <v>11</v>
+      </c>
+      <c r="B95">
         <v>45141</v>
       </c>
       <c r="C95">
@@ -2663,14 +2621,14 @@
         <v>55.42</v>
       </c>
       <c r="G95" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>14</v>
-      </c>
-      <c r="B96" s="2">
+        <v>11</v>
+      </c>
+      <c r="B96">
         <v>45141</v>
       </c>
       <c r="C96">
@@ -2686,14 +2644,14 @@
         <v>54.61</v>
       </c>
       <c r="G96" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>14</v>
-      </c>
-      <c r="B97" s="2">
+        <v>11</v>
+      </c>
+      <c r="B97">
         <v>45141</v>
       </c>
       <c r="C97">
@@ -2709,14 +2667,14 @@
         <v>55.15</v>
       </c>
       <c r="G97" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" s="2">
+        <v>13</v>
+      </c>
+      <c r="B98">
         <v>45141</v>
       </c>
       <c r="C98">
@@ -2732,17 +2690,17 @@
         <v>24.09</v>
       </c>
       <c r="G98" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H98" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" s="2">
+        <v>13</v>
+      </c>
+      <c r="B99">
         <v>45141</v>
       </c>
       <c r="C99">
@@ -2758,14 +2716,14 @@
         <v>44.12</v>
       </c>
       <c r="G99" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" s="2">
+        <v>13</v>
+      </c>
+      <c r="B100">
         <v>45141</v>
       </c>
       <c r="C100">
@@ -2781,14 +2739,14 @@
         <v>51.14</v>
       </c>
       <c r="G100" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" s="2">
+        <v>13</v>
+      </c>
+      <c r="B101">
         <v>45141</v>
       </c>
       <c r="C101">
@@ -2804,14 +2762,14 @@
         <v>53.57</v>
       </c>
       <c r="G101" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" s="2">
+        <v>13</v>
+      </c>
+      <c r="B102">
         <v>45141</v>
       </c>
       <c r="C102">
@@ -2827,14 +2785,14 @@
         <v>55.69</v>
       </c>
       <c r="G102" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" s="2">
+        <v>13</v>
+      </c>
+      <c r="B103">
         <v>45141</v>
       </c>
       <c r="C103">
@@ -2850,14 +2808,14 @@
         <v>56.53</v>
       </c>
       <c r="G103" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" s="2">
+        <v>13</v>
+      </c>
+      <c r="B104">
         <v>45141</v>
       </c>
       <c r="C104">
@@ -2873,14 +2831,14 @@
         <v>57.11</v>
       </c>
       <c r="G104" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" s="2">
+        <v>13</v>
+      </c>
+      <c r="B105">
         <v>45141</v>
       </c>
       <c r="C105">
@@ -2896,14 +2854,14 @@
         <v>57.11</v>
       </c>
       <c r="G105" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" s="2">
+        <v>13</v>
+      </c>
+      <c r="B106">
         <v>45141</v>
       </c>
       <c r="C106">
@@ -2919,14 +2877,14 @@
         <v>57.11</v>
       </c>
       <c r="G106" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" s="2">
+        <v>13</v>
+      </c>
+      <c r="B107">
         <v>45141</v>
       </c>
       <c r="C107">
@@ -2942,14 +2900,14 @@
         <v>56.82</v>
       </c>
       <c r="G107" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" s="2">
+        <v>13</v>
+      </c>
+      <c r="B108">
         <v>45141</v>
       </c>
       <c r="C108">
@@ -2965,14 +2923,14 @@
         <v>56.82</v>
       </c>
       <c r="G108" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" s="2">
+        <v>13</v>
+      </c>
+      <c r="B109">
         <v>45141</v>
       </c>
       <c r="C109">
@@ -2988,14 +2946,14 @@
         <v>56.25</v>
       </c>
       <c r="G109" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" s="2">
+        <v>13</v>
+      </c>
+      <c r="B110">
         <v>45141</v>
       </c>
       <c r="C110">
@@ -3011,14 +2969,14 @@
         <v>55.97</v>
       </c>
       <c r="G110" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" s="2">
+        <v>13</v>
+      </c>
+      <c r="B111">
         <v>45141</v>
       </c>
       <c r="C111">
@@ -3034,14 +2992,14 @@
         <v>55.97</v>
       </c>
       <c r="G111" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" s="2">
+        <v>13</v>
+      </c>
+      <c r="B112">
         <v>45141</v>
       </c>
       <c r="C112">
@@ -3057,14 +3015,14 @@
         <v>55.97</v>
       </c>
       <c r="G112" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" s="2">
+        <v>13</v>
+      </c>
+      <c r="B113">
         <v>45141</v>
       </c>
       <c r="C113">
@@ -3080,14 +3038,14 @@
         <v>55.69</v>
       </c>
       <c r="G113" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" s="2">
+        <v>13</v>
+      </c>
+      <c r="B114">
         <v>45141</v>
       </c>
       <c r="C114">
@@ -3103,14 +3061,14 @@
         <v>55.69</v>
       </c>
       <c r="G114" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" s="2">
+        <v>13</v>
+      </c>
+      <c r="B115">
         <v>45141</v>
       </c>
       <c r="C115">
@@ -3126,14 +3084,14 @@
         <v>55.69</v>
       </c>
       <c r="G115" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" s="2">
+        <v>13</v>
+      </c>
+      <c r="B116">
         <v>45141</v>
       </c>
       <c r="C116">
@@ -3149,14 +3107,14 @@
         <v>55.69</v>
       </c>
       <c r="G116" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" s="2">
+        <v>13</v>
+      </c>
+      <c r="B117">
         <v>45141</v>
       </c>
       <c r="C117">
@@ -3172,14 +3130,14 @@
         <v>55.69</v>
       </c>
       <c r="G117" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" s="2">
+        <v>13</v>
+      </c>
+      <c r="B118">
         <v>45141</v>
       </c>
       <c r="C118">
@@ -3195,14 +3153,14 @@
         <v>55.69</v>
       </c>
       <c r="G118" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" s="2">
+        <v>13</v>
+      </c>
+      <c r="B119">
         <v>45141</v>
       </c>
       <c r="C119">
@@ -3218,14 +3176,14 @@
         <v>55.97</v>
       </c>
       <c r="G119" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" s="2">
+        <v>13</v>
+      </c>
+      <c r="B120">
         <v>45141</v>
       </c>
       <c r="C120">
@@ -3241,14 +3199,14 @@
         <v>55.69</v>
       </c>
       <c r="G120" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" s="2">
+        <v>13</v>
+      </c>
+      <c r="B121">
         <v>45141</v>
       </c>
       <c r="C121">
@@ -3264,14 +3222,14 @@
         <v>55.97</v>
       </c>
       <c r="G121" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" s="2">
+        <v>13</v>
+      </c>
+      <c r="B122">
         <v>45141</v>
       </c>
       <c r="C122">
@@ -3287,14 +3245,14 @@
         <v>55.97</v>
       </c>
       <c r="G122" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" s="2">
+        <v>13</v>
+      </c>
+      <c r="B123">
         <v>45141</v>
       </c>
       <c r="C123">
@@ -3310,14 +3268,14 @@
         <v>55.69</v>
       </c>
       <c r="G123" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" s="2">
+        <v>13</v>
+      </c>
+      <c r="B124">
         <v>45141</v>
       </c>
       <c r="C124">
@@ -3333,14 +3291,14 @@
         <v>55.42</v>
       </c>
       <c r="G124" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" s="2">
+        <v>13</v>
+      </c>
+      <c r="B125">
         <v>45141</v>
       </c>
       <c r="C125">
@@ -3356,14 +3314,14 @@
         <v>55.42</v>
       </c>
       <c r="G125" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" s="2">
+        <v>13</v>
+      </c>
+      <c r="B126">
         <v>45141</v>
       </c>
       <c r="C126">
@@ -3379,14 +3337,14 @@
         <v>54.88</v>
       </c>
       <c r="G126" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" s="2">
+        <v>13</v>
+      </c>
+      <c r="B127">
         <v>45141</v>
       </c>
       <c r="C127">
@@ -3402,14 +3360,14 @@
         <v>55.42</v>
       </c>
       <c r="G127" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" s="2">
+        <v>13</v>
+      </c>
+      <c r="B128">
         <v>45141</v>
       </c>
       <c r="C128">
@@ -3425,14 +3383,14 @@
         <v>55.42</v>
       </c>
       <c r="G128" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" s="2">
+        <v>13</v>
+      </c>
+      <c r="B129">
         <v>45141</v>
       </c>
       <c r="C129">
@@ -3448,14 +3406,14 @@
         <v>55.42</v>
       </c>
       <c r="G129" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" s="2">
+        <v>13</v>
+      </c>
+      <c r="B130">
         <v>45141</v>
       </c>
       <c r="C130">
@@ -3471,14 +3429,14 @@
         <v>55.15</v>
       </c>
       <c r="G130" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" s="2">
+        <v>13</v>
+      </c>
+      <c r="B131">
         <v>45141</v>
       </c>
       <c r="C131">
@@ -3494,14 +3452,14 @@
         <v>55.15</v>
       </c>
       <c r="G131" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" s="2">
+        <v>13</v>
+      </c>
+      <c r="B132">
         <v>45141</v>
       </c>
       <c r="C132">
@@ -3517,14 +3475,14 @@
         <v>55.15</v>
       </c>
       <c r="G132" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" s="2">
+        <v>13</v>
+      </c>
+      <c r="B133">
         <v>45141</v>
       </c>
       <c r="C133">
@@ -3540,14 +3498,14 @@
         <v>55.15</v>
       </c>
       <c r="G133" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" s="2">
+        <v>13</v>
+      </c>
+      <c r="B134">
         <v>45141</v>
       </c>
       <c r="C134">
@@ -3563,14 +3521,14 @@
         <v>54.61</v>
       </c>
       <c r="G134" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" s="2">
+        <v>13</v>
+      </c>
+      <c r="B135">
         <v>45141</v>
       </c>
       <c r="C135">
@@ -3586,14 +3544,14 @@
         <v>54.61</v>
       </c>
       <c r="G135" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" s="2">
+        <v>13</v>
+      </c>
+      <c r="B136">
         <v>45141</v>
       </c>
       <c r="C136">
@@ -3609,14 +3567,14 @@
         <v>54.35</v>
       </c>
       <c r="G136" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" s="2">
+        <v>13</v>
+      </c>
+      <c r="B137">
         <v>45141</v>
       </c>
       <c r="C137">
@@ -3632,14 +3590,14 @@
         <v>54.61</v>
       </c>
       <c r="G137" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" s="2">
+        <v>13</v>
+      </c>
+      <c r="B138">
         <v>45141</v>
       </c>
       <c r="C138">
@@ -3655,14 +3613,14 @@
         <v>54.09</v>
       </c>
       <c r="G138" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" s="2">
+        <v>13</v>
+      </c>
+      <c r="B139">
         <v>45141</v>
       </c>
       <c r="C139">
@@ -3678,14 +3636,14 @@
         <v>54.09</v>
       </c>
       <c r="G139" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" s="2">
+        <v>13</v>
+      </c>
+      <c r="B140">
         <v>45141</v>
       </c>
       <c r="C140">
@@ -3701,14 +3659,14 @@
         <v>53.57</v>
       </c>
       <c r="G140" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" s="2">
+        <v>13</v>
+      </c>
+      <c r="B141">
         <v>45141</v>
       </c>
       <c r="C141">
@@ -3724,14 +3682,14 @@
         <v>53.57</v>
       </c>
       <c r="G141" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" s="2">
+        <v>13</v>
+      </c>
+      <c r="B142">
         <v>45141</v>
       </c>
       <c r="C142">
@@ -3747,14 +3705,14 @@
         <v>52.82</v>
       </c>
       <c r="G142" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" s="2">
+        <v>13</v>
+      </c>
+      <c r="B143">
         <v>45141</v>
       </c>
       <c r="C143">
@@ -3770,14 +3728,14 @@
         <v>53.32</v>
       </c>
       <c r="G143" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" s="2">
+        <v>13</v>
+      </c>
+      <c r="B144">
         <v>45141</v>
       </c>
       <c r="C144">
@@ -3793,14 +3751,14 @@
         <v>53.07</v>
       </c>
       <c r="G144" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" s="2">
+        <v>13</v>
+      </c>
+      <c r="B145">
         <v>45141</v>
       </c>
       <c r="C145">
@@ -3816,14 +3774,14 @@
         <v>52.57</v>
       </c>
       <c r="G145" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>16</v>
-      </c>
-      <c r="B146" s="2">
+        <v>15</v>
+      </c>
+      <c r="B146">
         <v>45133</v>
       </c>
       <c r="C146">
@@ -3839,17 +3797,17 @@
         <v>24.25</v>
       </c>
       <c r="G146" t="s">
-        <v>8</v>
-      </c>
-      <c r="H146" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+      <c r="H146" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>16</v>
-      </c>
-      <c r="B147" s="2">
+        <v>15</v>
+      </c>
+      <c r="B147">
         <v>45133</v>
       </c>
       <c r="C147">
@@ -3865,14 +3823,14 @@
         <v>43.95</v>
       </c>
       <c r="G147" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>16</v>
-      </c>
-      <c r="B148" s="2">
+        <v>15</v>
+      </c>
+      <c r="B148">
         <v>45133</v>
       </c>
       <c r="C148">
@@ -3888,14 +3846,14 @@
         <v>50.45</v>
       </c>
       <c r="G148" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>16</v>
-      </c>
-      <c r="B149" s="2">
+        <v>15</v>
+      </c>
+      <c r="B149">
         <v>45133</v>
       </c>
       <c r="C149">
@@ -3911,14 +3869,14 @@
         <v>53.57</v>
       </c>
       <c r="G149" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>16</v>
-      </c>
-      <c r="B150" s="2">
+        <v>15</v>
+      </c>
+      <c r="B150">
         <v>45133</v>
       </c>
       <c r="C150">
@@ -3934,14 +3892,14 @@
         <v>54.88</v>
       </c>
       <c r="G150" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>16</v>
-      </c>
-      <c r="B151" s="2">
+        <v>15</v>
+      </c>
+      <c r="B151">
         <v>45133</v>
       </c>
       <c r="C151">
@@ -3957,14 +3915,14 @@
         <v>54.61</v>
       </c>
       <c r="G151" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>16</v>
-      </c>
-      <c r="B152" s="2">
+        <v>15</v>
+      </c>
+      <c r="B152">
         <v>45133</v>
       </c>
       <c r="C152">
@@ -3980,14 +3938,14 @@
         <v>55.42</v>
       </c>
       <c r="G152" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>16</v>
-      </c>
-      <c r="B153" s="2">
+        <v>15</v>
+      </c>
+      <c r="B153">
         <v>45133</v>
       </c>
       <c r="C153">
@@ -4003,14 +3961,14 @@
         <v>55.42</v>
       </c>
       <c r="G153" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>16</v>
-      </c>
-      <c r="B154" s="2">
+        <v>15</v>
+      </c>
+      <c r="B154">
         <v>45133</v>
       </c>
       <c r="C154">
@@ -4026,14 +3984,14 @@
         <v>54.88</v>
       </c>
       <c r="G154" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>16</v>
-      </c>
-      <c r="B155" s="2">
+        <v>15</v>
+      </c>
+      <c r="B155">
         <v>45133</v>
       </c>
       <c r="C155">
@@ -4049,14 +4007,14 @@
         <v>54.35</v>
       </c>
       <c r="G155" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>16</v>
-      </c>
-      <c r="B156" s="2">
+        <v>15</v>
+      </c>
+      <c r="B156">
         <v>45133</v>
       </c>
       <c r="C156">
@@ -4072,14 +4030,14 @@
         <v>54.35</v>
       </c>
       <c r="G156" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>16</v>
-      </c>
-      <c r="B157" s="2">
+        <v>15</v>
+      </c>
+      <c r="B157">
         <v>45133</v>
       </c>
       <c r="C157">
@@ -4095,14 +4053,14 @@
         <v>54.09</v>
       </c>
       <c r="G157" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>16</v>
-      </c>
-      <c r="B158" s="2">
+        <v>15</v>
+      </c>
+      <c r="B158">
         <v>45133</v>
       </c>
       <c r="C158">
@@ -4118,14 +4076,14 @@
         <v>54.35</v>
       </c>
       <c r="G158" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>16</v>
-      </c>
-      <c r="B159" s="2">
+        <v>15</v>
+      </c>
+      <c r="B159">
         <v>45133</v>
       </c>
       <c r="C159">
@@ -4141,14 +4099,14 @@
         <v>53.57</v>
       </c>
       <c r="G159" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>16</v>
-      </c>
-      <c r="B160" s="2">
+        <v>15</v>
+      </c>
+      <c r="B160">
         <v>45133</v>
       </c>
       <c r="C160">
@@ -4164,14 +4122,14 @@
         <v>54.09</v>
       </c>
       <c r="G160" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>16</v>
-      </c>
-      <c r="B161" s="2">
+        <v>15</v>
+      </c>
+      <c r="B161">
         <v>45133</v>
       </c>
       <c r="C161">
@@ -4187,14 +4145,14 @@
         <v>53.83</v>
       </c>
       <c r="G161" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>16</v>
-      </c>
-      <c r="B162" s="2">
+        <v>15</v>
+      </c>
+      <c r="B162">
         <v>45133</v>
       </c>
       <c r="C162">
@@ -4210,14 +4168,14 @@
         <v>52.08</v>
       </c>
       <c r="G162" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>16</v>
-      </c>
-      <c r="B163" s="2">
+        <v>15</v>
+      </c>
+      <c r="B163">
         <v>45133</v>
       </c>
       <c r="C163">
@@ -4233,14 +4191,14 @@
         <v>56.25</v>
       </c>
       <c r="G163" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>16</v>
-      </c>
-      <c r="B164" s="2">
+        <v>15</v>
+      </c>
+      <c r="B164">
         <v>45133</v>
       </c>
       <c r="C164">
@@ -4256,14 +4214,14 @@
         <v>54.35</v>
       </c>
       <c r="G164" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>16</v>
-      </c>
-      <c r="B165" s="2">
+        <v>15</v>
+      </c>
+      <c r="B165">
         <v>45133</v>
       </c>
       <c r="C165">
@@ -4279,14 +4237,14 @@
         <v>54.35</v>
       </c>
       <c r="G165" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>16</v>
-      </c>
-      <c r="B166" s="2">
+        <v>15</v>
+      </c>
+      <c r="B166">
         <v>45133</v>
       </c>
       <c r="C166">
@@ -4302,14 +4260,14 @@
         <v>54.09</v>
       </c>
       <c r="G166" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>16</v>
-      </c>
-      <c r="B167" s="2">
+        <v>15</v>
+      </c>
+      <c r="B167">
         <v>45133</v>
       </c>
       <c r="C167">
@@ -4325,14 +4283,14 @@
         <v>54.09</v>
       </c>
       <c r="G167" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>16</v>
-      </c>
-      <c r="B168" s="2">
+        <v>15</v>
+      </c>
+      <c r="B168">
         <v>45133</v>
       </c>
       <c r="C168">
@@ -4348,14 +4306,14 @@
         <v>54.35</v>
       </c>
       <c r="G168" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>16</v>
-      </c>
-      <c r="B169" s="2">
+        <v>15</v>
+      </c>
+      <c r="B169">
         <v>45133</v>
       </c>
       <c r="C169">
@@ -4371,14 +4329,14 @@
         <v>54.88</v>
       </c>
       <c r="G169" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>16</v>
-      </c>
-      <c r="B170" s="2">
+        <v>15</v>
+      </c>
+      <c r="B170">
         <v>45133</v>
       </c>
       <c r="C170">
@@ -4394,14 +4352,14 @@
         <v>54.09</v>
       </c>
       <c r="G170" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>16</v>
-      </c>
-      <c r="B171" s="2">
+        <v>15</v>
+      </c>
+      <c r="B171">
         <v>45133</v>
       </c>
       <c r="C171">
@@ -4417,14 +4375,14 @@
         <v>54.09</v>
       </c>
       <c r="G171" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>16</v>
-      </c>
-      <c r="B172" s="2">
+        <v>15</v>
+      </c>
+      <c r="B172">
         <v>45133</v>
       </c>
       <c r="C172">
@@ -4440,14 +4398,14 @@
         <v>54.09</v>
       </c>
       <c r="G172" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>16</v>
-      </c>
-      <c r="B173" s="2">
+        <v>15</v>
+      </c>
+      <c r="B173">
         <v>45133</v>
       </c>
       <c r="C173">
@@ -4463,14 +4421,14 @@
         <v>53.57</v>
       </c>
       <c r="G173" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>16</v>
-      </c>
-      <c r="B174" s="2">
+        <v>15</v>
+      </c>
+      <c r="B174">
         <v>45133</v>
       </c>
       <c r="C174">
@@ -4486,14 +4444,14 @@
         <v>54.09</v>
       </c>
       <c r="G174" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>16</v>
-      </c>
-      <c r="B175" s="2">
+        <v>15</v>
+      </c>
+      <c r="B175">
         <v>45133</v>
       </c>
       <c r="C175">
@@ -4509,14 +4467,14 @@
         <v>53.07</v>
       </c>
       <c r="G175" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>16</v>
-      </c>
-      <c r="B176" s="2">
+        <v>15</v>
+      </c>
+      <c r="B176">
         <v>45133</v>
       </c>
       <c r="C176">
@@ -4532,14 +4490,14 @@
         <v>53.32</v>
       </c>
       <c r="G176" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>16</v>
-      </c>
-      <c r="B177" s="2">
+        <v>15</v>
+      </c>
+      <c r="B177">
         <v>45133</v>
       </c>
       <c r="C177">
@@ -4555,14 +4513,14 @@
         <v>53.32</v>
       </c>
       <c r="G177" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>16</v>
-      </c>
-      <c r="B178" s="2">
+        <v>15</v>
+      </c>
+      <c r="B178">
         <v>45133</v>
       </c>
       <c r="C178">
@@ -4578,14 +4536,14 @@
         <v>52.33</v>
       </c>
       <c r="G178" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>16</v>
-      </c>
-      <c r="B179" s="2">
+        <v>15</v>
+      </c>
+      <c r="B179">
         <v>45133</v>
       </c>
       <c r="C179">
@@ -4601,14 +4559,14 @@
         <v>51.84</v>
       </c>
       <c r="G179" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>16</v>
-      </c>
-      <c r="B180" s="2">
+        <v>15</v>
+      </c>
+      <c r="B180">
         <v>45133</v>
       </c>
       <c r="C180">
@@ -4624,14 +4582,14 @@
         <v>52.08</v>
       </c>
       <c r="G180" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>16</v>
-      </c>
-      <c r="B181" s="2">
+        <v>15</v>
+      </c>
+      <c r="B181">
         <v>45133</v>
       </c>
       <c r="C181">
@@ -4647,14 +4605,14 @@
         <v>52.33</v>
       </c>
       <c r="G181" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>16</v>
-      </c>
-      <c r="B182" s="2">
+        <v>15</v>
+      </c>
+      <c r="B182">
         <v>45133</v>
       </c>
       <c r="C182">
@@ -4670,14 +4628,14 @@
         <v>52.08</v>
       </c>
       <c r="G182" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>16</v>
-      </c>
-      <c r="B183" s="2">
+        <v>15</v>
+      </c>
+      <c r="B183">
         <v>45133</v>
       </c>
       <c r="C183">
@@ -4693,14 +4651,14 @@
         <v>51.61</v>
       </c>
       <c r="G183" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>16</v>
-      </c>
-      <c r="B184" s="2">
+        <v>15</v>
+      </c>
+      <c r="B184">
         <v>45133</v>
       </c>
       <c r="C184">
@@ -4716,14 +4674,14 @@
         <v>52.33</v>
       </c>
       <c r="G184" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>16</v>
-      </c>
-      <c r="B185" s="2">
+        <v>15</v>
+      </c>
+      <c r="B185">
         <v>45133</v>
       </c>
       <c r="C185">
@@ -4739,14 +4697,14 @@
         <v>51.84</v>
       </c>
       <c r="G185" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>16</v>
-      </c>
-      <c r="B186" s="2">
+        <v>15</v>
+      </c>
+      <c r="B186">
         <v>45133</v>
       </c>
       <c r="C186">
@@ -4762,14 +4720,14 @@
         <v>51.61</v>
       </c>
       <c r="G186" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>16</v>
-      </c>
-      <c r="B187" s="2">
+        <v>15</v>
+      </c>
+      <c r="B187">
         <v>45133</v>
       </c>
       <c r="C187">
@@ -4785,14 +4743,14 @@
         <v>51.61</v>
       </c>
       <c r="G187" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>16</v>
-      </c>
-      <c r="B188" s="2">
+        <v>15</v>
+      </c>
+      <c r="B188">
         <v>45133</v>
       </c>
       <c r="C188">
@@ -4808,14 +4766,14 @@
         <v>51.61</v>
       </c>
       <c r="G188" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>16</v>
-      </c>
-      <c r="B189" s="2">
+        <v>15</v>
+      </c>
+      <c r="B189">
         <v>45133</v>
       </c>
       <c r="C189">
@@ -4831,14 +4789,14 @@
         <v>51.14</v>
       </c>
       <c r="G189" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>16</v>
-      </c>
-      <c r="B190" s="2">
+        <v>15</v>
+      </c>
+      <c r="B190">
         <v>45133</v>
       </c>
       <c r="C190">
@@ -4854,14 +4812,14 @@
         <v>51.37</v>
       </c>
       <c r="G190" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>16</v>
-      </c>
-      <c r="B191" s="2">
+        <v>15</v>
+      </c>
+      <c r="B191">
         <v>45133</v>
       </c>
       <c r="C191">
@@ -4877,14 +4835,14 @@
         <v>51.37</v>
       </c>
       <c r="G191" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>16</v>
-      </c>
-      <c r="B192" s="2">
+        <v>15</v>
+      </c>
+      <c r="B192">
         <v>45133</v>
       </c>
       <c r="C192">
@@ -4900,14 +4858,14 @@
         <v>51.37</v>
       </c>
       <c r="G192" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>16</v>
-      </c>
-      <c r="B193" s="2">
+        <v>15</v>
+      </c>
+      <c r="B193">
         <v>45133</v>
       </c>
       <c r="C193">
@@ -4923,20 +4881,2969 @@
         <v>51.14</v>
       </c>
       <c r="G193" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>17</v>
+      </c>
+      <c r="C194">
+        <v>62.5</v>
+      </c>
+      <c r="D194">
+        <v>9.4999990000000007</v>
+      </c>
+      <c r="E194">
+        <v>9.499998999999999</v>
+      </c>
+      <c r="F194">
+        <v>23.684213020000001</v>
+      </c>
+      <c r="G194" t="s">
+        <v>9</v>
+      </c>
+      <c r="I194" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>17</v>
+      </c>
+      <c r="C195">
+        <v>125</v>
+      </c>
+      <c r="D195">
+        <v>14.704739999999999</v>
+      </c>
+      <c r="E195">
+        <v>5.2047410000000021</v>
+      </c>
+      <c r="F195">
+        <v>43.229816820000003</v>
+      </c>
+      <c r="G195" t="s">
+        <v>9</v>
+      </c>
+      <c r="I195" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>17</v>
+      </c>
+      <c r="C196">
+        <v>187.5</v>
+      </c>
+      <c r="D196">
+        <v>19.204737000000002</v>
+      </c>
+      <c r="E196">
+        <v>4.4999970000000005</v>
+      </c>
+      <c r="F196">
+        <v>50.000033330000001</v>
+      </c>
+      <c r="G196" t="s">
+        <v>9</v>
+      </c>
+      <c r="I196" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>17</v>
+      </c>
+      <c r="C197">
+        <v>250</v>
+      </c>
+      <c r="D197">
+        <v>23.504731</v>
+      </c>
+      <c r="E197">
+        <v>4.2999940000000016</v>
+      </c>
+      <c r="F197">
+        <v>52.325654409999999</v>
+      </c>
+      <c r="G197" t="s">
+        <v>9</v>
+      </c>
+      <c r="I197" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>17</v>
+      </c>
+      <c r="C198">
+        <v>312.5</v>
+      </c>
+      <c r="D198">
+        <v>27.604727</v>
+      </c>
+      <c r="E198">
+        <v>4.0999959999999973</v>
+      </c>
+      <c r="F198">
+        <v>54.878102320000004</v>
+      </c>
+      <c r="G198" t="s">
+        <v>9</v>
+      </c>
+      <c r="I198" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>17</v>
+      </c>
+      <c r="C199">
+        <v>375</v>
+      </c>
+      <c r="D199">
+        <v>31.644724</v>
+      </c>
+      <c r="E199">
+        <v>4.0399969999999996</v>
+      </c>
+      <c r="F199">
+        <v>55.693110660000002</v>
+      </c>
+      <c r="G199" t="s">
+        <v>9</v>
+      </c>
+      <c r="I199" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
+        <v>17</v>
+      </c>
+      <c r="C200">
+        <v>437.5</v>
+      </c>
+      <c r="D200">
+        <v>35.64472</v>
+      </c>
+      <c r="E200">
+        <v>3.999996000000003</v>
+      </c>
+      <c r="F200">
+        <v>56.25005625</v>
+      </c>
+      <c r="G200" t="s">
+        <v>9</v>
+      </c>
+      <c r="I200" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
+        <v>17</v>
+      </c>
+      <c r="C201">
+        <v>500</v>
+      </c>
+      <c r="D201">
+        <v>39.624720000000003</v>
+      </c>
+      <c r="E201">
+        <v>3.9799999999999969</v>
+      </c>
+      <c r="F201">
+        <v>56.532663319999997</v>
+      </c>
+      <c r="G201" t="s">
+        <v>9</v>
+      </c>
+      <c r="I201" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>17</v>
+      </c>
+      <c r="C202">
+        <v>562.5</v>
+      </c>
+      <c r="D202">
+        <v>43.604719000000003</v>
+      </c>
+      <c r="E202">
+        <v>3.9799989999999994</v>
+      </c>
+      <c r="F202">
+        <v>56.53267752</v>
+      </c>
+      <c r="G202" t="s">
+        <v>9</v>
+      </c>
+      <c r="I202" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
+        <v>17</v>
+      </c>
+      <c r="C203">
+        <v>625</v>
+      </c>
+      <c r="D203">
+        <v>47.584718000000002</v>
+      </c>
+      <c r="E203">
+        <v>3.9799989999999994</v>
+      </c>
+      <c r="F203">
+        <v>56.53267752</v>
+      </c>
+      <c r="G203" t="s">
+        <v>9</v>
+      </c>
+      <c r="I203" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>17</v>
+      </c>
+      <c r="C204">
+        <v>687.5</v>
+      </c>
+      <c r="D204">
+        <v>51.584715000000003</v>
+      </c>
+      <c r="E204">
+        <v>3.9999970000000005</v>
+      </c>
+      <c r="F204">
+        <v>56.250042190000002</v>
+      </c>
+      <c r="G204" t="s">
+        <v>9</v>
+      </c>
+      <c r="I204" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>17</v>
+      </c>
+      <c r="C205">
+        <v>750</v>
+      </c>
+      <c r="D205">
+        <v>55.604714999999999</v>
+      </c>
+      <c r="E205">
+        <v>4.0200000000000031</v>
+      </c>
+      <c r="F205">
+        <v>55.970149249999999</v>
+      </c>
+      <c r="G205" t="s">
+        <v>9</v>
+      </c>
+      <c r="I205" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>17</v>
+      </c>
+      <c r="C206">
+        <v>812.5</v>
+      </c>
+      <c r="D206">
+        <v>59.624715000000002</v>
+      </c>
+      <c r="E206">
+        <v>4.019999999999996</v>
+      </c>
+      <c r="F206">
+        <v>55.970149249999999</v>
+      </c>
+      <c r="G206" t="s">
+        <v>9</v>
+      </c>
+      <c r="I206" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>17</v>
+      </c>
+      <c r="C207">
+        <v>875</v>
+      </c>
+      <c r="D207">
+        <v>63.664713999999996</v>
+      </c>
+      <c r="E207">
+        <v>4.0399990000000088</v>
+      </c>
+      <c r="F207">
+        <v>55.693083090000002</v>
+      </c>
+      <c r="G207" t="s">
+        <v>9</v>
+      </c>
+      <c r="I207" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>17</v>
+      </c>
+      <c r="C208">
+        <v>937.5</v>
+      </c>
+      <c r="D208">
+        <v>67.744713000000004</v>
+      </c>
+      <c r="E208">
+        <v>4.0799989999999866</v>
+      </c>
+      <c r="F208">
+        <v>55.147072340000001</v>
+      </c>
+      <c r="G208" t="s">
+        <v>9</v>
+      </c>
+      <c r="I208" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>17</v>
+      </c>
+      <c r="C209">
+        <v>1000</v>
+      </c>
+      <c r="D209">
+        <v>71.824712000000005</v>
+      </c>
+      <c r="E209">
+        <v>4.0799990000000008</v>
+      </c>
+      <c r="F209">
+        <v>55.147072340000001</v>
+      </c>
+      <c r="G209" t="s">
+        <v>9</v>
+      </c>
+      <c r="I209" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>17</v>
+      </c>
+      <c r="C210">
+        <v>1062.5</v>
+      </c>
+      <c r="D210">
+        <v>75.904712000000004</v>
+      </c>
+      <c r="E210">
+        <v>4.0800000000000125</v>
+      </c>
+      <c r="F210">
+        <v>55.147058819999998</v>
+      </c>
+      <c r="G210" t="s">
+        <v>9</v>
+      </c>
+      <c r="I210" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>17</v>
+      </c>
+      <c r="C211">
+        <v>1125</v>
+      </c>
+      <c r="D211">
+        <v>79.984712000000002</v>
+      </c>
+      <c r="E211">
+        <v>4.0799999999999983</v>
+      </c>
+      <c r="F211">
+        <v>55.147058819999998</v>
+      </c>
+      <c r="G211" t="s">
+        <v>9</v>
+      </c>
+      <c r="I211" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>17</v>
+      </c>
+      <c r="C212">
+        <v>1187.5</v>
+      </c>
+      <c r="D212">
+        <v>84.044712000000004</v>
+      </c>
+      <c r="E212">
+        <v>4.0599999999999881</v>
+      </c>
+      <c r="F212">
+        <v>55.418719209999999</v>
+      </c>
+      <c r="G212" t="s">
+        <v>9</v>
+      </c>
+      <c r="I212" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>17</v>
+      </c>
+      <c r="C213">
+        <v>1250</v>
+      </c>
+      <c r="D213">
+        <v>88.104710999999995</v>
+      </c>
+      <c r="E213">
+        <v>4.0599990000000048</v>
+      </c>
+      <c r="F213">
+        <v>55.418732859999999</v>
+      </c>
+      <c r="G213" t="s">
+        <v>9</v>
+      </c>
+      <c r="I213" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>17</v>
+      </c>
+      <c r="C214">
+        <v>1312.5</v>
+      </c>
+      <c r="D214">
+        <v>92.184710999999993</v>
+      </c>
+      <c r="E214">
+        <v>4.0799999999999983</v>
+      </c>
+      <c r="F214">
+        <v>55.147058819999998</v>
+      </c>
+      <c r="G214" t="s">
+        <v>9</v>
+      </c>
+      <c r="I214" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>17</v>
+      </c>
+      <c r="C215">
+        <v>1375</v>
+      </c>
+      <c r="D215">
+        <v>96.264711000000005</v>
+      </c>
+      <c r="E215">
+        <v>4.0799999999999983</v>
+      </c>
+      <c r="F215">
+        <v>55.147058819999998</v>
+      </c>
+      <c r="G215" t="s">
+        <v>9</v>
+      </c>
+      <c r="I215" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>17</v>
+      </c>
+      <c r="C216">
+        <v>1437.5</v>
+      </c>
+      <c r="D216">
+        <v>100.364709</v>
+      </c>
+      <c r="E216">
+        <v>4.0999979999999994</v>
+      </c>
+      <c r="F216">
+        <v>54.878075549999998</v>
+      </c>
+      <c r="G216" t="s">
+        <v>9</v>
+      </c>
+      <c r="I216" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>17</v>
+      </c>
+      <c r="C217">
+        <v>1500</v>
+      </c>
+      <c r="D217">
+        <v>104.464708</v>
+      </c>
+      <c r="E217">
+        <v>4.0999990000000111</v>
+      </c>
+      <c r="F217">
+        <v>54.87806217</v>
+      </c>
+      <c r="G217" t="s">
+        <v>9</v>
+      </c>
+      <c r="I217" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>17</v>
+      </c>
+      <c r="C218">
+        <v>1562.5</v>
+      </c>
+      <c r="D218">
+        <v>108.544708</v>
+      </c>
+      <c r="E218">
+        <v>4.0799999999999983</v>
+      </c>
+      <c r="F218">
+        <v>55.147058819999998</v>
+      </c>
+      <c r="G218" t="s">
+        <v>9</v>
+      </c>
+      <c r="I218" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>17</v>
+      </c>
+      <c r="C219">
+        <v>1625</v>
+      </c>
+      <c r="D219">
+        <v>112.64470799999999</v>
+      </c>
+      <c r="E219">
+        <v>4.0999999999999943</v>
+      </c>
+      <c r="F219">
+        <v>54.87804878</v>
+      </c>
+      <c r="G219" t="s">
+        <v>9</v>
+      </c>
+      <c r="I219" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>17</v>
+      </c>
+      <c r="C220">
+        <v>1687.5</v>
+      </c>
+      <c r="D220">
+        <v>116.744705</v>
+      </c>
+      <c r="E220">
+        <v>4.0999970000000019</v>
+      </c>
+      <c r="F220">
+        <v>54.878088939999998</v>
+      </c>
+      <c r="G220" t="s">
+        <v>9</v>
+      </c>
+      <c r="I220" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>17</v>
+      </c>
+      <c r="C221">
+        <v>1750</v>
+      </c>
+      <c r="D221">
+        <v>120.884704</v>
+      </c>
+      <c r="E221">
+        <v>4.1399989999999889</v>
+      </c>
+      <c r="F221">
+        <v>54.347839209999997</v>
+      </c>
+      <c r="G221" t="s">
+        <v>9</v>
+      </c>
+      <c r="I221" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>17</v>
+      </c>
+      <c r="C222">
+        <v>1812.5</v>
+      </c>
+      <c r="D222">
+        <v>125.00470300000001</v>
+      </c>
+      <c r="E222">
+        <v>4.1199990000000071</v>
+      </c>
+      <c r="F222">
+        <v>54.611663739999997</v>
+      </c>
+      <c r="G222" t="s">
+        <v>9</v>
+      </c>
+      <c r="I222" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>17</v>
+      </c>
+      <c r="C223">
+        <v>1875</v>
+      </c>
+      <c r="D223">
+        <v>129.14470299999999</v>
+      </c>
+      <c r="E223">
+        <v>4.1400000000000148</v>
+      </c>
+      <c r="F223">
+        <v>54.347826089999998</v>
+      </c>
+      <c r="G223" t="s">
+        <v>9</v>
+      </c>
+      <c r="I223" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>17</v>
+      </c>
+      <c r="C224">
+        <v>1937.5</v>
+      </c>
+      <c r="D224">
+        <v>133.28470300000001</v>
+      </c>
+      <c r="E224">
+        <v>4.1399999999999864</v>
+      </c>
+      <c r="F224">
+        <v>54.347826089999998</v>
+      </c>
+      <c r="G224" t="s">
+        <v>9</v>
+      </c>
+      <c r="I224" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>17</v>
+      </c>
+      <c r="C225">
+        <v>2000</v>
+      </c>
+      <c r="D225">
+        <v>137.424702</v>
+      </c>
+      <c r="E225">
+        <v>4.1399990000000173</v>
+      </c>
+      <c r="F225">
+        <v>54.347839209999997</v>
+      </c>
+      <c r="G225" t="s">
+        <v>9</v>
+      </c>
+      <c r="I225" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>17</v>
+      </c>
+      <c r="C226">
+        <v>2062.5</v>
+      </c>
+      <c r="D226">
+        <v>141.56470200000001</v>
+      </c>
+      <c r="E226">
+        <v>4.1399999999999864</v>
+      </c>
+      <c r="F226">
+        <v>54.347826089999998</v>
+      </c>
+      <c r="G226" t="s">
+        <v>9</v>
+      </c>
+      <c r="I226" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>17</v>
+      </c>
+      <c r="C227">
+        <v>2125</v>
+      </c>
+      <c r="D227">
+        <v>145.704702</v>
+      </c>
+      <c r="E227">
+        <v>4.1399999999999864</v>
+      </c>
+      <c r="F227">
+        <v>54.347826089999998</v>
+      </c>
+      <c r="G227" t="s">
+        <v>9</v>
+      </c>
+      <c r="I227" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>17</v>
+      </c>
+      <c r="C228">
+        <v>2187.5</v>
+      </c>
+      <c r="D228">
+        <v>149.864701</v>
+      </c>
+      <c r="E228">
+        <v>4.1599989999999991</v>
+      </c>
+      <c r="F228">
+        <v>54.086551460000003</v>
+      </c>
+      <c r="G228" t="s">
+        <v>9</v>
+      </c>
+      <c r="I228" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>17</v>
+      </c>
+      <c r="C229">
+        <v>2250</v>
+      </c>
+      <c r="D229">
+        <v>154.0247</v>
+      </c>
+      <c r="E229">
+        <v>4.1599990000000275</v>
+      </c>
+      <c r="F229">
+        <v>54.086551460000003</v>
+      </c>
+      <c r="G229" t="s">
+        <v>9</v>
+      </c>
+      <c r="I229" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>17</v>
+      </c>
+      <c r="C230">
+        <v>2312.5</v>
+      </c>
+      <c r="D230">
+        <v>158.18469999999999</v>
+      </c>
+      <c r="E230">
+        <v>4.1599999999999966</v>
+      </c>
+      <c r="F230">
+        <v>54.08653846</v>
+      </c>
+      <c r="G230" t="s">
+        <v>9</v>
+      </c>
+      <c r="I230" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>17</v>
+      </c>
+      <c r="C231">
+        <v>2375</v>
+      </c>
+      <c r="D231">
+        <v>162.32470000000001</v>
+      </c>
+      <c r="E231">
+        <v>4.1399999999999864</v>
+      </c>
+      <c r="F231">
+        <v>54.347826089999998</v>
+      </c>
+      <c r="G231" t="s">
+        <v>9</v>
+      </c>
+      <c r="I231" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>17</v>
+      </c>
+      <c r="C232">
+        <v>2437.5</v>
+      </c>
+      <c r="D232">
+        <v>166.464699</v>
+      </c>
+      <c r="E232">
+        <v>4.1399990000000173</v>
+      </c>
+      <c r="F232">
+        <v>54.347839209999997</v>
+      </c>
+      <c r="G232" t="s">
+        <v>9</v>
+      </c>
+      <c r="I232" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>17</v>
+      </c>
+      <c r="C233">
+        <v>2500</v>
+      </c>
+      <c r="D233">
+        <v>170.60469900000001</v>
+      </c>
+      <c r="E233">
+        <v>4.1399999999999864</v>
+      </c>
+      <c r="F233">
+        <v>54.347826089999998</v>
+      </c>
+      <c r="G233" t="s">
+        <v>9</v>
+      </c>
+      <c r="I233" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>17</v>
+      </c>
+      <c r="C234">
+        <v>2562.5</v>
+      </c>
+      <c r="D234">
+        <v>174.76469900000001</v>
+      </c>
+      <c r="E234">
+        <v>4.1599999999999966</v>
+      </c>
+      <c r="F234">
+        <v>54.08653846</v>
+      </c>
+      <c r="G234" t="s">
+        <v>9</v>
+      </c>
+      <c r="I234" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>17</v>
+      </c>
+      <c r="C235">
+        <v>2625</v>
+      </c>
+      <c r="D235">
+        <v>178.94469900000001</v>
+      </c>
+      <c r="E235">
+        <v>4.1800000000000068</v>
+      </c>
+      <c r="F235">
+        <v>53.827751200000002</v>
+      </c>
+      <c r="G235" t="s">
+        <v>9</v>
+      </c>
+      <c r="I235" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>17</v>
+      </c>
+      <c r="C236">
+        <v>2687.5</v>
+      </c>
+      <c r="D236">
+        <v>183.12469899999999</v>
+      </c>
+      <c r="E236">
+        <v>4.1800000000000068</v>
+      </c>
+      <c r="F236">
+        <v>53.827751200000002</v>
+      </c>
+      <c r="G236" t="s">
+        <v>9</v>
+      </c>
+      <c r="I236" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>17</v>
+      </c>
+      <c r="C237">
+        <v>2750</v>
+      </c>
+      <c r="D237">
+        <v>187.304699</v>
+      </c>
+      <c r="E237">
+        <v>4.1799999999999784</v>
+      </c>
+      <c r="F237">
+        <v>53.827751200000002</v>
+      </c>
+      <c r="G237" t="s">
+        <v>9</v>
+      </c>
+      <c r="I237" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>17</v>
+      </c>
+      <c r="C238">
+        <v>2812.5</v>
+      </c>
+      <c r="D238">
+        <v>191.48469900000001</v>
+      </c>
+      <c r="E238">
+        <v>4.1800000000000068</v>
+      </c>
+      <c r="F238">
+        <v>53.827751200000002</v>
+      </c>
+      <c r="G238" t="s">
+        <v>9</v>
+      </c>
+      <c r="I238" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>17</v>
+      </c>
+      <c r="C239">
+        <v>2875</v>
+      </c>
+      <c r="D239">
+        <v>195.68469899999999</v>
+      </c>
+      <c r="E239">
+        <v>4.2000000000000171</v>
+      </c>
+      <c r="F239">
+        <v>53.571428570000002</v>
+      </c>
+      <c r="G239" t="s">
+        <v>9</v>
+      </c>
+      <c r="I239" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>17</v>
+      </c>
+      <c r="C240">
+        <v>2937.5</v>
+      </c>
+      <c r="D240">
+        <v>199.88469900000001</v>
+      </c>
+      <c r="E240">
+        <v>4.1999999999999886</v>
+      </c>
+      <c r="F240">
+        <v>53.571428570000002</v>
+      </c>
+      <c r="G240" t="s">
+        <v>9</v>
+      </c>
+      <c r="I240" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>17</v>
+      </c>
+      <c r="C241">
+        <v>3000</v>
+      </c>
+      <c r="D241">
+        <v>204.084699</v>
+      </c>
+      <c r="E241">
+        <v>4.1999999999999886</v>
+      </c>
+      <c r="F241">
+        <v>53.571428570000002</v>
+      </c>
+      <c r="G241" t="s">
+        <v>9</v>
+      </c>
+      <c r="I241" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>17</v>
+      </c>
+      <c r="C242">
+        <v>3062.5</v>
+      </c>
+      <c r="D242">
+        <v>208.28469799999999</v>
+      </c>
+      <c r="E242">
+        <v>4.1999990000000196</v>
+      </c>
+      <c r="F242">
+        <v>53.571441329999999</v>
+      </c>
+      <c r="G242" t="s">
+        <v>9</v>
+      </c>
+      <c r="I242" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>17</v>
+      </c>
+      <c r="C243">
+        <v>3125</v>
+      </c>
+      <c r="D243">
+        <v>212.48469800000001</v>
+      </c>
+      <c r="E243">
+        <v>4.1999999999999886</v>
+      </c>
+      <c r="F243">
+        <v>53.571428570000002</v>
+      </c>
+      <c r="G243" t="s">
+        <v>9</v>
+      </c>
+      <c r="I243" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>17</v>
+      </c>
+      <c r="C244">
+        <v>3187.5</v>
+      </c>
+      <c r="D244">
+        <v>216.70469800000001</v>
+      </c>
+      <c r="E244">
+        <v>4.2199999999999989</v>
+      </c>
+      <c r="F244">
+        <v>53.317535550000002</v>
+      </c>
+      <c r="G244" t="s">
+        <v>9</v>
+      </c>
+      <c r="I244" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>17</v>
+      </c>
+      <c r="C245">
+        <v>3250</v>
+      </c>
+      <c r="D245">
+        <v>220.964698</v>
+      </c>
+      <c r="E245">
+        <v>4.2599999999999909</v>
+      </c>
+      <c r="F245">
+        <v>52.81690141</v>
+      </c>
+      <c r="G245" t="s">
+        <v>9</v>
+      </c>
+      <c r="I245" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>17</v>
+      </c>
+      <c r="C246">
+        <v>3312.5</v>
+      </c>
+      <c r="D246">
+        <v>225.22469699999999</v>
+      </c>
+      <c r="E246">
+        <v>4.2599990000000219</v>
+      </c>
+      <c r="F246">
+        <v>52.816913810000003</v>
+      </c>
+      <c r="G246" t="s">
+        <v>9</v>
+      </c>
+      <c r="I246" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>17</v>
+      </c>
+      <c r="C247">
+        <v>3375</v>
+      </c>
+      <c r="D247">
+        <v>229.48469700000001</v>
+      </c>
+      <c r="E247">
+        <v>4.2599999999999909</v>
+      </c>
+      <c r="F247">
+        <v>52.81690141</v>
+      </c>
+      <c r="G247" t="s">
+        <v>9</v>
+      </c>
+      <c r="I247" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>17</v>
+      </c>
+      <c r="C248">
+        <v>3437.5</v>
+      </c>
+      <c r="D248">
+        <v>233.744697</v>
+      </c>
+      <c r="E248">
+        <v>4.2599999999999909</v>
+      </c>
+      <c r="F248">
+        <v>52.81690141</v>
+      </c>
+      <c r="G248" t="s">
+        <v>9</v>
+      </c>
+      <c r="I248" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>17</v>
+      </c>
+      <c r="C249">
+        <v>3500</v>
+      </c>
+      <c r="D249">
+        <v>238.02469600000001</v>
+      </c>
+      <c r="E249">
+        <v>4.2799990000000037</v>
+      </c>
+      <c r="F249">
+        <v>52.570105740000002</v>
+      </c>
+      <c r="G249" t="s">
+        <v>9</v>
+      </c>
+      <c r="I249" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>17</v>
+      </c>
+      <c r="C250">
+        <v>3562.5</v>
+      </c>
+      <c r="D250">
+        <v>242.32469599999999</v>
+      </c>
+      <c r="E250">
+        <v>4.3000000000000114</v>
+      </c>
+      <c r="F250">
+        <v>52.325581399999997</v>
+      </c>
+      <c r="G250" t="s">
+        <v>9</v>
+      </c>
+      <c r="I250" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>17</v>
+      </c>
+      <c r="C251">
+        <v>3625</v>
+      </c>
+      <c r="D251">
+        <v>246.60469499999999</v>
+      </c>
+      <c r="E251">
+        <v>4.2799989999999752</v>
+      </c>
+      <c r="F251">
+        <v>52.570105740000002</v>
+      </c>
+      <c r="G251" t="s">
+        <v>9</v>
+      </c>
+      <c r="I251" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>17</v>
+      </c>
+      <c r="C252">
+        <v>3687.5</v>
+      </c>
+      <c r="D252">
+        <v>250.884694</v>
+      </c>
+      <c r="E252">
+        <v>4.2799990000000321</v>
+      </c>
+      <c r="F252">
+        <v>52.570105740000002</v>
+      </c>
+      <c r="G252" t="s">
+        <v>9</v>
+      </c>
+      <c r="I252" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>17</v>
+      </c>
+      <c r="C253">
+        <v>3750</v>
+      </c>
+      <c r="D253">
+        <v>255.18469300000001</v>
+      </c>
+      <c r="E253">
+        <v>4.2999990000000139</v>
+      </c>
+      <c r="F253">
+        <v>52.325593560000002</v>
+      </c>
+      <c r="G253" t="s">
+        <v>9</v>
+      </c>
+      <c r="I253" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>17</v>
+      </c>
+      <c r="C254">
+        <v>3812.5</v>
+      </c>
+      <c r="D254">
+        <v>259.50469199999998</v>
+      </c>
+      <c r="E254">
+        <v>4.3199989999999957</v>
+      </c>
+      <c r="F254">
+        <v>52.083345389999998</v>
+      </c>
+      <c r="G254" t="s">
+        <v>9</v>
+      </c>
+      <c r="I254" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>17</v>
+      </c>
+      <c r="C255">
+        <v>3875</v>
+      </c>
+      <c r="D255">
+        <v>263.82469200000003</v>
+      </c>
+      <c r="E255">
+        <v>4.3199999999999932</v>
+      </c>
+      <c r="F255">
+        <v>52.083333330000002</v>
+      </c>
+      <c r="G255" t="s">
+        <v>9</v>
+      </c>
+      <c r="I255" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>17</v>
+      </c>
+      <c r="C256">
+        <v>3937.5</v>
+      </c>
+      <c r="D256">
+        <v>268.18469199999998</v>
+      </c>
+      <c r="E256">
+        <v>4.3599999999999568</v>
+      </c>
+      <c r="F256">
+        <v>51.605504590000002</v>
+      </c>
+      <c r="G256" t="s">
+        <v>9</v>
+      </c>
+      <c r="I256" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>17</v>
+      </c>
+      <c r="C257">
+        <v>4000</v>
+      </c>
+      <c r="D257">
+        <v>272.56469099999998</v>
+      </c>
+      <c r="E257">
+        <v>4.3799990000000548</v>
+      </c>
+      <c r="F257">
+        <v>51.36987474</v>
+      </c>
+      <c r="G257" t="s">
+        <v>9</v>
+      </c>
+      <c r="I257" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>19</v>
+      </c>
+      <c r="C258">
+        <v>62.5</v>
+      </c>
+      <c r="D258">
+        <v>9.3599990000000002</v>
+      </c>
+      <c r="E258">
+        <v>9.3599990000000002</v>
+      </c>
+      <c r="F258">
+        <v>24.03846411</v>
+      </c>
+      <c r="G258" t="s">
+        <v>9</v>
+      </c>
+      <c r="I258" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>19</v>
+      </c>
+      <c r="C259">
+        <v>125</v>
+      </c>
+      <c r="D259">
+        <v>14.561088</v>
+      </c>
+      <c r="E259">
+        <v>5.2010889999999996</v>
+      </c>
+      <c r="F259">
+        <v>43.26017109</v>
+      </c>
+      <c r="G259" t="s">
+        <v>9</v>
+      </c>
+      <c r="I259" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>19</v>
+      </c>
+      <c r="C260">
+        <v>187.5</v>
+      </c>
+      <c r="D260">
+        <v>19.091010000000001</v>
+      </c>
+      <c r="E260">
+        <v>4.5299219999999991</v>
+      </c>
+      <c r="F260">
+        <v>49.669729410000002</v>
+      </c>
+      <c r="G260" t="s">
+        <v>9</v>
+      </c>
+      <c r="I260" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>19</v>
+      </c>
+      <c r="C261">
+        <v>250</v>
+      </c>
+      <c r="D261">
+        <v>23.404933</v>
+      </c>
+      <c r="E261">
+        <v>4.3139229999999991</v>
+      </c>
+      <c r="F261">
+        <v>52.156702840000001</v>
+      </c>
+      <c r="G261" t="s">
+        <v>9</v>
+      </c>
+      <c r="I261" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
+        <v>19</v>
+      </c>
+      <c r="C262">
+        <v>312.5</v>
+      </c>
+      <c r="D262">
+        <v>27.564927999999998</v>
+      </c>
+      <c r="E262">
+        <v>4.1599950000000021</v>
+      </c>
+      <c r="F262">
+        <v>54.08660347</v>
+      </c>
+      <c r="G262" t="s">
+        <v>9</v>
+      </c>
+      <c r="I262" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
+        <v>19</v>
+      </c>
+      <c r="C263">
+        <v>375</v>
+      </c>
+      <c r="D263">
+        <v>31.664926999999999</v>
+      </c>
+      <c r="E263">
+        <v>4.0999990000000039</v>
+      </c>
+      <c r="F263">
+        <v>54.87806217</v>
+      </c>
+      <c r="G263" t="s">
+        <v>9</v>
+      </c>
+      <c r="I263" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
+        <v>19</v>
+      </c>
+      <c r="C264">
+        <v>437.5</v>
+      </c>
+      <c r="D264">
+        <v>35.724924999999999</v>
+      </c>
+      <c r="E264">
+        <v>4.0599979999999931</v>
+      </c>
+      <c r="F264">
+        <v>55.418746509999998</v>
+      </c>
+      <c r="G264" t="s">
+        <v>9</v>
+      </c>
+      <c r="I264" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
+        <v>19</v>
+      </c>
+      <c r="C265">
+        <v>500</v>
+      </c>
+      <c r="D265">
+        <v>39.784923999999997</v>
+      </c>
+      <c r="E265">
+        <v>4.0599990000000048</v>
+      </c>
+      <c r="F265">
+        <v>55.418732859999999</v>
+      </c>
+      <c r="G265" t="s">
+        <v>9</v>
+      </c>
+      <c r="I265" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A266" t="s">
+        <v>19</v>
+      </c>
+      <c r="C266">
+        <v>562.5</v>
+      </c>
+      <c r="D266">
+        <v>43.824922999999998</v>
+      </c>
+      <c r="E266">
+        <v>4.0399990000000017</v>
+      </c>
+      <c r="F266">
+        <v>55.693083090000002</v>
+      </c>
+      <c r="G266" t="s">
+        <v>9</v>
+      </c>
+      <c r="I266" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A267" t="s">
+        <v>19</v>
+      </c>
+      <c r="C267">
+        <v>625</v>
+      </c>
+      <c r="D267">
+        <v>47.864922999999997</v>
+      </c>
+      <c r="E267">
+        <v>4.0399999999999991</v>
+      </c>
+      <c r="F267">
+        <v>55.693069309999998</v>
+      </c>
+      <c r="G267" t="s">
+        <v>9</v>
+      </c>
+      <c r="I267" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A268" t="s">
+        <v>19</v>
+      </c>
+      <c r="C268">
+        <v>687.5</v>
+      </c>
+      <c r="D268">
+        <v>51.884923000000001</v>
+      </c>
+      <c r="E268">
+        <v>4.019999999999996</v>
+      </c>
+      <c r="F268">
+        <v>55.970149249999999</v>
+      </c>
+      <c r="G268" t="s">
+        <v>9</v>
+      </c>
+      <c r="I268" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A269" t="s">
+        <v>19</v>
+      </c>
+      <c r="C269">
+        <v>750</v>
+      </c>
+      <c r="D269">
+        <v>55.924922000000002</v>
+      </c>
+      <c r="E269">
+        <v>4.0399990000000088</v>
+      </c>
+      <c r="F269">
+        <v>55.693083090000002</v>
+      </c>
+      <c r="G269" t="s">
+        <v>9</v>
+      </c>
+      <c r="I269" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A270" t="s">
+        <v>19</v>
+      </c>
+      <c r="C270">
+        <v>812.5</v>
+      </c>
+      <c r="D270">
+        <v>59.984921999999997</v>
+      </c>
+      <c r="E270">
+        <v>4.0599999999999881</v>
+      </c>
+      <c r="F270">
+        <v>55.418719209999999</v>
+      </c>
+      <c r="G270" t="s">
+        <v>9</v>
+      </c>
+      <c r="I270" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A271" t="s">
+        <v>19</v>
+      </c>
+      <c r="C271">
+        <v>875</v>
+      </c>
+      <c r="D271">
+        <v>64.164919999999995</v>
+      </c>
+      <c r="E271">
+        <v>4.1799980000000119</v>
+      </c>
+      <c r="F271">
+        <v>53.827776950000001</v>
+      </c>
+      <c r="G271" t="s">
+        <v>9</v>
+      </c>
+      <c r="I271" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A272" t="s">
+        <v>19</v>
+      </c>
+      <c r="C272">
+        <v>937.5</v>
+      </c>
+      <c r="D272">
+        <v>68.224919999999997</v>
+      </c>
+      <c r="E272">
+        <v>4.0599999999999881</v>
+      </c>
+      <c r="F272">
+        <v>55.418719209999999</v>
+      </c>
+      <c r="G272" t="s">
+        <v>9</v>
+      </c>
+      <c r="I272" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>19</v>
+      </c>
+      <c r="C273">
+        <v>1000</v>
+      </c>
+      <c r="D273">
+        <v>72.304919999999996</v>
+      </c>
+      <c r="E273">
+        <v>4.0799999999999983</v>
+      </c>
+      <c r="F273">
+        <v>55.147058819999998</v>
+      </c>
+      <c r="G273" t="s">
+        <v>9</v>
+      </c>
+      <c r="I273" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>19</v>
+      </c>
+      <c r="C274">
+        <v>1062.5</v>
+      </c>
+      <c r="D274">
+        <v>76.404917999999995</v>
+      </c>
+      <c r="E274">
+        <v>4.0999980000000136</v>
+      </c>
+      <c r="F274">
+        <v>54.878075549999998</v>
+      </c>
+      <c r="G274" t="s">
+        <v>9</v>
+      </c>
+      <c r="I274" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>19</v>
+      </c>
+      <c r="C275">
+        <v>1125</v>
+      </c>
+      <c r="D275">
+        <v>80.524918</v>
+      </c>
+      <c r="E275">
+        <v>4.1199999999999903</v>
+      </c>
+      <c r="F275">
+        <v>54.611650490000002</v>
+      </c>
+      <c r="G275" t="s">
+        <v>9</v>
+      </c>
+      <c r="I275" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>19</v>
+      </c>
+      <c r="C276">
+        <v>1187.5</v>
+      </c>
+      <c r="D276">
+        <v>84.684917999999996</v>
+      </c>
+      <c r="E276">
+        <v>4.1599999999999966</v>
+      </c>
+      <c r="F276">
+        <v>54.08653846</v>
+      </c>
+      <c r="G276" t="s">
+        <v>9</v>
+      </c>
+      <c r="I276" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>19</v>
+      </c>
+      <c r="C277">
+        <v>1250</v>
+      </c>
+      <c r="D277">
+        <v>88.884916000000004</v>
+      </c>
+      <c r="E277">
+        <v>4.1999980000000079</v>
+      </c>
+      <c r="F277">
+        <v>53.571454080000002</v>
+      </c>
+      <c r="G277" t="s">
+        <v>9</v>
+      </c>
+      <c r="I277" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>19</v>
+      </c>
+      <c r="C278">
+        <v>1312.5</v>
+      </c>
+      <c r="D278">
+        <v>93.044916000000001</v>
+      </c>
+      <c r="E278">
+        <v>4.1599999999999966</v>
+      </c>
+      <c r="F278">
+        <v>54.08653846</v>
+      </c>
+      <c r="G278" t="s">
+        <v>9</v>
+      </c>
+      <c r="I278" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>19</v>
+      </c>
+      <c r="C279">
+        <v>1375</v>
+      </c>
+      <c r="D279">
+        <v>97.184916000000001</v>
+      </c>
+      <c r="E279">
+        <v>4.1400000000000006</v>
+      </c>
+      <c r="F279">
+        <v>54.347826089999998</v>
+      </c>
+      <c r="G279" t="s">
+        <v>9</v>
+      </c>
+      <c r="I279" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>19</v>
+      </c>
+      <c r="C280">
+        <v>1437.5</v>
+      </c>
+      <c r="D280">
+        <v>101.364915</v>
+      </c>
+      <c r="E280">
+        <v>4.1799989999999951</v>
+      </c>
+      <c r="F280">
+        <v>53.827764070000001</v>
+      </c>
+      <c r="G280" t="s">
+        <v>9</v>
+      </c>
+      <c r="I280" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>19</v>
+      </c>
+      <c r="C281">
+        <v>1500</v>
+      </c>
+      <c r="D281">
+        <v>105.504914</v>
+      </c>
+      <c r="E281">
+        <v>4.1399990000000031</v>
+      </c>
+      <c r="F281">
+        <v>54.347839209999997</v>
+      </c>
+      <c r="G281" t="s">
+        <v>9</v>
+      </c>
+      <c r="I281" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>19</v>
+      </c>
+      <c r="C282">
+        <v>1562.5</v>
+      </c>
+      <c r="D282">
+        <v>109.664914</v>
+      </c>
+      <c r="E282">
+        <v>4.1599999999999966</v>
+      </c>
+      <c r="F282">
+        <v>54.08653846</v>
+      </c>
+      <c r="G282" t="s">
+        <v>9</v>
+      </c>
+      <c r="I282" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>19</v>
+      </c>
+      <c r="C283">
+        <v>1625</v>
+      </c>
+      <c r="D283">
+        <v>113.84491300000001</v>
+      </c>
+      <c r="E283">
+        <v>4.1799990000000093</v>
+      </c>
+      <c r="F283">
+        <v>53.827764070000001</v>
+      </c>
+      <c r="G283" t="s">
+        <v>9</v>
+      </c>
+      <c r="I283" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>19</v>
+      </c>
+      <c r="C284">
+        <v>1687.5</v>
+      </c>
+      <c r="D284">
+        <v>118.004913</v>
+      </c>
+      <c r="E284">
+        <v>4.1599999999999966</v>
+      </c>
+      <c r="F284">
+        <v>54.08653846</v>
+      </c>
+      <c r="G284" t="s">
+        <v>9</v>
+      </c>
+      <c r="I284" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>19</v>
+      </c>
+      <c r="C285">
+        <v>1750</v>
+      </c>
+      <c r="D285">
+        <v>122.18491299999999</v>
+      </c>
+      <c r="E285">
+        <v>4.1800000000000068</v>
+      </c>
+      <c r="F285">
+        <v>53.827751200000002</v>
+      </c>
+      <c r="G285" t="s">
+        <v>9</v>
+      </c>
+      <c r="I285" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>19</v>
+      </c>
+      <c r="C286">
+        <v>1812.5</v>
+      </c>
+      <c r="D286">
+        <v>126.364913</v>
+      </c>
+      <c r="E286">
+        <v>4.1800000000000068</v>
+      </c>
+      <c r="F286">
+        <v>53.827751200000002</v>
+      </c>
+      <c r="G286" t="s">
+        <v>9</v>
+      </c>
+      <c r="I286" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>19</v>
+      </c>
+      <c r="C287">
+        <v>1875</v>
+      </c>
+      <c r="D287">
+        <v>130.524912</v>
+      </c>
+      <c r="E287">
+        <v>4.1599989999999991</v>
+      </c>
+      <c r="F287">
+        <v>54.086551460000003</v>
+      </c>
+      <c r="G287" t="s">
+        <v>9</v>
+      </c>
+      <c r="I287" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>19</v>
+      </c>
+      <c r="C288">
+        <v>1937.5</v>
+      </c>
+      <c r="D288">
+        <v>134.684912</v>
+      </c>
+      <c r="E288">
+        <v>4.1599999999999966</v>
+      </c>
+      <c r="F288">
+        <v>54.08653846</v>
+      </c>
+      <c r="G288" t="s">
+        <v>9</v>
+      </c>
+      <c r="I288" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>19</v>
+      </c>
+      <c r="C289">
+        <v>2000</v>
+      </c>
+      <c r="D289">
+        <v>138.864912</v>
+      </c>
+      <c r="E289">
+        <v>4.1799999999999784</v>
+      </c>
+      <c r="F289">
+        <v>53.827751200000002</v>
+      </c>
+      <c r="G289" t="s">
+        <v>9</v>
+      </c>
+      <c r="I289" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>19</v>
+      </c>
+      <c r="C290">
+        <v>2062.5</v>
+      </c>
+      <c r="D290">
+        <v>143.024911</v>
+      </c>
+      <c r="E290">
+        <v>4.1599989999999991</v>
+      </c>
+      <c r="F290">
+        <v>54.086551460000003</v>
+      </c>
+      <c r="G290" t="s">
+        <v>9</v>
+      </c>
+      <c r="I290" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>19</v>
+      </c>
+      <c r="C291">
+        <v>2125</v>
+      </c>
+      <c r="D291">
+        <v>147.28491</v>
+      </c>
+      <c r="E291">
+        <v>4.2599990000000219</v>
+      </c>
+      <c r="F291">
+        <v>52.816913810000003</v>
+      </c>
+      <c r="G291" t="s">
+        <v>9</v>
+      </c>
+      <c r="I291" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>19</v>
+      </c>
+      <c r="C292">
+        <v>2187.5</v>
+      </c>
+      <c r="D292">
+        <v>151.46490900000001</v>
+      </c>
+      <c r="E292">
+        <v>4.1799989999999809</v>
+      </c>
+      <c r="F292">
+        <v>53.827764070000001</v>
+      </c>
+      <c r="G292" t="s">
+        <v>9</v>
+      </c>
+      <c r="I292" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>19</v>
+      </c>
+      <c r="C293">
+        <v>2250</v>
+      </c>
+      <c r="D293">
+        <v>155.66490899999999</v>
+      </c>
+      <c r="E293">
+        <v>4.2000000000000171</v>
+      </c>
+      <c r="F293">
+        <v>53.571428570000002</v>
+      </c>
+      <c r="G293" t="s">
+        <v>9</v>
+      </c>
+      <c r="I293" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>19</v>
+      </c>
+      <c r="C294">
+        <v>2312.5</v>
+      </c>
+      <c r="D294">
+        <v>159.86490699999999</v>
+      </c>
+      <c r="E294">
+        <v>4.1999979999999937</v>
+      </c>
+      <c r="F294">
+        <v>53.571454080000002</v>
+      </c>
+      <c r="G294" t="s">
+        <v>9</v>
+      </c>
+      <c r="I294" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>19</v>
+      </c>
+      <c r="C295">
+        <v>2375</v>
+      </c>
+      <c r="D295">
+        <v>164.044906</v>
+      </c>
+      <c r="E295">
+        <v>4.1799990000000093</v>
+      </c>
+      <c r="F295">
+        <v>53.827764070000001</v>
+      </c>
+      <c r="G295" t="s">
+        <v>9</v>
+      </c>
+      <c r="I295" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>19</v>
+      </c>
+      <c r="C296">
+        <v>2437.5</v>
+      </c>
+      <c r="D296">
+        <v>168.24490599999999</v>
+      </c>
+      <c r="E296">
+        <v>4.1999999999999886</v>
+      </c>
+      <c r="F296">
+        <v>53.571428570000002</v>
+      </c>
+      <c r="G296" t="s">
+        <v>9</v>
+      </c>
+      <c r="I296" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>19</v>
+      </c>
+      <c r="C297">
+        <v>2500</v>
+      </c>
+      <c r="D297">
+        <v>172.444906</v>
+      </c>
+      <c r="E297">
+        <v>4.1999999999999886</v>
+      </c>
+      <c r="F297">
+        <v>53.571428570000002</v>
+      </c>
+      <c r="G297" t="s">
+        <v>9</v>
+      </c>
+      <c r="I297" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>19</v>
+      </c>
+      <c r="C298">
+        <v>2562.5</v>
+      </c>
+      <c r="D298">
+        <v>176.62490500000001</v>
+      </c>
+      <c r="E298">
+        <v>4.1799990000000093</v>
+      </c>
+      <c r="F298">
+        <v>53.827764070000001</v>
+      </c>
+      <c r="G298" t="s">
+        <v>9</v>
+      </c>
+      <c r="I298" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>19</v>
+      </c>
+      <c r="C299">
+        <v>2625</v>
+      </c>
+      <c r="D299">
+        <v>180.84490500000001</v>
+      </c>
+      <c r="E299">
+        <v>4.2199999999999989</v>
+      </c>
+      <c r="F299">
+        <v>53.317535550000002</v>
+      </c>
+      <c r="G299" t="s">
+        <v>9</v>
+      </c>
+      <c r="I299" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>19</v>
+      </c>
+      <c r="C300">
+        <v>2687.5</v>
+      </c>
+      <c r="D300">
+        <v>185.044904</v>
+      </c>
+      <c r="E300">
+        <v>4.1999989999999912</v>
+      </c>
+      <c r="F300">
+        <v>53.571441329999999</v>
+      </c>
+      <c r="G300" t="s">
+        <v>9</v>
+      </c>
+      <c r="I300" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>19</v>
+      </c>
+      <c r="C301">
+        <v>2750</v>
+      </c>
+      <c r="D301">
+        <v>189.28490300000001</v>
+      </c>
+      <c r="E301">
+        <v>4.2399990000000116</v>
+      </c>
+      <c r="F301">
+        <v>53.066050250000004</v>
+      </c>
+      <c r="G301" t="s">
+        <v>9</v>
+      </c>
+      <c r="I301" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>19</v>
+      </c>
+      <c r="C302">
+        <v>2812.5</v>
+      </c>
+      <c r="D302">
+        <v>193.50490300000001</v>
+      </c>
+      <c r="E302">
+        <v>4.2199999999999989</v>
+      </c>
+      <c r="F302">
+        <v>53.317535550000002</v>
+      </c>
+      <c r="G302" t="s">
+        <v>9</v>
+      </c>
+      <c r="I302" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>19</v>
+      </c>
+      <c r="C303">
+        <v>2875</v>
+      </c>
+      <c r="D303">
+        <v>197.74490299999999</v>
+      </c>
+      <c r="E303">
+        <v>4.2400000000000091</v>
+      </c>
+      <c r="F303">
+        <v>53.066037739999999</v>
+      </c>
+      <c r="G303" t="s">
+        <v>9</v>
+      </c>
+      <c r="I303" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>19</v>
+      </c>
+      <c r="C304">
+        <v>2937.5</v>
+      </c>
+      <c r="D304">
+        <v>201.984903</v>
+      </c>
+      <c r="E304">
+        <v>4.2399999999999807</v>
+      </c>
+      <c r="F304">
+        <v>53.066037739999999</v>
+      </c>
+      <c r="G304" t="s">
+        <v>9</v>
+      </c>
+      <c r="I304" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>19</v>
+      </c>
+      <c r="C305">
+        <v>3000</v>
+      </c>
+      <c r="D305">
+        <v>206.24490299999999</v>
+      </c>
+      <c r="E305">
+        <v>4.2600000000000193</v>
+      </c>
+      <c r="F305">
+        <v>52.81690141</v>
+      </c>
+      <c r="G305" t="s">
+        <v>9</v>
+      </c>
+      <c r="I305" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>19</v>
+      </c>
+      <c r="C306">
+        <v>3062.5</v>
+      </c>
+      <c r="D306">
+        <v>210.48490200000001</v>
+      </c>
+      <c r="E306">
+        <v>4.2399989999999832</v>
+      </c>
+      <c r="F306">
+        <v>53.066050250000004</v>
+      </c>
+      <c r="G306" t="s">
+        <v>9</v>
+      </c>
+      <c r="I306" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>19</v>
+      </c>
+      <c r="C307">
+        <v>3125</v>
+      </c>
+      <c r="D307">
+        <v>214.744902</v>
+      </c>
+      <c r="E307">
+        <v>4.2600000000000193</v>
+      </c>
+      <c r="F307">
+        <v>52.81690141</v>
+      </c>
+      <c r="G307" t="s">
+        <v>9</v>
+      </c>
+      <c r="I307" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>19</v>
+      </c>
+      <c r="C308">
+        <v>3187.5</v>
+      </c>
+      <c r="D308">
+        <v>219.00490199999999</v>
+      </c>
+      <c r="E308">
+        <v>4.2599999999999909</v>
+      </c>
+      <c r="F308">
+        <v>52.81690141</v>
+      </c>
+      <c r="G308" t="s">
+        <v>9</v>
+      </c>
+      <c r="I308" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>19</v>
+      </c>
+      <c r="C309">
+        <v>3250</v>
+      </c>
+      <c r="D309">
+        <v>223.364902</v>
+      </c>
+      <c r="E309">
+        <v>4.3600000000000136</v>
+      </c>
+      <c r="F309">
+        <v>51.605504590000002</v>
+      </c>
+      <c r="G309" t="s">
+        <v>9</v>
+      </c>
+      <c r="I309" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>19</v>
+      </c>
+      <c r="C310">
+        <v>3312.5</v>
+      </c>
+      <c r="D310">
+        <v>227.644901</v>
+      </c>
+      <c r="E310">
+        <v>4.2799989999999752</v>
+      </c>
+      <c r="F310">
+        <v>52.570105740000002</v>
+      </c>
+      <c r="G310" t="s">
+        <v>9</v>
+      </c>
+      <c r="I310" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>19</v>
+      </c>
+      <c r="C311">
+        <v>3375</v>
+      </c>
+      <c r="D311">
+        <v>231.964901</v>
+      </c>
+      <c r="E311">
+        <v>4.3200000000000216</v>
+      </c>
+      <c r="F311">
+        <v>52.083333330000002</v>
+      </c>
+      <c r="G311" t="s">
+        <v>9</v>
+      </c>
+      <c r="I311" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>19</v>
+      </c>
+      <c r="C312">
+        <v>3437.5</v>
+      </c>
+      <c r="D312">
+        <v>236.28490099999999</v>
+      </c>
+      <c r="E312">
+        <v>4.3199999999999932</v>
+      </c>
+      <c r="F312">
+        <v>52.083333330000002</v>
+      </c>
+      <c r="G312" t="s">
+        <v>9</v>
+      </c>
+      <c r="I312" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>19</v>
+      </c>
+      <c r="C313">
+        <v>3500</v>
+      </c>
+      <c r="D313">
+        <v>240.60490100000001</v>
+      </c>
+      <c r="E313">
+        <v>4.3199999999999932</v>
+      </c>
+      <c r="F313">
+        <v>52.083333330000002</v>
+      </c>
+      <c r="G313" t="s">
+        <v>9</v>
+      </c>
+      <c r="I313" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>19</v>
+      </c>
+      <c r="C314">
+        <v>3562.5</v>
+      </c>
+      <c r="D314">
+        <v>244.92490100000001</v>
+      </c>
+      <c r="E314">
+        <v>4.3199999999999932</v>
+      </c>
+      <c r="F314">
+        <v>52.083333330000002</v>
+      </c>
+      <c r="G314" t="s">
+        <v>9</v>
+      </c>
+      <c r="I314" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>19</v>
+      </c>
+      <c r="C315">
+        <v>3625</v>
+      </c>
+      <c r="D315">
+        <v>249.26489799999999</v>
+      </c>
+      <c r="E315">
+        <v>4.3399970000000394</v>
+      </c>
+      <c r="F315">
+        <v>51.843353810000004</v>
+      </c>
+      <c r="G315" t="s">
+        <v>9</v>
+      </c>
+      <c r="I315" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>19</v>
+      </c>
+      <c r="C316">
+        <v>3687.5</v>
+      </c>
+      <c r="D316">
+        <v>253.624898</v>
+      </c>
+      <c r="E316">
+        <v>4.3599999999999568</v>
+      </c>
+      <c r="F316">
+        <v>51.605504590000002</v>
+      </c>
+      <c r="G316" t="s">
+        <v>9</v>
+      </c>
+      <c r="I316" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>19</v>
+      </c>
+      <c r="C317">
+        <v>3750</v>
+      </c>
+      <c r="D317">
+        <v>258.00489800000003</v>
+      </c>
+      <c r="E317">
+        <v>4.3799999999999955</v>
+      </c>
+      <c r="F317">
+        <v>51.369863010000003</v>
+      </c>
+      <c r="G317" t="s">
+        <v>9</v>
+      </c>
+      <c r="I317" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>19</v>
+      </c>
+      <c r="C318">
+        <v>3812.5</v>
+      </c>
+      <c r="D318">
+        <v>262.40489600000001</v>
+      </c>
+      <c r="E318">
+        <v>4.3999980000000392</v>
+      </c>
+      <c r="F318">
+        <v>51.136386880000003</v>
+      </c>
+      <c r="G318" t="s">
+        <v>9</v>
+      </c>
+      <c r="I318" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>19</v>
+      </c>
+      <c r="C319">
+        <v>3875</v>
+      </c>
+      <c r="D319">
+        <v>266.80489599999999</v>
+      </c>
+      <c r="E319">
+        <v>4.3999999999999773</v>
+      </c>
+      <c r="F319">
+        <v>51.136363639999999</v>
+      </c>
+      <c r="G319" t="s">
+        <v>9</v>
+      </c>
+      <c r="I319" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>19</v>
+      </c>
+      <c r="C320">
+        <v>3937.5</v>
+      </c>
+      <c r="D320">
+        <v>271.20489500000002</v>
+      </c>
+      <c r="E320">
+        <v>4.3999989999999798</v>
+      </c>
+      <c r="F320">
+        <v>51.136375260000001</v>
+      </c>
+      <c r="G320" t="s">
+        <v>9</v>
+      </c>
+      <c r="I320" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>19</v>
+      </c>
+      <c r="C321">
+        <v>4000</v>
+      </c>
+      <c r="D321">
+        <v>275.64489400000002</v>
+      </c>
+      <c r="E321">
+        <v>4.4399990000000003</v>
+      </c>
+      <c r="F321">
+        <v>50.675687089999997</v>
+      </c>
+      <c r="G321" t="s">
+        <v>9</v>
+      </c>
+      <c r="I321" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H193" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H193">
-      <sortCondition descending="1" ref="B1:B193"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:H193" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
-    <hyperlink ref="H146" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="H2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="H50" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="H50" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="H146" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:I193 A194:A321 I194:I321" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{9d5ca952-e4a5-43e6-b17c-c01d313ad135}" enabled="0" method="" siteId="{9d5ca952-e4a5-43e6-b17c-c01d313ad135}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/pages/video_analysis/IP_Master_Women.xlsx
+++ b/pages/video_analysis/IP_Master_Women.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sportnzgroup-my.sharepoint.com/personal/anja_kuys_hpsnz_org_nz/Documents/Desktop/Scripts/CNZPD/pages/video_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_895A468780AFE1A16BBC3229C9E314422081DEFC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A59DB67-EAE6-4B0A-949F-2DAEC2BC9915}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_AFAA658680BF63C7274CA376ADE30E422081DE5F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE9766A7-B058-404D-8BF5-19940765D433}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1620" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="21">
   <si>
     <t>Title</t>
   </si>
@@ -83,6 +83,9 @@
   </si>
   <si>
     <t>26-07-31 Glasgow CWG Shearman Q</t>
+  </si>
+  <si>
+    <t>26-07-31 Glasgow CWG Botha F</t>
   </si>
 </sst>
 </file>
@@ -424,10 +427,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I321"/>
+  <dimension ref="A1:I385"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="41.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -7825,6 +7834,1478 @@
         <v>9</v>
       </c>
       <c r="I321" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>20</v>
+      </c>
+      <c r="C322">
+        <v>62.5</v>
+      </c>
+      <c r="D322">
+        <v>9.5199979999999993</v>
+      </c>
+      <c r="E322">
+        <v>9.5199980000000011</v>
+      </c>
+      <c r="F322">
+        <v>23.63445875</v>
+      </c>
+      <c r="G322" t="s">
+        <v>9</v>
+      </c>
+      <c r="I322" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>20</v>
+      </c>
+      <c r="C323">
+        <v>125</v>
+      </c>
+      <c r="D323">
+        <v>14.732263</v>
+      </c>
+      <c r="E323">
+        <v>5.2122649999999986</v>
+      </c>
+      <c r="F323">
+        <v>43.167413779999997</v>
+      </c>
+      <c r="G323" t="s">
+        <v>9</v>
+      </c>
+      <c r="I323" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>20</v>
+      </c>
+      <c r="C324">
+        <v>187.5</v>
+      </c>
+      <c r="D324">
+        <v>19.240527</v>
+      </c>
+      <c r="E324">
+        <v>4.5082640000000005</v>
+      </c>
+      <c r="F324">
+        <v>49.908346100000003</v>
+      </c>
+      <c r="G324" t="s">
+        <v>9</v>
+      </c>
+      <c r="I324" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>20</v>
+      </c>
+      <c r="C325">
+        <v>250</v>
+      </c>
+      <c r="D325">
+        <v>23.516403</v>
+      </c>
+      <c r="E325">
+        <v>4.2758759999999967</v>
+      </c>
+      <c r="F325">
+        <v>52.620796300000002</v>
+      </c>
+      <c r="G325" t="s">
+        <v>9</v>
+      </c>
+      <c r="I325" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>20</v>
+      </c>
+      <c r="C326">
+        <v>312.5</v>
+      </c>
+      <c r="D326">
+        <v>27.648592000000001</v>
+      </c>
+      <c r="E326">
+        <v>4.1321890000000039</v>
+      </c>
+      <c r="F326">
+        <v>54.450558770000001</v>
+      </c>
+      <c r="G326" t="s">
+        <v>9</v>
+      </c>
+      <c r="I326" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
+        <v>20</v>
+      </c>
+      <c r="C327">
+        <v>375</v>
+      </c>
+      <c r="D327">
+        <v>31.713542</v>
+      </c>
+      <c r="E327">
+        <v>4.0649499999999961</v>
+      </c>
+      <c r="F327">
+        <v>55.351234329999997</v>
+      </c>
+      <c r="G327" t="s">
+        <v>9</v>
+      </c>
+      <c r="I327" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A328" t="s">
+        <v>20</v>
+      </c>
+      <c r="C328">
+        <v>437.5</v>
+      </c>
+      <c r="D328">
+        <v>35.773541999999999</v>
+      </c>
+      <c r="E328">
+        <v>4.0600000000000023</v>
+      </c>
+      <c r="F328">
+        <v>55.418719209999999</v>
+      </c>
+      <c r="G328" t="s">
+        <v>9</v>
+      </c>
+      <c r="I328" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
+        <v>20</v>
+      </c>
+      <c r="C329">
+        <v>500</v>
+      </c>
+      <c r="D329">
+        <v>39.793542000000002</v>
+      </c>
+      <c r="E329">
+        <v>4.0200000000000031</v>
+      </c>
+      <c r="F329">
+        <v>55.970149249999999</v>
+      </c>
+      <c r="G329" t="s">
+        <v>9</v>
+      </c>
+      <c r="I329" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A330" t="s">
+        <v>20</v>
+      </c>
+      <c r="C330">
+        <v>562.5</v>
+      </c>
+      <c r="D330">
+        <v>43.793542000000002</v>
+      </c>
+      <c r="E330">
+        <v>4</v>
+      </c>
+      <c r="F330">
+        <v>56.25</v>
+      </c>
+      <c r="G330" t="s">
+        <v>9</v>
+      </c>
+      <c r="I330" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A331" t="s">
+        <v>20</v>
+      </c>
+      <c r="C331">
+        <v>625</v>
+      </c>
+      <c r="D331">
+        <v>47.817993999999999</v>
+      </c>
+      <c r="E331">
+        <v>4.0244519999999966</v>
+      </c>
+      <c r="F331">
+        <v>55.90823297</v>
+      </c>
+      <c r="G331" t="s">
+        <v>9</v>
+      </c>
+      <c r="I331" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>20</v>
+      </c>
+      <c r="C332">
+        <v>687.5</v>
+      </c>
+      <c r="D332">
+        <v>51.837992</v>
+      </c>
+      <c r="E332">
+        <v>4.0199980000000011</v>
+      </c>
+      <c r="F332">
+        <v>55.970177100000001</v>
+      </c>
+      <c r="G332" t="s">
+        <v>9</v>
+      </c>
+      <c r="I332" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>20</v>
+      </c>
+      <c r="C333">
+        <v>750</v>
+      </c>
+      <c r="D333">
+        <v>55.897981999999999</v>
+      </c>
+      <c r="E333">
+        <v>4.0599899999999991</v>
+      </c>
+      <c r="F333">
+        <v>55.418855710000003</v>
+      </c>
+      <c r="G333" t="s">
+        <v>9</v>
+      </c>
+      <c r="I333" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>20</v>
+      </c>
+      <c r="C334">
+        <v>812.5</v>
+      </c>
+      <c r="D334">
+        <v>59.937975999999999</v>
+      </c>
+      <c r="E334">
+        <v>4.0399940000000072</v>
+      </c>
+      <c r="F334">
+        <v>55.693152019999999</v>
+      </c>
+      <c r="G334" t="s">
+        <v>9</v>
+      </c>
+      <c r="I334" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>20</v>
+      </c>
+      <c r="C335">
+        <v>875</v>
+      </c>
+      <c r="D335">
+        <v>64.037968000000006</v>
+      </c>
+      <c r="E335">
+        <v>4.0999920000000003</v>
+      </c>
+      <c r="F335">
+        <v>54.87815586</v>
+      </c>
+      <c r="G335" t="s">
+        <v>9</v>
+      </c>
+      <c r="I335" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>20</v>
+      </c>
+      <c r="C336">
+        <v>937.5</v>
+      </c>
+      <c r="D336">
+        <v>68.097962999999993</v>
+      </c>
+      <c r="E336">
+        <v>4.0599950000000007</v>
+      </c>
+      <c r="F336">
+        <v>55.418787459999997</v>
+      </c>
+      <c r="G336" t="s">
+        <v>9</v>
+      </c>
+      <c r="I336" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A337" t="s">
+        <v>20</v>
+      </c>
+      <c r="C337">
+        <v>1000</v>
+      </c>
+      <c r="D337">
+        <v>72.217956999999998</v>
+      </c>
+      <c r="E337">
+        <v>4.1199939999999913</v>
+      </c>
+      <c r="F337">
+        <v>54.611730020000003</v>
+      </c>
+      <c r="G337" t="s">
+        <v>9</v>
+      </c>
+      <c r="I337" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A338" t="s">
+        <v>20</v>
+      </c>
+      <c r="C338">
+        <v>1062.5</v>
+      </c>
+      <c r="D338">
+        <v>76.297951999999995</v>
+      </c>
+      <c r="E338">
+        <v>4.0799949999999967</v>
+      </c>
+      <c r="F338">
+        <v>55.147126409999998</v>
+      </c>
+      <c r="G338" t="s">
+        <v>9</v>
+      </c>
+      <c r="I338" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A339" t="s">
+        <v>20</v>
+      </c>
+      <c r="C339">
+        <v>1125</v>
+      </c>
+      <c r="D339">
+        <v>80.397945000000007</v>
+      </c>
+      <c r="E339">
+        <v>4.099993000000012</v>
+      </c>
+      <c r="F339">
+        <v>54.87814247</v>
+      </c>
+      <c r="G339" t="s">
+        <v>9</v>
+      </c>
+      <c r="I339" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A340" t="s">
+        <v>20</v>
+      </c>
+      <c r="C340">
+        <v>1187.5</v>
+      </c>
+      <c r="D340">
+        <v>84.497936999999993</v>
+      </c>
+      <c r="E340">
+        <v>4.0999919999999861</v>
+      </c>
+      <c r="F340">
+        <v>54.87815586</v>
+      </c>
+      <c r="G340" t="s">
+        <v>9</v>
+      </c>
+      <c r="I340" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>20</v>
+      </c>
+      <c r="C341">
+        <v>1250</v>
+      </c>
+      <c r="D341">
+        <v>88.577934999999997</v>
+      </c>
+      <c r="E341">
+        <v>4.0799980000000033</v>
+      </c>
+      <c r="F341">
+        <v>55.147085859999997</v>
+      </c>
+      <c r="G341" t="s">
+        <v>9</v>
+      </c>
+      <c r="I341" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A342" t="s">
+        <v>20</v>
+      </c>
+      <c r="C342">
+        <v>1312.5</v>
+      </c>
+      <c r="D342">
+        <v>92.637932000000006</v>
+      </c>
+      <c r="E342">
+        <v>4.0599970000000098</v>
+      </c>
+      <c r="F342">
+        <v>55.418760159999998</v>
+      </c>
+      <c r="G342" t="s">
+        <v>9</v>
+      </c>
+      <c r="I342" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A343" t="s">
+        <v>20</v>
+      </c>
+      <c r="C343">
+        <v>1375</v>
+      </c>
+      <c r="D343">
+        <v>96.717930999999993</v>
+      </c>
+      <c r="E343">
+        <v>4.0799990000000008</v>
+      </c>
+      <c r="F343">
+        <v>55.147072340000001</v>
+      </c>
+      <c r="G343" t="s">
+        <v>9</v>
+      </c>
+      <c r="I343" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A344" t="s">
+        <v>20</v>
+      </c>
+      <c r="C344">
+        <v>1437.5</v>
+      </c>
+      <c r="D344">
+        <v>100.79792999999999</v>
+      </c>
+      <c r="E344">
+        <v>4.0799989999999866</v>
+      </c>
+      <c r="F344">
+        <v>55.147072340000001</v>
+      </c>
+      <c r="G344" t="s">
+        <v>9</v>
+      </c>
+      <c r="I344" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A345" t="s">
+        <v>20</v>
+      </c>
+      <c r="C345">
+        <v>1500</v>
+      </c>
+      <c r="D345">
+        <v>104.89792799999999</v>
+      </c>
+      <c r="E345">
+        <v>4.0999979999999994</v>
+      </c>
+      <c r="F345">
+        <v>54.878075549999998</v>
+      </c>
+      <c r="G345" t="s">
+        <v>9</v>
+      </c>
+      <c r="I345" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A346" t="s">
+        <v>20</v>
+      </c>
+      <c r="C346">
+        <v>1562.5</v>
+      </c>
+      <c r="D346">
+        <v>108.977926</v>
+      </c>
+      <c r="E346">
+        <v>4.0799980000000033</v>
+      </c>
+      <c r="F346">
+        <v>55.147085859999997</v>
+      </c>
+      <c r="G346" t="s">
+        <v>9</v>
+      </c>
+      <c r="I346" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A347" t="s">
+        <v>20</v>
+      </c>
+      <c r="C347">
+        <v>1625</v>
+      </c>
+      <c r="D347">
+        <v>113.057923</v>
+      </c>
+      <c r="E347">
+        <v>4.0799970000000059</v>
+      </c>
+      <c r="F347">
+        <v>55.147099369999999</v>
+      </c>
+      <c r="G347" t="s">
+        <v>9</v>
+      </c>
+      <c r="I347" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>20</v>
+      </c>
+      <c r="C348">
+        <v>1687.5</v>
+      </c>
+      <c r="D348">
+        <v>117.137922</v>
+      </c>
+      <c r="E348">
+        <v>4.0799990000000008</v>
+      </c>
+      <c r="F348">
+        <v>55.147072340000001</v>
+      </c>
+      <c r="G348" t="s">
+        <v>9</v>
+      </c>
+      <c r="I348" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>20</v>
+      </c>
+      <c r="C349">
+        <v>1750</v>
+      </c>
+      <c r="D349">
+        <v>121.217921</v>
+      </c>
+      <c r="E349">
+        <v>4.0799989999999866</v>
+      </c>
+      <c r="F349">
+        <v>55.147072340000001</v>
+      </c>
+      <c r="G349" t="s">
+        <v>9</v>
+      </c>
+      <c r="I349" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A350" t="s">
+        <v>20</v>
+      </c>
+      <c r="C350">
+        <v>1812.5</v>
+      </c>
+      <c r="D350">
+        <v>125.297921</v>
+      </c>
+      <c r="E350">
+        <v>4.0800000000000125</v>
+      </c>
+      <c r="F350">
+        <v>55.147058819999998</v>
+      </c>
+      <c r="G350" t="s">
+        <v>9</v>
+      </c>
+      <c r="I350" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A351" t="s">
+        <v>20</v>
+      </c>
+      <c r="C351">
+        <v>1875</v>
+      </c>
+      <c r="D351">
+        <v>129.397921</v>
+      </c>
+      <c r="E351">
+        <v>4.0999999999999943</v>
+      </c>
+      <c r="F351">
+        <v>54.87804878</v>
+      </c>
+      <c r="G351" t="s">
+        <v>9</v>
+      </c>
+      <c r="I351" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A352" t="s">
+        <v>20</v>
+      </c>
+      <c r="C352">
+        <v>1937.5</v>
+      </c>
+      <c r="D352">
+        <v>133.47792000000001</v>
+      </c>
+      <c r="E352">
+        <v>4.079999000000015</v>
+      </c>
+      <c r="F352">
+        <v>55.147072340000001</v>
+      </c>
+      <c r="G352" t="s">
+        <v>9</v>
+      </c>
+      <c r="I352" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A353" t="s">
+        <v>20</v>
+      </c>
+      <c r="C353">
+        <v>2000</v>
+      </c>
+      <c r="D353">
+        <v>137.57792000000001</v>
+      </c>
+      <c r="E353">
+        <v>4.0999999999999943</v>
+      </c>
+      <c r="F353">
+        <v>54.87804878</v>
+      </c>
+      <c r="G353" t="s">
+        <v>9</v>
+      </c>
+      <c r="I353" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A354" t="s">
+        <v>20</v>
+      </c>
+      <c r="C354">
+        <v>2062.5</v>
+      </c>
+      <c r="D354">
+        <v>141.65791999999999</v>
+      </c>
+      <c r="E354">
+        <v>4.0799999999999841</v>
+      </c>
+      <c r="F354">
+        <v>55.147058819999998</v>
+      </c>
+      <c r="G354" t="s">
+        <v>9</v>
+      </c>
+      <c r="I354" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A355" t="s">
+        <v>20</v>
+      </c>
+      <c r="C355">
+        <v>2125</v>
+      </c>
+      <c r="D355">
+        <v>145.77791999999999</v>
+      </c>
+      <c r="E355">
+        <v>4.1200000000000045</v>
+      </c>
+      <c r="F355">
+        <v>54.611650490000002</v>
+      </c>
+      <c r="G355" t="s">
+        <v>9</v>
+      </c>
+      <c r="I355" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A356" t="s">
+        <v>20</v>
+      </c>
+      <c r="C356">
+        <v>2187.5</v>
+      </c>
+      <c r="D356">
+        <v>149.89792</v>
+      </c>
+      <c r="E356">
+        <v>4.1200000000000045</v>
+      </c>
+      <c r="F356">
+        <v>54.611650490000002</v>
+      </c>
+      <c r="G356" t="s">
+        <v>9</v>
+      </c>
+      <c r="I356" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A357" t="s">
+        <v>20</v>
+      </c>
+      <c r="C357">
+        <v>2250</v>
+      </c>
+      <c r="D357">
+        <v>153.99791999999999</v>
+      </c>
+      <c r="E357">
+        <v>4.0999999999999943</v>
+      </c>
+      <c r="F357">
+        <v>54.87804878</v>
+      </c>
+      <c r="G357" t="s">
+        <v>9</v>
+      </c>
+      <c r="I357" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A358" t="s">
+        <v>20</v>
+      </c>
+      <c r="C358">
+        <v>2312.5</v>
+      </c>
+      <c r="D358">
+        <v>158.09791999999999</v>
+      </c>
+      <c r="E358">
+        <v>4.0999999999999943</v>
+      </c>
+      <c r="F358">
+        <v>54.87804878</v>
+      </c>
+      <c r="G358" t="s">
+        <v>9</v>
+      </c>
+      <c r="I358" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A359" t="s">
+        <v>20</v>
+      </c>
+      <c r="C359">
+        <v>2375</v>
+      </c>
+      <c r="D359">
+        <v>162.21791999999999</v>
+      </c>
+      <c r="E359">
+        <v>4.1200000000000045</v>
+      </c>
+      <c r="F359">
+        <v>54.611650490000002</v>
+      </c>
+      <c r="G359" t="s">
+        <v>9</v>
+      </c>
+      <c r="I359" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A360" t="s">
+        <v>20</v>
+      </c>
+      <c r="C360">
+        <v>2437.5</v>
+      </c>
+      <c r="D360">
+        <v>166.33792</v>
+      </c>
+      <c r="E360">
+        <v>4.1200000000000045</v>
+      </c>
+      <c r="F360">
+        <v>54.611650490000002</v>
+      </c>
+      <c r="G360" t="s">
+        <v>9</v>
+      </c>
+      <c r="I360" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A361" t="s">
+        <v>20</v>
+      </c>
+      <c r="C361">
+        <v>2500</v>
+      </c>
+      <c r="D361">
+        <v>170.47792000000001</v>
+      </c>
+      <c r="E361">
+        <v>4.1400000000000148</v>
+      </c>
+      <c r="F361">
+        <v>54.347826089999998</v>
+      </c>
+      <c r="G361" t="s">
+        <v>9</v>
+      </c>
+      <c r="I361" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A362" t="s">
+        <v>20</v>
+      </c>
+      <c r="C362">
+        <v>2562.5</v>
+      </c>
+      <c r="D362">
+        <v>174.61792</v>
+      </c>
+      <c r="E362">
+        <v>4.1399999999999864</v>
+      </c>
+      <c r="F362">
+        <v>54.347826089999998</v>
+      </c>
+      <c r="G362" t="s">
+        <v>9</v>
+      </c>
+      <c r="I362" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A363" t="s">
+        <v>20</v>
+      </c>
+      <c r="C363">
+        <v>2625</v>
+      </c>
+      <c r="D363">
+        <v>178.73792</v>
+      </c>
+      <c r="E363">
+        <v>4.1200000000000045</v>
+      </c>
+      <c r="F363">
+        <v>54.611650490000002</v>
+      </c>
+      <c r="G363" t="s">
+        <v>9</v>
+      </c>
+      <c r="I363" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A364" t="s">
+        <v>20</v>
+      </c>
+      <c r="C364">
+        <v>2687.5</v>
+      </c>
+      <c r="D364">
+        <v>182.87791999999999</v>
+      </c>
+      <c r="E364">
+        <v>4.1399999999999864</v>
+      </c>
+      <c r="F364">
+        <v>54.347826089999998</v>
+      </c>
+      <c r="G364" t="s">
+        <v>9</v>
+      </c>
+      <c r="I364" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A365" t="s">
+        <v>20</v>
+      </c>
+      <c r="C365">
+        <v>2750</v>
+      </c>
+      <c r="D365">
+        <v>187.01792</v>
+      </c>
+      <c r="E365">
+        <v>4.1400000000000148</v>
+      </c>
+      <c r="F365">
+        <v>54.347826089999998</v>
+      </c>
+      <c r="G365" t="s">
+        <v>9</v>
+      </c>
+      <c r="I365" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A366" t="s">
+        <v>20</v>
+      </c>
+      <c r="C366">
+        <v>2812.5</v>
+      </c>
+      <c r="D366">
+        <v>191.17792</v>
+      </c>
+      <c r="E366">
+        <v>4.1599999999999966</v>
+      </c>
+      <c r="F366">
+        <v>54.08653846</v>
+      </c>
+      <c r="G366" t="s">
+        <v>9</v>
+      </c>
+      <c r="I366" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A367" t="s">
+        <v>20</v>
+      </c>
+      <c r="C367">
+        <v>2875</v>
+      </c>
+      <c r="D367">
+        <v>195.33792</v>
+      </c>
+      <c r="E367">
+        <v>4.1599999999999966</v>
+      </c>
+      <c r="F367">
+        <v>54.08653846</v>
+      </c>
+      <c r="G367" t="s">
+        <v>9</v>
+      </c>
+      <c r="I367" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A368" t="s">
+        <v>20</v>
+      </c>
+      <c r="C368">
+        <v>2937.5</v>
+      </c>
+      <c r="D368">
+        <v>199.49791999999999</v>
+      </c>
+      <c r="E368">
+        <v>4.1599999999999966</v>
+      </c>
+      <c r="F368">
+        <v>54.08653846</v>
+      </c>
+      <c r="G368" t="s">
+        <v>9</v>
+      </c>
+      <c r="I368" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A369" t="s">
+        <v>20</v>
+      </c>
+      <c r="C369">
+        <v>3000</v>
+      </c>
+      <c r="D369">
+        <v>203.677919</v>
+      </c>
+      <c r="E369">
+        <v>4.1799990000000093</v>
+      </c>
+      <c r="F369">
+        <v>53.827764070000001</v>
+      </c>
+      <c r="G369" t="s">
+        <v>9</v>
+      </c>
+      <c r="I369" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A370" t="s">
+        <v>20</v>
+      </c>
+      <c r="C370">
+        <v>3062.5</v>
+      </c>
+      <c r="D370">
+        <v>207.91791900000001</v>
+      </c>
+      <c r="E370">
+        <v>4.2400000000000091</v>
+      </c>
+      <c r="F370">
+        <v>53.066037739999999</v>
+      </c>
+      <c r="G370" t="s">
+        <v>9</v>
+      </c>
+      <c r="I370" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A371" t="s">
+        <v>20</v>
+      </c>
+      <c r="C371">
+        <v>3125</v>
+      </c>
+      <c r="D371">
+        <v>212.117919</v>
+      </c>
+      <c r="E371">
+        <v>4.1999999999999886</v>
+      </c>
+      <c r="F371">
+        <v>53.571428570000002</v>
+      </c>
+      <c r="G371" t="s">
+        <v>9</v>
+      </c>
+      <c r="I371" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A372" t="s">
+        <v>20</v>
+      </c>
+      <c r="C372">
+        <v>3187.5</v>
+      </c>
+      <c r="D372">
+        <v>216.337919</v>
+      </c>
+      <c r="E372">
+        <v>4.2199999999999989</v>
+      </c>
+      <c r="F372">
+        <v>53.317535550000002</v>
+      </c>
+      <c r="G372" t="s">
+        <v>9</v>
+      </c>
+      <c r="I372" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A373" t="s">
+        <v>20</v>
+      </c>
+      <c r="C373">
+        <v>3250</v>
+      </c>
+      <c r="D373">
+        <v>220.557919</v>
+      </c>
+      <c r="E373">
+        <v>4.2199999999999989</v>
+      </c>
+      <c r="F373">
+        <v>53.317535550000002</v>
+      </c>
+      <c r="G373" t="s">
+        <v>9</v>
+      </c>
+      <c r="I373" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A374" t="s">
+        <v>20</v>
+      </c>
+      <c r="C374">
+        <v>3312.5</v>
+      </c>
+      <c r="D374">
+        <v>224.777919</v>
+      </c>
+      <c r="E374">
+        <v>4.2199999999999989</v>
+      </c>
+      <c r="F374">
+        <v>53.317535550000002</v>
+      </c>
+      <c r="G374" t="s">
+        <v>9</v>
+      </c>
+      <c r="I374" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A375" t="s">
+        <v>20</v>
+      </c>
+      <c r="C375">
+        <v>3375</v>
+      </c>
+      <c r="D375">
+        <v>228.997919</v>
+      </c>
+      <c r="E375">
+        <v>4.2199999999999989</v>
+      </c>
+      <c r="F375">
+        <v>53.317535550000002</v>
+      </c>
+      <c r="G375" t="s">
+        <v>9</v>
+      </c>
+      <c r="I375" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A376" t="s">
+        <v>20</v>
+      </c>
+      <c r="C376">
+        <v>3437.5</v>
+      </c>
+      <c r="D376">
+        <v>233.23791900000001</v>
+      </c>
+      <c r="E376">
+        <v>4.2400000000000091</v>
+      </c>
+      <c r="F376">
+        <v>53.066037739999999</v>
+      </c>
+      <c r="G376" t="s">
+        <v>9</v>
+      </c>
+      <c r="I376" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A377" t="s">
+        <v>20</v>
+      </c>
+      <c r="C377">
+        <v>3500</v>
+      </c>
+      <c r="D377">
+        <v>237.457919</v>
+      </c>
+      <c r="E377">
+        <v>4.2199999999999989</v>
+      </c>
+      <c r="F377">
+        <v>53.317535550000002</v>
+      </c>
+      <c r="G377" t="s">
+        <v>9</v>
+      </c>
+      <c r="I377" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A378" t="s">
+        <v>20</v>
+      </c>
+      <c r="C378">
+        <v>3562.5</v>
+      </c>
+      <c r="D378">
+        <v>241.69791900000001</v>
+      </c>
+      <c r="E378">
+        <v>4.2400000000000091</v>
+      </c>
+      <c r="F378">
+        <v>53.066037739999999</v>
+      </c>
+      <c r="G378" t="s">
+        <v>9</v>
+      </c>
+      <c r="I378" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A379" t="s">
+        <v>20</v>
+      </c>
+      <c r="C379">
+        <v>3625</v>
+      </c>
+      <c r="D379">
+        <v>245.95791</v>
+      </c>
+      <c r="E379">
+        <v>4.2599909999999852</v>
+      </c>
+      <c r="F379">
+        <v>52.817012990000002</v>
+      </c>
+      <c r="G379" t="s">
+        <v>9</v>
+      </c>
+      <c r="I379" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A380" t="s">
+        <v>20</v>
+      </c>
+      <c r="C380">
+        <v>3687.5</v>
+      </c>
+      <c r="D380">
+        <v>250.21789799999999</v>
+      </c>
+      <c r="E380">
+        <v>4.2599880000000212</v>
+      </c>
+      <c r="F380">
+        <v>52.817050190000003</v>
+      </c>
+      <c r="G380" t="s">
+        <v>9</v>
+      </c>
+      <c r="I380" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A381" t="s">
+        <v>20</v>
+      </c>
+      <c r="C381">
+        <v>3750</v>
+      </c>
+      <c r="D381">
+        <v>254.47788800000001</v>
+      </c>
+      <c r="E381">
+        <v>4.2599899999999593</v>
+      </c>
+      <c r="F381">
+        <v>52.817025389999998</v>
+      </c>
+      <c r="G381" t="s">
+        <v>9</v>
+      </c>
+      <c r="I381" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A382" t="s">
+        <v>20</v>
+      </c>
+      <c r="C382">
+        <v>3812.5</v>
+      </c>
+      <c r="D382">
+        <v>258.73788300000001</v>
+      </c>
+      <c r="E382">
+        <v>4.2599950000000035</v>
+      </c>
+      <c r="F382">
+        <v>52.816963399999999</v>
+      </c>
+      <c r="G382" t="s">
+        <v>9</v>
+      </c>
+      <c r="I382" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A383" t="s">
+        <v>20</v>
+      </c>
+      <c r="C383">
+        <v>3875</v>
+      </c>
+      <c r="D383">
+        <v>262.99787900000001</v>
+      </c>
+      <c r="E383">
+        <v>4.259996000000001</v>
+      </c>
+      <c r="F383">
+        <v>52.816951000000003</v>
+      </c>
+      <c r="G383" t="s">
+        <v>9</v>
+      </c>
+      <c r="I383" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A384" t="s">
+        <v>20</v>
+      </c>
+      <c r="C384">
+        <v>3937.5</v>
+      </c>
+      <c r="D384">
+        <v>267.23787399999998</v>
+      </c>
+      <c r="E384">
+        <v>4.2399950000000217</v>
+      </c>
+      <c r="F384">
+        <v>53.066100310000003</v>
+      </c>
+      <c r="G384" t="s">
+        <v>9</v>
+      </c>
+      <c r="I384" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A385" t="s">
+        <v>20</v>
+      </c>
+      <c r="C385">
+        <v>4000</v>
+      </c>
+      <c r="D385">
+        <v>271.49786799999998</v>
+      </c>
+      <c r="E385">
+        <v>4.2599940000000061</v>
+      </c>
+      <c r="F385">
+        <v>52.816975800000002</v>
+      </c>
+      <c r="G385" t="s">
+        <v>9</v>
+      </c>
+      <c r="I385" t="s">
         <v>18</v>
       </c>
     </row>
@@ -7837,13 +9318,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I193 A194:A321 I194:I321" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I321 A322:A385 I322:I385" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{9d5ca952-e4a5-43e6-b17c-c01d313ad135}" enabled="0" method="" siteId="{9d5ca952-e4a5-43e6-b17c-c01d313ad135}" removed="1"/>
-</clbl:labelList>
 </file>
--- a/pages/video_analysis/IP_Master_Women.xlsx
+++ b/pages/video_analysis/IP_Master_Women.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sportnzgroup-my.sharepoint.com/personal/anja_kuys_hpsnz_org_nz/Documents/Desktop/Scripts/CNZPD/pages/video_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_AFAA658680BF63C7274CA376ADE30E422081DE5F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE9766A7-B058-404D-8BF5-19940765D433}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_AFAA658680BF63C7274CA376ADE30E422081DE5F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6896326C-145C-40B9-8182-18C9CD98A771}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1620" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="24">
   <si>
     <t>Title</t>
   </si>
@@ -86,6 +86,15 @@
   </si>
   <si>
     <t>26-07-31 Glasgow CWG Botha F</t>
+  </si>
+  <si>
+    <t>https://youtu.be/jPjRLOpCRmI</t>
+  </si>
+  <si>
+    <t>https://youtu.be/tsK9f37v1Tg</t>
+  </si>
+  <si>
+    <t>https://youtu.be/4U3LBIosxHA</t>
   </si>
 </sst>
 </file>
@@ -428,7 +437,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I385"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="41.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.83203125" bestFit="1" customWidth="1"/>
@@ -439,7 +448,7 @@
     <col min="8" max="8" width="27.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -465,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -491,7 +500,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -514,7 +523,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -537,7 +546,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -560,7 +569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -583,7 +592,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -606,7 +615,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -629,7 +638,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -652,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -675,7 +684,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -698,7 +707,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -721,7 +730,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -744,7 +753,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -767,7 +776,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -790,7 +799,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -813,7 +822,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -836,7 +845,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -859,7 +868,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -882,7 +891,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -905,7 +914,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -928,7 +937,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -951,7 +960,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -974,7 +983,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -997,7 +1006,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -1020,7 +1029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -1043,7 +1052,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -1066,7 +1075,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -1089,7 +1098,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -1112,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>8</v>
       </c>
@@ -1135,7 +1144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>8</v>
       </c>
@@ -1158,7 +1167,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>8</v>
       </c>
@@ -1181,7 +1190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>8</v>
       </c>
@@ -1204,7 +1213,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>8</v>
       </c>
@@ -1227,7 +1236,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>8</v>
       </c>
@@ -1250,7 +1259,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>8</v>
       </c>
@@ -1273,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -1296,7 +1305,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -1319,7 +1328,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>8</v>
       </c>
@@ -1342,7 +1351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -1365,7 +1374,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>8</v>
       </c>
@@ -1388,7 +1397,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>8</v>
       </c>
@@ -1411,7 +1420,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>8</v>
       </c>
@@ -1434,7 +1443,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>8</v>
       </c>
@@ -1457,7 +1466,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>8</v>
       </c>
@@ -1480,7 +1489,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>8</v>
       </c>
@@ -1503,7 +1512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>8</v>
       </c>
@@ -1526,7 +1535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>8</v>
       </c>
@@ -1549,7 +1558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -1572,7 +1581,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>11</v>
       </c>
@@ -1598,7 +1607,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>11</v>
       </c>
@@ -1621,7 +1630,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>11</v>
       </c>
@@ -1644,7 +1653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>11</v>
       </c>
@@ -1667,7 +1676,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>11</v>
       </c>
@@ -1690,7 +1699,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>11</v>
       </c>
@@ -1713,7 +1722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -1736,7 +1745,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>11</v>
       </c>
@@ -1759,7 +1768,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>11</v>
       </c>
@@ -1782,7 +1791,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>11</v>
       </c>
@@ -1805,7 +1814,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>11</v>
       </c>
@@ -1828,7 +1837,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>11</v>
       </c>
@@ -1851,7 +1860,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>11</v>
       </c>
@@ -1874,7 +1883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -1897,7 +1906,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>11</v>
       </c>
@@ -1920,7 +1929,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>11</v>
       </c>
@@ -1943,7 +1952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>11</v>
       </c>
@@ -1966,7 +1975,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>11</v>
       </c>
@@ -1989,7 +1998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>11</v>
       </c>
@@ -2012,7 +2021,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>11</v>
       </c>
@@ -2035,7 +2044,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>11</v>
       </c>
@@ -2058,7 +2067,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>11</v>
       </c>
@@ -2081,7 +2090,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>11</v>
       </c>
@@ -2104,7 +2113,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>11</v>
       </c>
@@ -2127,7 +2136,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>11</v>
       </c>
@@ -2150,7 +2159,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>11</v>
       </c>
@@ -2173,7 +2182,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>11</v>
       </c>
@@ -2196,7 +2205,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>11</v>
       </c>
@@ -2219,7 +2228,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>11</v>
       </c>
@@ -2242,7 +2251,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>11</v>
       </c>
@@ -2265,7 +2274,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>11</v>
       </c>
@@ -2288,7 +2297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>11</v>
       </c>
@@ -2311,7 +2320,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>11</v>
       </c>
@@ -2334,7 +2343,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>11</v>
       </c>
@@ -2357,7 +2366,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>11</v>
       </c>
@@ -2380,7 +2389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>11</v>
       </c>
@@ -2403,7 +2412,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>11</v>
       </c>
@@ -2426,7 +2435,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>11</v>
       </c>
@@ -2449,7 +2458,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>11</v>
       </c>
@@ -2472,7 +2481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>11</v>
       </c>
@@ -2495,7 +2504,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>11</v>
       </c>
@@ -2518,7 +2527,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>11</v>
       </c>
@@ -2541,7 +2550,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>11</v>
       </c>
@@ -2564,7 +2573,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>11</v>
       </c>
@@ -2587,7 +2596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>11</v>
       </c>
@@ -2610,7 +2619,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>11</v>
       </c>
@@ -2633,7 +2642,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>11</v>
       </c>
@@ -2656,7 +2665,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>11</v>
       </c>
@@ -2679,7 +2688,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>13</v>
       </c>
@@ -2705,7 +2714,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>13</v>
       </c>
@@ -2728,7 +2737,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>13</v>
       </c>
@@ -2751,7 +2760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>13</v>
       </c>
@@ -2774,7 +2783,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>13</v>
       </c>
@@ -2797,7 +2806,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>13</v>
       </c>
@@ -2820,7 +2829,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>13</v>
       </c>
@@ -2843,7 +2852,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>13</v>
       </c>
@@ -2866,7 +2875,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>13</v>
       </c>
@@ -2889,7 +2898,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>13</v>
       </c>
@@ -2912,7 +2921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>13</v>
       </c>
@@ -2935,7 +2944,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>13</v>
       </c>
@@ -2958,7 +2967,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>13</v>
       </c>
@@ -2981,7 +2990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>13</v>
       </c>
@@ -3004,7 +3013,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>13</v>
       </c>
@@ -3027,7 +3036,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>13</v>
       </c>
@@ -3050,7 +3059,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>13</v>
       </c>
@@ -3073,7 +3082,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>13</v>
       </c>
@@ -3096,7 +3105,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>13</v>
       </c>
@@ -3119,7 +3128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>13</v>
       </c>
@@ -3142,7 +3151,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>13</v>
       </c>
@@ -3165,7 +3174,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>13</v>
       </c>
@@ -3188,7 +3197,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>13</v>
       </c>
@@ -3211,7 +3220,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>13</v>
       </c>
@@ -3234,7 +3243,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>13</v>
       </c>
@@ -3257,7 +3266,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>13</v>
       </c>
@@ -3280,7 +3289,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>13</v>
       </c>
@@ -3303,7 +3312,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>13</v>
       </c>
@@ -3326,7 +3335,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>13</v>
       </c>
@@ -3349,7 +3358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>13</v>
       </c>
@@ -3372,7 +3381,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>13</v>
       </c>
@@ -3395,7 +3404,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>13</v>
       </c>
@@ -3418,7 +3427,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>13</v>
       </c>
@@ -3441,7 +3450,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>13</v>
       </c>
@@ -3464,7 +3473,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>13</v>
       </c>
@@ -3487,7 +3496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>13</v>
       </c>
@@ -3510,7 +3519,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>13</v>
       </c>
@@ -3533,7 +3542,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>13</v>
       </c>
@@ -3556,7 +3565,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>13</v>
       </c>
@@ -3579,7 +3588,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>13</v>
       </c>
@@ -3602,7 +3611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>13</v>
       </c>
@@ -3625,7 +3634,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>13</v>
       </c>
@@ -3648,7 +3657,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>13</v>
       </c>
@@ -3671,7 +3680,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>13</v>
       </c>
@@ -3694,7 +3703,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>13</v>
       </c>
@@ -3717,7 +3726,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>13</v>
       </c>
@@ -3740,7 +3749,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>13</v>
       </c>
@@ -3763,7 +3772,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>13</v>
       </c>
@@ -3786,7 +3795,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>15</v>
       </c>
@@ -3812,7 +3821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>15</v>
       </c>
@@ -3835,7 +3844,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>15</v>
       </c>
@@ -3858,7 +3867,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>15</v>
       </c>
@@ -3881,7 +3890,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>15</v>
       </c>
@@ -3904,7 +3913,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>15</v>
       </c>
@@ -3927,7 +3936,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>15</v>
       </c>
@@ -3950,7 +3959,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>15</v>
       </c>
@@ -3973,7 +3982,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>15</v>
       </c>
@@ -3996,7 +4005,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>15</v>
       </c>
@@ -4019,7 +4028,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>15</v>
       </c>
@@ -4042,7 +4051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>15</v>
       </c>
@@ -4065,7 +4074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>15</v>
       </c>
@@ -4088,7 +4097,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>15</v>
       </c>
@@ -4111,7 +4120,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>15</v>
       </c>
@@ -4134,7 +4143,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>15</v>
       </c>
@@ -4157,7 +4166,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>15</v>
       </c>
@@ -4180,7 +4189,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>15</v>
       </c>
@@ -4203,7 +4212,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>15</v>
       </c>
@@ -4226,7 +4235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>15</v>
       </c>
@@ -4249,7 +4258,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>15</v>
       </c>
@@ -4272,7 +4281,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>15</v>
       </c>
@@ -4295,7 +4304,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>15</v>
       </c>
@@ -4318,7 +4327,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>15</v>
       </c>
@@ -4341,7 +4350,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>15</v>
       </c>
@@ -4364,7 +4373,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>15</v>
       </c>
@@ -4387,7 +4396,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>15</v>
       </c>
@@ -4410,7 +4419,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>15</v>
       </c>
@@ -4433,7 +4442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>15</v>
       </c>
@@ -4456,7 +4465,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>15</v>
       </c>
@@ -4479,7 +4488,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>15</v>
       </c>
@@ -4502,7 +4511,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>15</v>
       </c>
@@ -4525,7 +4534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>15</v>
       </c>
@@ -4548,7 +4557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>15</v>
       </c>
@@ -4571,7 +4580,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>15</v>
       </c>
@@ -4594,7 +4603,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>15</v>
       </c>
@@ -4617,7 +4626,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>15</v>
       </c>
@@ -4640,7 +4649,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>15</v>
       </c>
@@ -4663,7 +4672,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>15</v>
       </c>
@@ -4686,7 +4695,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>15</v>
       </c>
@@ -4709,7 +4718,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>15</v>
       </c>
@@ -4732,7 +4741,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>15</v>
       </c>
@@ -4755,7 +4764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>15</v>
       </c>
@@ -4778,7 +4787,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>15</v>
       </c>
@@ -4801,7 +4810,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>15</v>
       </c>
@@ -4824,7 +4833,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>15</v>
       </c>
@@ -4847,7 +4856,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>15</v>
       </c>
@@ -4870,7 +4879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>15</v>
       </c>
@@ -4893,7 +4902,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>17</v>
       </c>
@@ -4912,11 +4921,14 @@
       <c r="G194" t="s">
         <v>9</v>
       </c>
+      <c r="H194" t="s">
+        <v>21</v>
+      </c>
       <c r="I194" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>17</v>
       </c>
@@ -4939,7 +4951,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>17</v>
       </c>
@@ -4962,7 +4974,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>17</v>
       </c>
@@ -4985,7 +4997,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>17</v>
       </c>
@@ -5008,7 +5020,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>17</v>
       </c>
@@ -5031,7 +5043,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>17</v>
       </c>
@@ -5054,7 +5066,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>17</v>
       </c>
@@ -5077,7 +5089,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>17</v>
       </c>
@@ -5100,7 +5112,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>17</v>
       </c>
@@ -5123,7 +5135,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>17</v>
       </c>
@@ -5146,7 +5158,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>17</v>
       </c>
@@ -5169,7 +5181,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>17</v>
       </c>
@@ -5192,7 +5204,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>17</v>
       </c>
@@ -5215,7 +5227,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>17</v>
       </c>
@@ -5238,7 +5250,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>17</v>
       </c>
@@ -5261,7 +5273,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>17</v>
       </c>
@@ -5284,7 +5296,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>17</v>
       </c>
@@ -5307,7 +5319,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>17</v>
       </c>
@@ -5330,7 +5342,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>17</v>
       </c>
@@ -5353,7 +5365,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>17</v>
       </c>
@@ -5376,7 +5388,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>17</v>
       </c>
@@ -5399,7 +5411,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>17</v>
       </c>
@@ -5422,7 +5434,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>17</v>
       </c>
@@ -5445,7 +5457,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>17</v>
       </c>
@@ -5468,7 +5480,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>17</v>
       </c>
@@ -5491,7 +5503,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>17</v>
       </c>
@@ -5514,7 +5526,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>17</v>
       </c>
@@ -5537,7 +5549,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>17</v>
       </c>
@@ -5560,7 +5572,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>17</v>
       </c>
@@ -5583,7 +5595,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>17</v>
       </c>
@@ -5606,7 +5618,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>17</v>
       </c>
@@ -5629,7 +5641,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>17</v>
       </c>
@@ -5652,7 +5664,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>17</v>
       </c>
@@ -5675,7 +5687,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>17</v>
       </c>
@@ -5698,7 +5710,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>17</v>
       </c>
@@ -5721,7 +5733,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>17</v>
       </c>
@@ -5744,7 +5756,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>17</v>
       </c>
@@ -5767,7 +5779,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>17</v>
       </c>
@@ -5790,7 +5802,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>17</v>
       </c>
@@ -5813,7 +5825,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>17</v>
       </c>
@@ -5836,7 +5848,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>17</v>
       </c>
@@ -5859,7 +5871,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>17</v>
       </c>
@@ -5882,7 +5894,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>17</v>
       </c>
@@ -5905,7 +5917,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>17</v>
       </c>
@@ -5928,7 +5940,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>17</v>
       </c>
@@ -5951,7 +5963,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>17</v>
       </c>
@@ -5974,7 +5986,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>17</v>
       </c>
@@ -5997,7 +6009,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>17</v>
       </c>
@@ -6020,7 +6032,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>17</v>
       </c>
@@ -6043,7 +6055,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>17</v>
       </c>
@@ -6066,7 +6078,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>17</v>
       </c>
@@ -6089,7 +6101,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>17</v>
       </c>
@@ -6112,7 +6124,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>17</v>
       </c>
@@ -6135,7 +6147,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>17</v>
       </c>
@@ -6158,7 +6170,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>17</v>
       </c>
@@ -6181,7 +6193,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>17</v>
       </c>
@@ -6204,7 +6216,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>17</v>
       </c>
@@ -6227,7 +6239,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>17</v>
       </c>
@@ -6250,7 +6262,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>17</v>
       </c>
@@ -6273,7 +6285,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>17</v>
       </c>
@@ -6296,7 +6308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>17</v>
       </c>
@@ -6319,7 +6331,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>17</v>
       </c>
@@ -6342,7 +6354,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>17</v>
       </c>
@@ -6365,7 +6377,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>19</v>
       </c>
@@ -6384,11 +6396,14 @@
       <c r="G258" t="s">
         <v>9</v>
       </c>
+      <c r="H258" t="s">
+        <v>23</v>
+      </c>
       <c r="I258" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>19</v>
       </c>
@@ -6411,7 +6426,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>19</v>
       </c>
@@ -6434,7 +6449,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>19</v>
       </c>
@@ -6457,7 +6472,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>19</v>
       </c>
@@ -6480,7 +6495,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>19</v>
       </c>
@@ -6503,7 +6518,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>19</v>
       </c>
@@ -6526,7 +6541,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>19</v>
       </c>
@@ -6549,7 +6564,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>19</v>
       </c>
@@ -6572,7 +6587,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>19</v>
       </c>
@@ -6595,7 +6610,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>19</v>
       </c>
@@ -6618,7 +6633,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>19</v>
       </c>
@@ -6641,7 +6656,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>19</v>
       </c>
@@ -6664,7 +6679,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>19</v>
       </c>
@@ -6687,7 +6702,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>19</v>
       </c>
@@ -6710,7 +6725,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>19</v>
       </c>
@@ -6733,7 +6748,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>19</v>
       </c>
@@ -6756,7 +6771,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>19</v>
       </c>
@@ -6779,7 +6794,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>19</v>
       </c>
@@ -6802,7 +6817,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>19</v>
       </c>
@@ -6825,7 +6840,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>19</v>
       </c>
@@ -6848,7 +6863,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>19</v>
       </c>
@@ -6871,7 +6886,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>19</v>
       </c>
@@ -6894,7 +6909,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>19</v>
       </c>
@@ -6917,7 +6932,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>19</v>
       </c>
@@ -6940,7 +6955,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>19</v>
       </c>
@@ -6963,7 +6978,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>19</v>
       </c>
@@ -6986,7 +7001,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>19</v>
       </c>
@@ -7009,7 +7024,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>19</v>
       </c>
@@ -7032,7 +7047,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>19</v>
       </c>
@@ -7055,7 +7070,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>19</v>
       </c>
@@ -7078,7 +7093,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>19</v>
       </c>
@@ -7101,7 +7116,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>19</v>
       </c>
@@ -7124,7 +7139,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>19</v>
       </c>
@@ -7147,7 +7162,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>19</v>
       </c>
@@ -7170,7 +7185,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>19</v>
       </c>
@@ -7193,7 +7208,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>19</v>
       </c>
@@ -7216,7 +7231,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>19</v>
       </c>
@@ -7239,7 +7254,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>19</v>
       </c>
@@ -7262,7 +7277,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>19</v>
       </c>
@@ -7285,7 +7300,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>19</v>
       </c>
@@ -7308,7 +7323,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>19</v>
       </c>
@@ -7331,7 +7346,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>19</v>
       </c>
@@ -7354,7 +7369,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>19</v>
       </c>
@@ -7377,7 +7392,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>19</v>
       </c>
@@ -7400,7 +7415,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>19</v>
       </c>
@@ -7423,7 +7438,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>19</v>
       </c>
@@ -7446,7 +7461,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>19</v>
       </c>
@@ -7469,7 +7484,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>19</v>
       </c>
@@ -7492,7 +7507,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>19</v>
       </c>
@@ -7515,7 +7530,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>19</v>
       </c>
@@ -7538,7 +7553,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>19</v>
       </c>
@@ -7561,7 +7576,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>19</v>
       </c>
@@ -7584,7 +7599,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>19</v>
       </c>
@@ -7607,7 +7622,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>19</v>
       </c>
@@ -7630,7 +7645,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>19</v>
       </c>
@@ -7653,7 +7668,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>19</v>
       </c>
@@ -7676,7 +7691,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>19</v>
       </c>
@@ -7699,7 +7714,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="316" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>19</v>
       </c>
@@ -7722,7 +7737,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>19</v>
       </c>
@@ -7745,7 +7760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>19</v>
       </c>
@@ -7768,7 +7783,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>19</v>
       </c>
@@ -7791,7 +7806,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>19</v>
       </c>
@@ -7814,7 +7829,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>19</v>
       </c>
@@ -7837,7 +7852,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="322" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>20</v>
       </c>
@@ -7856,11 +7871,14 @@
       <c r="G322" t="s">
         <v>9</v>
       </c>
+      <c r="H322" t="s">
+        <v>22</v>
+      </c>
       <c r="I322" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="323" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>20</v>
       </c>
@@ -7883,7 +7901,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="324" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>20</v>
       </c>
@@ -7906,7 +7924,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="325" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>20</v>
       </c>
@@ -7929,7 +7947,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="326" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>20</v>
       </c>
@@ -7952,7 +7970,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="327" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>20</v>
       </c>
@@ -7975,7 +7993,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="328" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>20</v>
       </c>
@@ -7998,7 +8016,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="329" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>20</v>
       </c>
@@ -8021,7 +8039,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="330" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>20</v>
       </c>
@@ -8044,7 +8062,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="331" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>20</v>
       </c>
@@ -8067,7 +8085,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="332" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>20</v>
       </c>
@@ -8090,7 +8108,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>20</v>
       </c>
@@ -8113,7 +8131,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="334" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>20</v>
       </c>
@@ -8136,7 +8154,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="335" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>20</v>
       </c>
@@ -8159,7 +8177,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="336" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>20</v>
       </c>
@@ -8182,7 +8200,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="337" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>20</v>
       </c>
@@ -8205,7 +8223,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="338" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>20</v>
       </c>
@@ -8228,7 +8246,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="339" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>20</v>
       </c>
@@ -8251,7 +8269,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="340" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>20</v>
       </c>
@@ -8274,7 +8292,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="341" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>20</v>
       </c>
@@ -8297,7 +8315,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="342" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>20</v>
       </c>
@@ -8320,7 +8338,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="343" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>20</v>
       </c>
@@ -8343,7 +8361,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="344" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>20</v>
       </c>
@@ -8366,7 +8384,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="345" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>20</v>
       </c>
@@ -8389,7 +8407,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="346" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>20</v>
       </c>
@@ -8412,7 +8430,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="347" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>20</v>
       </c>
@@ -8435,7 +8453,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="348" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>20</v>
       </c>
@@ -8458,7 +8476,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="349" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>20</v>
       </c>
@@ -8481,7 +8499,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="350" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>20</v>
       </c>
@@ -8504,7 +8522,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="351" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>20</v>
       </c>
@@ -8527,7 +8545,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="352" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>20</v>
       </c>
@@ -8550,7 +8568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="353" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>20</v>
       </c>
@@ -8573,7 +8591,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="354" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>20</v>
       </c>
@@ -8596,7 +8614,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="355" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>20</v>
       </c>
@@ -8619,7 +8637,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="356" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>20</v>
       </c>
@@ -8642,7 +8660,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="357" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>20</v>
       </c>
@@ -8665,7 +8683,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="358" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>20</v>
       </c>
@@ -8688,7 +8706,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="359" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>20</v>
       </c>
@@ -8711,7 +8729,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="360" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>20</v>
       </c>
@@ -8734,7 +8752,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="361" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>20</v>
       </c>
@@ -8757,7 +8775,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="362" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>20</v>
       </c>
@@ -8780,7 +8798,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="363" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>20</v>
       </c>
@@ -8803,7 +8821,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="364" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>20</v>
       </c>
@@ -8826,7 +8844,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="365" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>20</v>
       </c>
@@ -8849,7 +8867,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="366" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>20</v>
       </c>
@@ -8872,7 +8890,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="367" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>20</v>
       </c>
@@ -8895,7 +8913,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="368" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>20</v>
       </c>
@@ -8918,7 +8936,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="369" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>20</v>
       </c>
@@ -8941,7 +8959,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="370" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>20</v>
       </c>
@@ -8964,7 +8982,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="371" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>20</v>
       </c>
@@ -8987,7 +9005,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="372" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>20</v>
       </c>
@@ -9010,7 +9028,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="373" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>20</v>
       </c>
@@ -9033,7 +9051,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="374" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>20</v>
       </c>
@@ -9056,7 +9074,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="375" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>20</v>
       </c>
@@ -9079,7 +9097,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="376" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>20</v>
       </c>
@@ -9102,7 +9120,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="377" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>20</v>
       </c>
@@ -9125,7 +9143,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="378" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>20</v>
       </c>
@@ -9148,7 +9166,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="379" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>20</v>
       </c>
@@ -9171,7 +9189,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="380" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>20</v>
       </c>
@@ -9194,7 +9212,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="381" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>20</v>
       </c>
@@ -9217,7 +9235,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="382" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>20</v>
       </c>
@@ -9240,7 +9258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="383" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>20</v>
       </c>
@@ -9263,7 +9281,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="384" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>20</v>
       </c>
@@ -9286,7 +9304,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="385" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>20</v>
       </c>
@@ -9318,7 +9336,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I321 A322:A385 I322:I385" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I193 A322:A385 I322:I385 A195:I257 A194:G194 I194 A259:I321 A258:G258 I258" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>